--- a/camera_events.xlsx
+++ b/camera_events.xlsx
@@ -5,12 +5,12 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\Synergy Safety Group\DEN\Reports\Camera Reports\Dashboard\Fiore and Sons\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\Synergy Safety Group\DEN\Dashboard\DEN Camera System\Fiore and Sons\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{17369C6B-0EFA-459C-8C7D-B37309BB462E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{4E7B70DD-3959-4495-9D32-9138EA3A4DB1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="735" yWindow="735" windowWidth="23280" windowHeight="14535" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5820" yWindow="1515" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DRIVE-ALERTS" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3651" uniqueCount="1439">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3672" uniqueCount="1453">
   <si>
     <t>DRIVE ALERTS</t>
   </si>
@@ -2578,7 +2578,7 @@
     <t>Dave Hays</t>
   </si>
   <si>
-    <t>PU6415DaveHays</t>
+    <t>PU6415SPARE</t>
   </si>
   <si>
     <t>281474988790122-1770748833888</t>
@@ -3781,25 +3781,64 @@
     <t>03/13/26 11:05 EDT</t>
   </si>
   <si>
-    <t>03/13/26 06:16 EDT</t>
-  </si>
-  <si>
-    <t>281474982930717-1773396989612</t>
-  </si>
-  <si>
-    <t>2.3mi E of Berkley CO</t>
-  </si>
-  <si>
-    <t>03/13/26 07:55 EDT</t>
-  </si>
-  <si>
-    <t>281474994873792-1773402912022</t>
-  </si>
-  <si>
-    <t>2mi W of Loveland CO</t>
-  </si>
-  <si>
-    <t>03/13/26 08:21 EDT</t>
+    <t>281474988118283-1773414345090</t>
+  </si>
+  <si>
+    <t>03/13/26 13:04 EDT</t>
+  </si>
+  <si>
+    <t>281474988596947-1773421487963</t>
+  </si>
+  <si>
+    <t>4.7mi SE of Commerce City CO</t>
+  </si>
+  <si>
+    <t>03/16/26 14:18 EDT</t>
+  </si>
+  <si>
+    <t>03/16/26 14:27 EDT</t>
+  </si>
+  <si>
+    <t>03/13/26 13:15 EDT</t>
+  </si>
+  <si>
+    <t>281474998210375-1773422123779</t>
+  </si>
+  <si>
+    <t>1.3mi N of Greenwood Village CO</t>
+  </si>
+  <si>
+    <t>03/16/26 14:12 EDT</t>
+  </si>
+  <si>
+    <t>03/13/26 15:04 EDT</t>
+  </si>
+  <si>
+    <t>281474988147905-1773428690449</t>
+  </si>
+  <si>
+    <t>5.5mi SE of Commerce City CO</t>
+  </si>
+  <si>
+    <t>03/16/26 14:16 EDT</t>
+  </si>
+  <si>
+    <t>03/16/26 22:44 EDT</t>
+  </si>
+  <si>
+    <t>03/13/26 16:10 EDT</t>
+  </si>
+  <si>
+    <t>281474989384378-1773432658111</t>
+  </si>
+  <si>
+    <t>3.6mi SE of Erie CO</t>
+  </si>
+  <si>
+    <t>03/16/26 13:12 EDT</t>
+  </si>
+  <si>
+    <t>03/13/26 16:31 EDT</t>
   </si>
   <si>
     <t>Kelly Montoya</t>
@@ -3808,13 +3847,445 @@
     <t>AU3369KellyMontoya</t>
   </si>
   <si>
-    <t>281474988538017-1773404519974</t>
-  </si>
-  <si>
-    <t>4.8mi W of Denver CO</t>
-  </si>
-  <si>
-    <t>03/13/26 08:24 EDT</t>
+    <t>281474988538017-1773433895424</t>
+  </si>
+  <si>
+    <t>2.7mi N of Aurora CO</t>
+  </si>
+  <si>
+    <t>03/16/26 14:22 EDT</t>
+  </si>
+  <si>
+    <t>03/19/26 09:03 EDT</t>
+  </si>
+  <si>
+    <t>03/13/26 17:17 EDT</t>
+  </si>
+  <si>
+    <t>281474998210156-1773436635361</t>
+  </si>
+  <si>
+    <t>1.4mi N of Derby CO</t>
+  </si>
+  <si>
+    <t>03/13/26 18:39 EDT</t>
+  </si>
+  <si>
+    <t>281474998210156-1773441565501</t>
+  </si>
+  <si>
+    <t>2.1mi W of Timnath CO</t>
+  </si>
+  <si>
+    <t>03/14/26 08:43 EDT</t>
+  </si>
+  <si>
+    <t>281474998210156-1773492223092</t>
+  </si>
+  <si>
+    <t>03/14/26 09:25 EDT</t>
+  </si>
+  <si>
+    <t>281474988055427-1773494702970</t>
+  </si>
+  <si>
+    <t>0.3mi NE of Firestone CO</t>
+  </si>
+  <si>
+    <t>03/16/26 13:05 EDT</t>
+  </si>
+  <si>
+    <t>03/16/26 13:56 EDT</t>
+  </si>
+  <si>
+    <t>03/14/26 14:10 EDT</t>
+  </si>
+  <si>
+    <t>281474998172291-1773511849784</t>
+  </si>
+  <si>
+    <t>1.1mi NW of Parker CO</t>
+  </si>
+  <si>
+    <t>03/14/26 18:17 EDT</t>
+  </si>
+  <si>
+    <t>281474989365899-1773526656718</t>
+  </si>
+  <si>
+    <t>6.5mi E of Commerce City CO</t>
+  </si>
+  <si>
+    <t>03/16/26 14:20 EDT</t>
+  </si>
+  <si>
+    <t>03/16/26 14:34 EDT</t>
+  </si>
+  <si>
+    <t>03/16/26 07:49 EDT</t>
+  </si>
+  <si>
+    <t>281474982930699-1773661759945</t>
+  </si>
+  <si>
+    <t>1.5mi S of Northglenn CO</t>
+  </si>
+  <si>
+    <t>03/17/26 11:19 EDT</t>
+  </si>
+  <si>
+    <t>03/16/26 08:15 EDT</t>
+  </si>
+  <si>
+    <t>281474988596947-1773663333731</t>
+  </si>
+  <si>
+    <t>4mi NE of Evans CO</t>
+  </si>
+  <si>
+    <t>03/17/26 11:21 EDT</t>
+  </si>
+  <si>
+    <t>03/16/26 09:24 EDT</t>
+  </si>
+  <si>
+    <t>281474988469578-1773667461027</t>
+  </si>
+  <si>
+    <t>0.9mi SW of Centennial CO</t>
+  </si>
+  <si>
+    <t>03/17/26 11:15 EDT</t>
+  </si>
+  <si>
+    <t>03/16/26 18:06 EDT</t>
+  </si>
+  <si>
+    <t>281474988882385-1773698760254</t>
+  </si>
+  <si>
+    <t>1mi NW of Welby CO</t>
+  </si>
+  <si>
+    <t>03/16/26 19:21 EDT</t>
+  </si>
+  <si>
+    <t>281474998210156-1773703263703</t>
+  </si>
+  <si>
+    <t>03/17/26 08:49 EDT</t>
+  </si>
+  <si>
+    <t>281474998210156-1773751754659</t>
+  </si>
+  <si>
+    <t>2.2mi W of Timnath CO</t>
+  </si>
+  <si>
+    <t>03/17/26 09:19 EDT</t>
+  </si>
+  <si>
+    <t>TT.4629</t>
+  </si>
+  <si>
+    <t>281474982930719-1773753586655</t>
+  </si>
+  <si>
+    <t>2.7mi NE of Stonegate CO</t>
+  </si>
+  <si>
+    <t>03/18/26 09:38 EDT</t>
+  </si>
+  <si>
+    <t>03/17/26 12:11 EDT</t>
+  </si>
+  <si>
+    <t>281474991239618-1773763871614</t>
+  </si>
+  <si>
+    <t>0.6mi S of Dove Valley CO</t>
+  </si>
+  <si>
+    <t>03/18/26 09:42 EDT</t>
+  </si>
+  <si>
+    <t>03/19/26 09:09 EDT</t>
+  </si>
+  <si>
+    <t>03/18/26 09:30 EDT</t>
+  </si>
+  <si>
+    <t>281474988147905-1773840623248</t>
+  </si>
+  <si>
+    <t>1.2mi S of Welby CO</t>
+  </si>
+  <si>
+    <t>03/19/26 11:58 EDT</t>
+  </si>
+  <si>
+    <t>03/19/26 12:00 EDT</t>
+  </si>
+  <si>
+    <t>03/18/26 17:33 EDT</t>
+  </si>
+  <si>
+    <t>281474998210375-1773869597510</t>
+  </si>
+  <si>
+    <t>3.7mi SE of Edgewater CO</t>
+  </si>
+  <si>
+    <t>03/19/26 12:03 EDT</t>
+  </si>
+  <si>
+    <t>03/18/26 17:34 EDT</t>
+  </si>
+  <si>
+    <t>281474989384378-1773869690713</t>
+  </si>
+  <si>
+    <t>4.9mi NW of Arvada CO</t>
+  </si>
+  <si>
+    <t>03/19/26 11:55 EDT</t>
+  </si>
+  <si>
+    <t>03/19/26 16:45 EDT</t>
+  </si>
+  <si>
+    <t>281474988055427-1773953128975</t>
+  </si>
+  <si>
+    <t>4.7mi NW of Four Square Mile CO</t>
+  </si>
+  <si>
+    <t>03/20/26 12:00 EDT</t>
+  </si>
+  <si>
+    <t>03/20/26 12:01 EDT</t>
+  </si>
+  <si>
+    <t>03/20/26 07:10 EDT</t>
+  </si>
+  <si>
+    <t>281474988538017-1774005052987</t>
+  </si>
+  <si>
+    <t>03/20/26 07:54 EDT</t>
+  </si>
+  <si>
+    <t>281474988469578-1774007652169</t>
+  </si>
+  <si>
+    <t>0.6mi W of Todd Creek CO</t>
+  </si>
+  <si>
+    <t>03/20/26 07:58 EDT</t>
+  </si>
+  <si>
+    <t>281474988535988-1774007880017</t>
+  </si>
+  <si>
+    <t>0.7mi N of Frederick CO</t>
+  </si>
+  <si>
+    <t>03/20/26 08:26 EDT</t>
+  </si>
+  <si>
+    <t>281474988055427-1774009578183</t>
+  </si>
+  <si>
+    <t>0.7mi W of Firestone CO</t>
+  </si>
+  <si>
+    <t>03/20/26 08:32 EDT</t>
+  </si>
+  <si>
+    <t>281474994873792-1774009940963</t>
+  </si>
+  <si>
+    <t>3.5mi NW of Firestone CO</t>
+  </si>
+  <si>
+    <t>03/20/26 08:33 EDT</t>
+  </si>
+  <si>
+    <t>281474988330103-1774009991973</t>
+  </si>
+  <si>
+    <t>2.5mi W of Dakota Ridge CO</t>
+  </si>
+  <si>
+    <t>03/20/26 08:39 EDT</t>
+  </si>
+  <si>
+    <t>281474995127998-1774010353015</t>
+  </si>
+  <si>
+    <t>8.8mi E of The Pinery CO</t>
+  </si>
+  <si>
+    <t>281474988147905-1774010375425</t>
+  </si>
+  <si>
+    <t>2.6mi E of Denver CO</t>
+  </si>
+  <si>
+    <t>03/20/26 08:44 EDT</t>
+  </si>
+  <si>
+    <t>281474995127998-1774010640965</t>
+  </si>
+  <si>
+    <t>9.1mi E of Parker CO</t>
+  </si>
+  <si>
+    <t>03/20/26 08:56 EDT</t>
+  </si>
+  <si>
+    <t>281474985934443-1774011415974</t>
+  </si>
+  <si>
+    <t>4.4mi NW of Four Square Mile CO</t>
+  </si>
+  <si>
+    <t>03/20/26 09:24 EDT</t>
+  </si>
+  <si>
+    <t>281474988414844-1774013049524</t>
+  </si>
+  <si>
+    <t>2.4mi W of Four Square Mile CO</t>
+  </si>
+  <si>
+    <t>03/20/26 11:44 EDT</t>
+  </si>
+  <si>
+    <t>281474985934443-1774021461981</t>
+  </si>
+  <si>
+    <t>4.5mi NW of Four Square Mile CO</t>
+  </si>
+  <si>
+    <t>03/20/26 11:45 EDT</t>
+  </si>
+  <si>
+    <t>Pedro Esparza</t>
+  </si>
+  <si>
+    <t>PU4330PedroEsparza</t>
+  </si>
+  <si>
+    <t>281474994772182-1774021516974</t>
+  </si>
+  <si>
+    <t>3.2mi W of Sheridan CO</t>
+  </si>
+  <si>
+    <t>03/20/26 12:10 EDT</t>
+  </si>
+  <si>
+    <t>281474998210375-1774023025978</t>
+  </si>
+  <si>
+    <t>1.3mi W of Parker CO</t>
+  </si>
+  <si>
+    <t>03/20/26 12:23 EDT</t>
+  </si>
+  <si>
+    <t>281474998210375-1774023802962</t>
+  </si>
+  <si>
+    <t>1.2mi W of Parker CO</t>
+  </si>
+  <si>
+    <t>281474988147905-1774023829800</t>
+  </si>
+  <si>
+    <t>4.2mi NW of Aurora CO</t>
+  </si>
+  <si>
+    <t>03/20/26 12:40 EDT</t>
+  </si>
+  <si>
+    <t>281474989384378-1774024811419</t>
+  </si>
+  <si>
+    <t>03/20/26 14:05 EDT</t>
+  </si>
+  <si>
+    <t>281474982930732-1774029943642</t>
+  </si>
+  <si>
+    <t>03/20/26 16:25 EDT</t>
+  </si>
+  <si>
+    <t>281474982930719-1774038336540</t>
+  </si>
+  <si>
+    <t>1.6mi SE of Columbine CO</t>
+  </si>
+  <si>
+    <t>03/20/26 16:54 EDT</t>
+  </si>
+  <si>
+    <t>281474988302231-1774040096962</t>
+  </si>
+  <si>
+    <t>2.8mi NW of Commerce City CO</t>
+  </si>
+  <si>
+    <t>03/20/26 16:55 EDT</t>
+  </si>
+  <si>
+    <t>281474988302231-1774040110964</t>
+  </si>
+  <si>
+    <t>03/20/26 17:09 EDT</t>
+  </si>
+  <si>
+    <t>281474995127998-1774040997967</t>
+  </si>
+  <si>
+    <t>10.6mi E of The Pinery CO</t>
+  </si>
+  <si>
+    <t>03/20/26 17:14 EDT</t>
+  </si>
+  <si>
+    <t>281474989363431-1774041269893</t>
+  </si>
+  <si>
+    <t>2.8mi W of Louisville CO</t>
+  </si>
+  <si>
+    <t>03/20/26 17:17 EDT</t>
+  </si>
+  <si>
+    <t>281474989365899-1774041425722</t>
+  </si>
+  <si>
+    <t>2.8mi NW of Four Square Mile CO</t>
+  </si>
+  <si>
+    <t>03/20/26 17:32 EDT</t>
+  </si>
+  <si>
+    <t>281474988055427-1774042377981</t>
+  </si>
+  <si>
+    <t>03/20/26 17:45 EDT</t>
+  </si>
+  <si>
+    <t>281474994873792-1774043157966</t>
+  </si>
+  <si>
+    <t>3.4mi NW of Firestone CO</t>
+  </si>
+  <si>
+    <t>03/20/26 18:11 EDT</t>
   </si>
   <si>
     <t>Arturo Amaya</t>
@@ -3823,166 +4294,79 @@
     <t>PU7134ArturoAmaya</t>
   </si>
   <si>
-    <t>281474988848879-1773404680965</t>
-  </si>
-  <si>
-    <t>3.8mi SE of Edgewater CO</t>
-  </si>
-  <si>
-    <t>281474988848879-1773404699973</t>
-  </si>
-  <si>
-    <t>3.8mi N of Sheridan CO</t>
-  </si>
-  <si>
-    <t>03/13/26 08:37 EDT</t>
-  </si>
-  <si>
-    <t>281474998210375-1773405435024</t>
-  </si>
-  <si>
-    <t>1.3mi W of Parker CO</t>
-  </si>
-  <si>
-    <t>03/13/26 08:46 EDT</t>
-  </si>
-  <si>
-    <t>281474995127998-1773405984013</t>
-  </si>
-  <si>
-    <t>9.1mi E of Parker CO</t>
-  </si>
-  <si>
-    <t>03/13/26 08:53 EDT</t>
-  </si>
-  <si>
-    <t>281474988302231-1773406433017</t>
-  </si>
-  <si>
-    <t>2.8mi NW of Commerce City CO</t>
-  </si>
-  <si>
-    <t>03/13/26 08:59 EDT</t>
-  </si>
-  <si>
-    <t>281474988414844-1773406785606</t>
-  </si>
-  <si>
-    <t>2.5mi SW of Centennial CO</t>
-  </si>
-  <si>
-    <t>03/13/26 09:18 EDT</t>
-  </si>
-  <si>
-    <t>281474998210375-1773407904967</t>
-  </si>
-  <si>
-    <t>1.6mi S of Gleneagle CO</t>
-  </si>
-  <si>
-    <t>03/13/26 09:22 EDT</t>
-  </si>
-  <si>
-    <t>281474988538017-1773408153973</t>
-  </si>
-  <si>
-    <t>281474988538017-1773408171960</t>
-  </si>
-  <si>
-    <t>03/13/26 09:25 EDT</t>
-  </si>
-  <si>
-    <t>281474982930739-1773408346144</t>
-  </si>
-  <si>
-    <t>2.5mi SE of Berkley CO</t>
-  </si>
-  <si>
-    <t>03/13/26 09:32 EDT</t>
-  </si>
-  <si>
-    <t>281474988275018-1773408738321</t>
-  </si>
-  <si>
-    <t>3.9mi NE of Evans CO</t>
-  </si>
-  <si>
-    <t>03/13/26 09:49 EDT</t>
-  </si>
-  <si>
-    <t>281474994873792-1773409798964</t>
-  </si>
-  <si>
-    <t>3.1mi NW of Firestone CO</t>
-  </si>
-  <si>
-    <t>03/13/26 09:50 EDT</t>
-  </si>
-  <si>
-    <t>Michael Puckett</t>
-  </si>
-  <si>
-    <t>PU9516MichaelPucket</t>
-  </si>
-  <si>
-    <t>281474988780270-1773409852973</t>
-  </si>
-  <si>
-    <t>4.3mi N of Aurora CO</t>
-  </si>
-  <si>
-    <t>03/13/26 09:53 EDT</t>
-  </si>
-  <si>
-    <t>281474988275018-1773410038323</t>
-  </si>
-  <si>
-    <t>3.6mi NE of Evans CO</t>
-  </si>
-  <si>
-    <t>03/13/26 10:09 EDT</t>
-  </si>
-  <si>
-    <t>281474994873792-1773410957956</t>
-  </si>
-  <si>
-    <t>3.5mi NW of Firestone CO</t>
-  </si>
-  <si>
-    <t>03/13/26 10:26 EDT</t>
-  </si>
-  <si>
-    <t>281474981965562-1773411990955</t>
-  </si>
-  <si>
-    <t>3.9mi SE of Berkley CO</t>
-  </si>
-  <si>
-    <t>281474982930714-1773412018963</t>
-  </si>
-  <si>
-    <t>03/13/26 10:53 EDT</t>
-  </si>
-  <si>
-    <t>281474981965562-1773413618956</t>
-  </si>
-  <si>
-    <t>3.8mi SE of Berkley CO</t>
-  </si>
-  <si>
-    <t>281474988118283-1773414345090</t>
-  </si>
-  <si>
-    <t>03/13/26 11:29 EDT</t>
-  </si>
-  <si>
-    <t>Luis 1908</t>
-  </si>
-  <si>
-    <t>281474982930736-1773415744963</t>
-  </si>
-  <si>
-    <t>03/13/26 11:43 EDT</t>
+    <t>281474988848879-1774044713499</t>
+  </si>
+  <si>
+    <t>2.9mi E of Edgewater CO</t>
+  </si>
+  <si>
+    <t>03/20/26 18:16 EDT</t>
+  </si>
+  <si>
+    <t>281474989365899-1774044993976</t>
+  </si>
+  <si>
+    <t>4.1mi E of Edgewater CO</t>
+  </si>
+  <si>
+    <t>03/20/26 18:57 EDT</t>
+  </si>
+  <si>
+    <t>281474988414844-1774047465789</t>
+  </si>
+  <si>
+    <t>1.4mi S of Aurora CO</t>
+  </si>
+  <si>
+    <t>03/21/26 09:41 EDT</t>
+  </si>
+  <si>
+    <t>281474988148287-1774100474024</t>
+  </si>
+  <si>
+    <t>281474988148287-1774100514024</t>
+  </si>
+  <si>
+    <t>2.5mi SE of Edgewater CO</t>
+  </si>
+  <si>
+    <t>03/21/26 13:12 EDT</t>
+  </si>
+  <si>
+    <t>281474988148287-1774113130980</t>
+  </si>
+  <si>
+    <t>4.8mi NW of Aurora CO</t>
+  </si>
+  <si>
+    <t>03/21/26 13:50 EDT</t>
+  </si>
+  <si>
+    <t>281474988148287-1774115440601</t>
+  </si>
+  <si>
+    <t>1.9mi NE of Cherry Hills Village CO</t>
+  </si>
+  <si>
+    <t>03/21/26 13:55 EDT</t>
+  </si>
+  <si>
+    <t>281474988055427-1774115702975</t>
+  </si>
+  <si>
+    <t>2mi NW of Four Square Mile CO</t>
+  </si>
+  <si>
+    <t>03/21/26 14:01 EDT</t>
+  </si>
+  <si>
+    <t>281474985934443-1774116077975</t>
+  </si>
+  <si>
+    <t>4.8mi N of Aurora CO</t>
+  </si>
+  <si>
+    <t>03/21/26 16:16 EDT</t>
   </si>
   <si>
     <t>Luis Hernandez</t>
@@ -3991,352 +4375,10 @@
     <t>PU7791LuisHernandez</t>
   </si>
   <si>
-    <t>281474988794180-1773416634485</t>
-  </si>
-  <si>
-    <t>1.4mi SW of Parker CO</t>
-  </si>
-  <si>
-    <t>03/13/26 11:44 EDT</t>
-  </si>
-  <si>
-    <t>281474981965562-1773416679557</t>
-  </si>
-  <si>
-    <t>03/13/26 12:20 EDT</t>
-  </si>
-  <si>
-    <t>281474982930712-1773418836968</t>
-  </si>
-  <si>
-    <t>03/13/26 12:21 EDT</t>
-  </si>
-  <si>
-    <t>Don Derbidge</t>
-  </si>
-  <si>
-    <t>PU9494DonDerbridge</t>
-  </si>
-  <si>
-    <t>281474988389049-1773418866987</t>
-  </si>
-  <si>
-    <t>281474982930732-1773418874173</t>
-  </si>
-  <si>
-    <t>2.8mi SE of Berkley CO</t>
-  </si>
-  <si>
-    <t>03/13/26 12:42 EDT</t>
-  </si>
-  <si>
-    <t>281474998210375-1773420135072</t>
-  </si>
-  <si>
-    <t>1.3mi NW of Monument CO</t>
-  </si>
-  <si>
-    <t>03/13/26 12:59 EDT</t>
-  </si>
-  <si>
-    <t>281474988147905-1773421196534</t>
-  </si>
-  <si>
-    <t>3.4mi E of Commerce City CO</t>
-  </si>
-  <si>
-    <t>03/13/26 13:04 EDT</t>
-  </si>
-  <si>
-    <t>281474988596947-1773421487963</t>
-  </si>
-  <si>
-    <t>4.7mi SE of Commerce City CO</t>
-  </si>
-  <si>
-    <t>03/13/26 13:15 EDT</t>
-  </si>
-  <si>
-    <t>281474998210375-1773422123779</t>
-  </si>
-  <si>
-    <t>1.3mi N of Greenwood Village CO</t>
-  </si>
-  <si>
-    <t>03/13/26 13:17 EDT</t>
-  </si>
-  <si>
-    <t>281474982930712-1773422261993</t>
-  </si>
-  <si>
-    <t>03/13/26 14:05 EDT</t>
-  </si>
-  <si>
-    <t>281474985153050-1773425144973</t>
-  </si>
-  <si>
-    <t>Truman 1556</t>
-  </si>
-  <si>
-    <t>VAC-0342</t>
-  </si>
-  <si>
-    <t>281474994121377-1773425159426</t>
-  </si>
-  <si>
-    <t>4.1mi N of Englewood CO</t>
-  </si>
-  <si>
-    <t>03/13/26 14:29 EDT</t>
-  </si>
-  <si>
-    <t>281474988147905-1773426546580</t>
-  </si>
-  <si>
-    <t>03/13/26 14:31 EDT</t>
-  </si>
-  <si>
-    <t>281474985153050-1773426706972</t>
-  </si>
-  <si>
-    <t>03/13/26 15:02 EDT</t>
-  </si>
-  <si>
-    <t>281474988389049-1773428554976</t>
-  </si>
-  <si>
-    <t>03/13/26 15:04 EDT</t>
-  </si>
-  <si>
-    <t>281474988147905-1773428690449</t>
-  </si>
-  <si>
-    <t>5.5mi SE of Commerce City CO</t>
-  </si>
-  <si>
-    <t>03/13/26 15:06 EDT</t>
-  </si>
-  <si>
-    <t>Jasmyn Jamison</t>
-  </si>
-  <si>
-    <t>PU8712JasmynJamison</t>
-  </si>
-  <si>
-    <t>281474995099755-1773428794205</t>
-  </si>
-  <si>
-    <t>0.7mi W of Northglenn CO</t>
-  </si>
-  <si>
-    <t>03/13/26 15:08 EDT</t>
-  </si>
-  <si>
-    <t>281474982930730-1773428908958</t>
-  </si>
-  <si>
-    <t>03/13/26 15:55 EDT</t>
-  </si>
-  <si>
-    <t>281474995127998-1773431716039</t>
-  </si>
-  <si>
-    <t>10.5mi E of The Pinery CO</t>
-  </si>
-  <si>
-    <t>03/13/26 16:06 EDT</t>
-  </si>
-  <si>
-    <t>281474988147905-1773432378214</t>
-  </si>
-  <si>
-    <t>03/13/26 16:10 EDT</t>
-  </si>
-  <si>
-    <t>281474989384378-1773432658111</t>
-  </si>
-  <si>
-    <t>3.6mi SE of Erie CO</t>
-  </si>
-  <si>
-    <t>03/13/26 16:31 EDT</t>
-  </si>
-  <si>
-    <t>281474988538017-1773433895424</t>
-  </si>
-  <si>
-    <t>2.7mi N of Aurora CO</t>
-  </si>
-  <si>
-    <t>03/13/26 16:42 EDT</t>
-  </si>
-  <si>
-    <t>281474982930705-1773434531145</t>
-  </si>
-  <si>
-    <t>1.2mi N of Derby CO</t>
-  </si>
-  <si>
-    <t>03/13/26 17:01 EDT</t>
-  </si>
-  <si>
-    <t>281474995127998-1773435682392</t>
-  </si>
-  <si>
-    <t>03/13/26 17:12 EDT</t>
-  </si>
-  <si>
-    <t>281474988596947-1773436329972</t>
-  </si>
-  <si>
-    <t>3.3mi E of Commerce City CO</t>
-  </si>
-  <si>
-    <t>03/13/26 17:17 EDT</t>
-  </si>
-  <si>
-    <t>281474998210156-1773436635361</t>
-  </si>
-  <si>
-    <t>1.4mi N of Derby CO</t>
-  </si>
-  <si>
-    <t>03/13/26 17:20 EDT</t>
-  </si>
-  <si>
-    <t>281474988330103-1773436818042</t>
-  </si>
-  <si>
-    <t>2.5mi W of Dakota Ridge CO</t>
-  </si>
-  <si>
-    <t>03/13/26 17:40 EDT</t>
-  </si>
-  <si>
-    <t>Preston Anderson</t>
-  </si>
-  <si>
-    <t>PU7389PrestonAnderson</t>
-  </si>
-  <si>
-    <t>281474995132300-1773438011014</t>
-  </si>
-  <si>
-    <t>2.9mi SE of Edgewater CO</t>
-  </si>
-  <si>
-    <t>03/13/26 17:45 EDT</t>
-  </si>
-  <si>
-    <t>281474988596947-1773438341649</t>
-  </si>
-  <si>
-    <t>9.8mi NE of Lochbuie CO</t>
-  </si>
-  <si>
-    <t>03/13/26 17:52 EDT</t>
-  </si>
-  <si>
-    <t>281474998210375-1773438776963</t>
-  </si>
-  <si>
-    <t>1.4mi W of Parker CO</t>
-  </si>
-  <si>
-    <t>03/13/26 17:53 EDT</t>
-  </si>
-  <si>
-    <t>281474998210375-1773438806964</t>
-  </si>
-  <si>
-    <t>03/13/26 18:22 EDT</t>
-  </si>
-  <si>
-    <t>281474988389049-1773440561977</t>
-  </si>
-  <si>
-    <t>2mi N of Cherry Hills Village CO</t>
-  </si>
-  <si>
-    <t>03/13/26 18:28 EDT</t>
-  </si>
-  <si>
-    <t>281474995132300-1773440883965</t>
-  </si>
-  <si>
-    <t>1.3mi SW of Greenwood Village CO</t>
-  </si>
-  <si>
-    <t>03/13/26 18:38 EDT</t>
-  </si>
-  <si>
-    <t>281474982930708-1773441512061</t>
-  </si>
-  <si>
-    <t>0.3mi NW of Firestone CO</t>
-  </si>
-  <si>
-    <t>03/13/26 18:39 EDT</t>
-  </si>
-  <si>
-    <t>281474998210156-1773441565501</t>
-  </si>
-  <si>
-    <t>2.1mi W of Timnath CO</t>
-  </si>
-  <si>
-    <t>03/13/26 18:46 EDT</t>
-  </si>
-  <si>
-    <t>281474989384378-1773442006083</t>
-  </si>
-  <si>
-    <t>2.3mi W of Timnath CO</t>
-  </si>
-  <si>
-    <t>03/13/26 19:01 EDT</t>
-  </si>
-  <si>
-    <t>281474988148287-1773442896973</t>
-  </si>
-  <si>
-    <t>3.1mi SE of Edgewater CO</t>
-  </si>
-  <si>
-    <t>03/13/26 19:20 EDT</t>
-  </si>
-  <si>
-    <t>281474988302231-1773444041966</t>
-  </si>
-  <si>
-    <t>03/13/26 20:21 EDT</t>
-  </si>
-  <si>
-    <t>281474995132300-1773447711980</t>
-  </si>
-  <si>
-    <t>03/14/26 08:43 EDT</t>
-  </si>
-  <si>
-    <t>281474998210156-1773492223092</t>
-  </si>
-  <si>
-    <t>03/14/26 09:14 EDT</t>
-  </si>
-  <si>
-    <t>281474988055427-1773494068018</t>
-  </si>
-  <si>
-    <t>0.7mi W of Firestone CO</t>
-  </si>
-  <si>
-    <t>03/14/26 09:25 EDT</t>
-  </si>
-  <si>
-    <t>281474988055427-1773494702970</t>
-  </si>
-  <si>
-    <t>0.3mi NE of Firestone CO</t>
+    <t>281474988794180-1774124216971</t>
+  </si>
+  <si>
+    <t>4.7mi N of Aurora CO</t>
   </si>
 </sst>
 </file>
@@ -4698,7 +4740,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M413"/>
+  <dimension ref="A1:M408"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="13" width="15" customWidth="1"/>
@@ -17056,30 +17098,28 @@
     </row>
     <row r="349" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A349" s="3" t="s">
+        <v>1252</v>
+      </c>
+      <c r="B349" s="3" t="s">
+        <v>758</v>
+      </c>
+      <c r="C349" s="3" t="s">
+        <v>759</v>
+      </c>
+      <c r="D349" s="3" t="s">
         <v>1253</v>
       </c>
-      <c r="B349" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="C349" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="D349" s="3" t="s">
-        <v>1254</v>
-      </c>
       <c r="E349" s="3" t="s">
-        <v>123</v>
+        <v>469</v>
       </c>
       <c r="F349" s="3" t="s">
-        <v>1255</v>
+        <v>842</v>
       </c>
       <c r="G349" s="3"/>
       <c r="H349" s="3">
-        <v>62</v>
-      </c>
-      <c r="I349" s="3">
-        <v>55</v>
-      </c>
+        <v>41</v>
+      </c>
+      <c r="I349" s="3"/>
       <c r="J349" s="3" t="s">
         <v>471</v>
       </c>
@@ -17089,185 +17129,223 @@
     </row>
     <row r="350" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A350" s="3" t="s">
+        <v>1254</v>
+      </c>
+      <c r="B350" s="3" t="s">
+        <v>1058</v>
+      </c>
+      <c r="C350" s="3" t="s">
+        <v>1059</v>
+      </c>
+      <c r="D350" s="3" t="s">
+        <v>1255</v>
+      </c>
+      <c r="E350" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="F350" s="3" t="s">
         <v>1256</v>
       </c>
-      <c r="B350" s="3" t="s">
-        <v>1069</v>
-      </c>
-      <c r="C350" s="3" t="s">
-        <v>1070</v>
-      </c>
-      <c r="D350" s="3" t="s">
-        <v>1257</v>
-      </c>
-      <c r="E350" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="F350" s="3" t="s">
-        <v>1258</v>
-      </c>
-      <c r="G350" s="3"/>
+      <c r="G350" s="3" t="s">
+        <v>748</v>
+      </c>
       <c r="H350" s="3">
-        <v>18</v>
+        <v>39</v>
       </c>
       <c r="I350" s="3"/>
       <c r="J350" s="3" t="s">
-        <v>471</v>
-      </c>
-      <c r="K350" s="3"/>
-      <c r="L350" s="3"/>
-      <c r="M350" s="3"/>
+        <v>21</v>
+      </c>
+      <c r="K350" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="L350" s="3" t="s">
+        <v>1257</v>
+      </c>
+      <c r="M350" s="3" t="s">
+        <v>1258</v>
+      </c>
     </row>
     <row r="351" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A351" s="3" t="s">
         <v>1259</v>
       </c>
       <c r="B351" s="3" t="s">
+        <v>890</v>
+      </c>
+      <c r="C351" s="3" t="s">
+        <v>891</v>
+      </c>
+      <c r="D351" s="3" t="s">
         <v>1260</v>
       </c>
-      <c r="C351" s="3" t="s">
+      <c r="E351" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="F351" s="3" t="s">
         <v>1261</v>
       </c>
-      <c r="D351" s="3" t="s">
+      <c r="G351" s="3" t="s">
+        <v>748</v>
+      </c>
+      <c r="H351" s="3">
+        <v>60</v>
+      </c>
+      <c r="I351" s="3">
+        <v>65</v>
+      </c>
+      <c r="J351" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="K351" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="L351" s="3" t="s">
         <v>1262</v>
       </c>
-      <c r="E351" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="F351" s="3" t="s">
-        <v>1263</v>
-      </c>
-      <c r="G351" s="3"/>
-      <c r="H351" s="3">
-        <v>16</v>
-      </c>
-      <c r="I351" s="3"/>
-      <c r="J351" s="3" t="s">
-        <v>471</v>
-      </c>
-      <c r="K351" s="3"/>
-      <c r="L351" s="3"/>
       <c r="M351" s="3"/>
     </row>
     <row r="352" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A352" s="3" t="s">
+        <v>1263</v>
+      </c>
+      <c r="B352" s="3" t="s">
+        <v>896</v>
+      </c>
+      <c r="C352" s="3" t="s">
+        <v>897</v>
+      </c>
+      <c r="D352" s="3" t="s">
         <v>1264</v>
       </c>
-      <c r="B352" s="3" t="s">
+      <c r="E352" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="F352" s="3" t="s">
         <v>1265</v>
       </c>
-      <c r="C352" s="3" t="s">
-        <v>1266</v>
-      </c>
-      <c r="D352" s="3" t="s">
-        <v>1267</v>
-      </c>
-      <c r="E352" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="F352" s="3" t="s">
-        <v>1268</v>
-      </c>
-      <c r="G352" s="3"/>
-      <c r="H352" s="3">
-        <v>21</v>
-      </c>
+      <c r="G352" s="3" t="s">
+        <v>748</v>
+      </c>
+      <c r="H352" s="3"/>
       <c r="I352" s="3"/>
       <c r="J352" s="3" t="s">
-        <v>471</v>
-      </c>
-      <c r="K352" s="3"/>
-      <c r="L352" s="3"/>
-      <c r="M352" s="3"/>
+        <v>21</v>
+      </c>
+      <c r="K352" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="L352" s="3" t="s">
+        <v>1266</v>
+      </c>
+      <c r="M352" s="3" t="s">
+        <v>1267</v>
+      </c>
     </row>
     <row r="353" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A353" s="3" t="s">
-        <v>1264</v>
+        <v>1268</v>
       </c>
       <c r="B353" s="3" t="s">
-        <v>1265</v>
+        <v>781</v>
       </c>
       <c r="C353" s="3" t="s">
-        <v>1266</v>
+        <v>782</v>
       </c>
       <c r="D353" s="3" t="s">
         <v>1269</v>
       </c>
       <c r="E353" s="3" t="s">
-        <v>19</v>
+        <v>123</v>
       </c>
       <c r="F353" s="3" t="s">
         <v>1270</v>
       </c>
-      <c r="G353" s="3"/>
+      <c r="G353" s="3" t="s">
+        <v>748</v>
+      </c>
       <c r="H353" s="3">
-        <v>29</v>
-      </c>
-      <c r="I353" s="3"/>
+        <v>74</v>
+      </c>
+      <c r="I353" s="3">
+        <v>75</v>
+      </c>
       <c r="J353" s="3" t="s">
-        <v>471</v>
-      </c>
-      <c r="K353" s="3"/>
-      <c r="L353" s="3"/>
+        <v>21</v>
+      </c>
+      <c r="K353" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="L353" s="3" t="s">
+        <v>1271</v>
+      </c>
       <c r="M353" s="3"/>
     </row>
     <row r="354" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A354" s="3" t="s">
-        <v>1271</v>
+        <v>1272</v>
       </c>
       <c r="B354" s="3" t="s">
-        <v>890</v>
+        <v>1273</v>
       </c>
       <c r="C354" s="3" t="s">
-        <v>891</v>
+        <v>1274</v>
       </c>
       <c r="D354" s="3" t="s">
-        <v>1272</v>
+        <v>1275</v>
       </c>
       <c r="E354" s="3" t="s">
-        <v>19</v>
+        <v>123</v>
       </c>
       <c r="F354" s="3" t="s">
-        <v>1273</v>
-      </c>
-      <c r="G354" s="3"/>
+        <v>1276</v>
+      </c>
+      <c r="G354" s="3" t="s">
+        <v>748</v>
+      </c>
       <c r="H354" s="3">
-        <v>21</v>
-      </c>
-      <c r="I354" s="3"/>
+        <v>31</v>
+      </c>
+      <c r="I354" s="3">
+        <v>75</v>
+      </c>
       <c r="J354" s="3" t="s">
-        <v>471</v>
-      </c>
-      <c r="K354" s="3"/>
-      <c r="L354" s="3"/>
-      <c r="M354" s="3"/>
+        <v>21</v>
+      </c>
+      <c r="K354" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="L354" s="3" t="s">
+        <v>1277</v>
+      </c>
+      <c r="M354" s="3" t="s">
+        <v>1278</v>
+      </c>
     </row>
     <row r="355" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A355" s="3" t="s">
-        <v>1274</v>
+        <v>1279</v>
       </c>
       <c r="B355" s="3" t="s">
-        <v>1019</v>
+        <v>1163</v>
       </c>
       <c r="C355" s="3" t="s">
-        <v>1020</v>
+        <v>1164</v>
       </c>
       <c r="D355" s="3" t="s">
-        <v>1275</v>
+        <v>1280</v>
       </c>
       <c r="E355" s="3" t="s">
-        <v>19</v>
+        <v>45</v>
       </c>
       <c r="F355" s="3" t="s">
-        <v>1276</v>
+        <v>1281</v>
       </c>
       <c r="G355" s="3"/>
       <c r="H355" s="3">
-        <v>24</v>
-      </c>
-      <c r="I355" s="3">
-        <v>40</v>
-      </c>
+        <v>42</v>
+      </c>
+      <c r="I355" s="3"/>
       <c r="J355" s="3" t="s">
         <v>471</v>
       </c>
@@ -17277,26 +17355,26 @@
     </row>
     <row r="356" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A356" s="3" t="s">
-        <v>1277</v>
+        <v>1282</v>
       </c>
       <c r="B356" s="3" t="s">
-        <v>811</v>
+        <v>1163</v>
       </c>
       <c r="C356" s="3" t="s">
-        <v>812</v>
+        <v>1164</v>
       </c>
       <c r="D356" s="3" t="s">
-        <v>1278</v>
+        <v>1283</v>
       </c>
       <c r="E356" s="3" t="s">
-        <v>19</v>
+        <v>45</v>
       </c>
       <c r="F356" s="3" t="s">
-        <v>1279</v>
+        <v>1284</v>
       </c>
       <c r="G356" s="3"/>
       <c r="H356" s="3">
-        <v>17</v>
+        <v>57</v>
       </c>
       <c r="I356" s="3"/>
       <c r="J356" s="3" t="s">
@@ -17308,30 +17386,28 @@
     </row>
     <row r="357" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A357" s="3" t="s">
-        <v>1280</v>
+        <v>1285</v>
       </c>
       <c r="B357" s="3" t="s">
-        <v>870</v>
+        <v>1163</v>
       </c>
       <c r="C357" s="3" t="s">
-        <v>871</v>
+        <v>1164</v>
       </c>
       <c r="D357" s="3" t="s">
-        <v>1281</v>
+        <v>1286</v>
       </c>
       <c r="E357" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F357" s="3" t="s">
-        <v>1282</v>
+        <v>1284</v>
       </c>
       <c r="G357" s="3"/>
       <c r="H357" s="3">
-        <v>55</v>
-      </c>
-      <c r="I357" s="3">
-        <v>65</v>
-      </c>
+        <v>63</v>
+      </c>
+      <c r="I357" s="3"/>
       <c r="J357" s="3" t="s">
         <v>471</v>
       </c>
@@ -17341,57 +17417,65 @@
     </row>
     <row r="358" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A358" s="3" t="s">
-        <v>1283</v>
+        <v>1287</v>
       </c>
       <c r="B358" s="3" t="s">
-        <v>890</v>
+        <v>1115</v>
       </c>
       <c r="C358" s="3" t="s">
-        <v>891</v>
+        <v>1116</v>
       </c>
       <c r="D358" s="3" t="s">
-        <v>1284</v>
+        <v>1288</v>
       </c>
       <c r="E358" s="3" t="s">
         <v>19</v>
       </c>
       <c r="F358" s="3" t="s">
-        <v>1285</v>
-      </c>
-      <c r="G358" s="3"/>
+        <v>1289</v>
+      </c>
+      <c r="G358" s="3" t="s">
+        <v>748</v>
+      </c>
       <c r="H358" s="3">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="I358" s="3"/>
       <c r="J358" s="3" t="s">
-        <v>471</v>
-      </c>
-      <c r="K358" s="3"/>
-      <c r="L358" s="3"/>
-      <c r="M358" s="3"/>
+        <v>21</v>
+      </c>
+      <c r="K358" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="L358" s="3" t="s">
+        <v>1290</v>
+      </c>
+      <c r="M358" s="3" t="s">
+        <v>1291</v>
+      </c>
     </row>
     <row r="359" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A359" s="3" t="s">
-        <v>1286</v>
+        <v>1292</v>
       </c>
       <c r="B359" s="3" t="s">
-        <v>1260</v>
+        <v>925</v>
       </c>
       <c r="C359" s="3" t="s">
-        <v>1261</v>
+        <v>926</v>
       </c>
       <c r="D359" s="3" t="s">
-        <v>1287</v>
+        <v>1293</v>
       </c>
       <c r="E359" s="3" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="F359" s="3" t="s">
-        <v>1263</v>
+        <v>1294</v>
       </c>
       <c r="G359" s="3"/>
       <c r="H359" s="3">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="I359" s="3"/>
       <c r="J359" s="3" t="s">
@@ -17403,152 +17487,178 @@
     </row>
     <row r="360" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A360" s="3" t="s">
-        <v>1286</v>
+        <v>1295</v>
       </c>
       <c r="B360" s="3" t="s">
-        <v>1260</v>
+        <v>791</v>
       </c>
       <c r="C360" s="3" t="s">
-        <v>1261</v>
+        <v>792</v>
       </c>
       <c r="D360" s="3" t="s">
-        <v>1288</v>
+        <v>1296</v>
       </c>
       <c r="E360" s="3" t="s">
-        <v>19</v>
+        <v>123</v>
       </c>
       <c r="F360" s="3" t="s">
-        <v>1263</v>
-      </c>
-      <c r="G360" s="3"/>
+        <v>1297</v>
+      </c>
+      <c r="G360" s="3" t="s">
+        <v>748</v>
+      </c>
       <c r="H360" s="3">
-        <v>26</v>
+        <v>71</v>
       </c>
       <c r="I360" s="3"/>
       <c r="J360" s="3" t="s">
-        <v>471</v>
-      </c>
-      <c r="K360" s="3"/>
-      <c r="L360" s="3"/>
-      <c r="M360" s="3"/>
+        <v>21</v>
+      </c>
+      <c r="K360" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="L360" s="3" t="s">
+        <v>1298</v>
+      </c>
+      <c r="M360" s="3" t="s">
+        <v>1299</v>
+      </c>
     </row>
     <row r="361" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A361" s="3" t="s">
-        <v>1289</v>
+        <v>1300</v>
       </c>
       <c r="B361" s="3" t="s">
-        <v>493</v>
+        <v>63</v>
       </c>
       <c r="C361" s="3" t="s">
-        <v>494</v>
+        <v>64</v>
       </c>
       <c r="D361" s="3" t="s">
-        <v>1290</v>
+        <v>1301</v>
       </c>
       <c r="E361" s="3" t="s">
-        <v>26</v>
+        <v>123</v>
       </c>
       <c r="F361" s="3" t="s">
-        <v>1291</v>
-      </c>
-      <c r="G361" s="3"/>
+        <v>1302</v>
+      </c>
+      <c r="G361" s="3" t="s">
+        <v>748</v>
+      </c>
       <c r="H361" s="3">
-        <v>18</v>
+        <v>63</v>
       </c>
       <c r="I361" s="3"/>
       <c r="J361" s="3" t="s">
-        <v>471</v>
-      </c>
-      <c r="K361" s="3"/>
-      <c r="L361" s="3"/>
+        <v>21</v>
+      </c>
+      <c r="K361" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="L361" s="3" t="s">
+        <v>1303</v>
+      </c>
       <c r="M361" s="3"/>
     </row>
     <row r="362" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A362" s="3" t="s">
-        <v>1292</v>
+        <v>1304</v>
       </c>
       <c r="B362" s="3" t="s">
-        <v>1168</v>
+        <v>1058</v>
       </c>
       <c r="C362" s="3" t="s">
-        <v>1169</v>
+        <v>1059</v>
       </c>
       <c r="D362" s="3" t="s">
-        <v>1293</v>
+        <v>1305</v>
       </c>
       <c r="E362" s="3" t="s">
-        <v>100</v>
+        <v>123</v>
       </c>
       <c r="F362" s="3" t="s">
-        <v>1294</v>
-      </c>
-      <c r="G362" s="3"/>
+        <v>1306</v>
+      </c>
+      <c r="G362" s="3" t="s">
+        <v>748</v>
+      </c>
       <c r="H362" s="3">
-        <v>47</v>
+        <v>19</v>
       </c>
       <c r="I362" s="3"/>
       <c r="J362" s="3" t="s">
-        <v>471</v>
-      </c>
-      <c r="K362" s="3"/>
-      <c r="L362" s="3"/>
+        <v>21</v>
+      </c>
+      <c r="K362" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="L362" s="3" t="s">
+        <v>1307</v>
+      </c>
       <c r="M362" s="3"/>
     </row>
     <row r="363" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A363" s="3" t="s">
-        <v>1295</v>
+        <v>1308</v>
       </c>
       <c r="B363" s="3" t="s">
-        <v>1069</v>
+        <v>805</v>
       </c>
       <c r="C363" s="3" t="s">
-        <v>1070</v>
+        <v>806</v>
       </c>
       <c r="D363" s="3" t="s">
-        <v>1296</v>
+        <v>1309</v>
       </c>
       <c r="E363" s="3" t="s">
-        <v>19</v>
+        <v>123</v>
       </c>
       <c r="F363" s="3" t="s">
-        <v>1297</v>
-      </c>
-      <c r="G363" s="3"/>
+        <v>1310</v>
+      </c>
+      <c r="G363" s="3" t="s">
+        <v>748</v>
+      </c>
       <c r="H363" s="3">
-        <v>18</v>
+        <v>63</v>
       </c>
       <c r="I363" s="3">
-        <v>45</v>
+        <v>65</v>
       </c>
       <c r="J363" s="3" t="s">
-        <v>471</v>
-      </c>
-      <c r="K363" s="3"/>
-      <c r="L363" s="3"/>
+        <v>21</v>
+      </c>
+      <c r="K363" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="L363" s="3" t="s">
+        <v>1311</v>
+      </c>
       <c r="M363" s="3"/>
     </row>
     <row r="364" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A364" s="3" t="s">
-        <v>1298</v>
+        <v>1312</v>
       </c>
       <c r="B364" s="3" t="s">
-        <v>1299</v>
+        <v>1083</v>
       </c>
       <c r="C364" s="3" t="s">
-        <v>1300</v>
+        <v>1084</v>
       </c>
       <c r="D364" s="3" t="s">
-        <v>1301</v>
+        <v>1313</v>
       </c>
       <c r="E364" s="3" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="F364" s="3" t="s">
-        <v>1302</v>
+        <v>1314</v>
       </c>
       <c r="G364" s="3"/>
       <c r="H364" s="3">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="I364" s="3"/>
       <c r="J364" s="3" t="s">
@@ -17560,26 +17670,26 @@
     </row>
     <row r="365" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A365" s="3" t="s">
-        <v>1303</v>
+        <v>1315</v>
       </c>
       <c r="B365" s="3" t="s">
-        <v>1168</v>
+        <v>1163</v>
       </c>
       <c r="C365" s="3" t="s">
-        <v>1169</v>
+        <v>1164</v>
       </c>
       <c r="D365" s="3" t="s">
-        <v>1304</v>
+        <v>1316</v>
       </c>
       <c r="E365" s="3" t="s">
-        <v>100</v>
+        <v>45</v>
       </c>
       <c r="F365" s="3" t="s">
-        <v>1305</v>
+        <v>1235</v>
       </c>
       <c r="G365" s="3"/>
       <c r="H365" s="3">
-        <v>44</v>
+        <v>5</v>
       </c>
       <c r="I365" s="3"/>
       <c r="J365" s="3" t="s">
@@ -17591,26 +17701,26 @@
     </row>
     <row r="366" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A366" s="3" t="s">
-        <v>1306</v>
+        <v>1317</v>
       </c>
       <c r="B366" s="3" t="s">
-        <v>1069</v>
+        <v>1163</v>
       </c>
       <c r="C366" s="3" t="s">
-        <v>1070</v>
+        <v>1164</v>
       </c>
       <c r="D366" s="3" t="s">
-        <v>1307</v>
+        <v>1318</v>
       </c>
       <c r="E366" s="3" t="s">
-        <v>19</v>
+        <v>45</v>
       </c>
       <c r="F366" s="3" t="s">
-        <v>1308</v>
+        <v>1319</v>
       </c>
       <c r="G366" s="3"/>
       <c r="H366" s="3">
-        <v>14</v>
+        <v>29</v>
       </c>
       <c r="I366" s="3">
         <v>45</v>
@@ -17624,212 +17734,262 @@
     </row>
     <row r="367" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A367" s="3" t="s">
-        <v>1309</v>
+        <v>1320</v>
       </c>
       <c r="B367" s="3" t="s">
-        <v>153</v>
+        <v>180</v>
       </c>
       <c r="C367" s="3" t="s">
-        <v>154</v>
+        <v>1321</v>
       </c>
       <c r="D367" s="3" t="s">
-        <v>1310</v>
+        <v>1322</v>
       </c>
       <c r="E367" s="3" t="s">
-        <v>19</v>
+        <v>123</v>
       </c>
       <c r="F367" s="3" t="s">
-        <v>1311</v>
-      </c>
-      <c r="G367" s="3"/>
+        <v>1323</v>
+      </c>
+      <c r="G367" s="3" t="s">
+        <v>748</v>
+      </c>
       <c r="H367" s="3">
-        <v>12</v>
-      </c>
-      <c r="I367" s="3"/>
+        <v>53</v>
+      </c>
+      <c r="I367" s="3">
+        <v>75</v>
+      </c>
       <c r="J367" s="3" t="s">
-        <v>471</v>
-      </c>
-      <c r="K367" s="3"/>
-      <c r="L367" s="3"/>
+        <v>21</v>
+      </c>
+      <c r="K367" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="L367" s="3" t="s">
+        <v>1324</v>
+      </c>
       <c r="M367" s="3"/>
     </row>
     <row r="368" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A368" s="3" t="s">
-        <v>1309</v>
+        <v>1325</v>
       </c>
       <c r="B368" s="3" t="s">
-        <v>110</v>
+        <v>368</v>
       </c>
       <c r="C368" s="3" t="s">
-        <v>111</v>
+        <v>369</v>
       </c>
       <c r="D368" s="3" t="s">
-        <v>1312</v>
+        <v>1326</v>
       </c>
       <c r="E368" s="3" t="s">
-        <v>19</v>
+        <v>123</v>
       </c>
       <c r="F368" s="3" t="s">
-        <v>1311</v>
-      </c>
-      <c r="G368" s="3"/>
+        <v>1327</v>
+      </c>
+      <c r="G368" s="3" t="s">
+        <v>748</v>
+      </c>
       <c r="H368" s="3">
-        <v>11</v>
+        <v>41</v>
       </c>
       <c r="I368" s="3"/>
       <c r="J368" s="3" t="s">
-        <v>471</v>
-      </c>
-      <c r="K368" s="3"/>
-      <c r="L368" s="3"/>
-      <c r="M368" s="3"/>
+        <v>21</v>
+      </c>
+      <c r="K368" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="L368" s="3" t="s">
+        <v>1328</v>
+      </c>
+      <c r="M368" s="3" t="s">
+        <v>1329</v>
+      </c>
     </row>
     <row r="369" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A369" s="3" t="s">
-        <v>1313</v>
+        <v>1330</v>
       </c>
       <c r="B369" s="3" t="s">
-        <v>153</v>
+        <v>896</v>
       </c>
       <c r="C369" s="3" t="s">
-        <v>154</v>
+        <v>897</v>
       </c>
       <c r="D369" s="3" t="s">
-        <v>1314</v>
+        <v>1331</v>
       </c>
       <c r="E369" s="3" t="s">
-        <v>19</v>
+        <v>123</v>
       </c>
       <c r="F369" s="3" t="s">
-        <v>1315</v>
-      </c>
-      <c r="G369" s="3"/>
+        <v>1332</v>
+      </c>
+      <c r="G369" s="3" t="s">
+        <v>748</v>
+      </c>
       <c r="H369" s="3">
-        <v>11</v>
-      </c>
-      <c r="I369" s="3"/>
+        <v>59</v>
+      </c>
+      <c r="I369" s="3">
+        <v>65</v>
+      </c>
       <c r="J369" s="3" t="s">
-        <v>471</v>
-      </c>
-      <c r="K369" s="3"/>
-      <c r="L369" s="3"/>
-      <c r="M369" s="3"/>
+        <v>21</v>
+      </c>
+      <c r="K369" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="L369" s="3" t="s">
+        <v>1333</v>
+      </c>
+      <c r="M369" s="3" t="s">
+        <v>1334</v>
+      </c>
     </row>
     <row r="370" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A370" s="3" t="s">
-        <v>1252</v>
+        <v>1335</v>
       </c>
       <c r="B370" s="3" t="s">
-        <v>758</v>
+        <v>890</v>
       </c>
       <c r="C370" s="3" t="s">
-        <v>759</v>
+        <v>891</v>
       </c>
       <c r="D370" s="3" t="s">
-        <v>1316</v>
+        <v>1336</v>
       </c>
       <c r="E370" s="3" t="s">
-        <v>469</v>
+        <v>123</v>
       </c>
       <c r="F370" s="3" t="s">
-        <v>842</v>
-      </c>
-      <c r="G370" s="3"/>
+        <v>1337</v>
+      </c>
+      <c r="G370" s="3" t="s">
+        <v>748</v>
+      </c>
       <c r="H370" s="3">
-        <v>41</v>
-      </c>
-      <c r="I370" s="3"/>
+        <v>49</v>
+      </c>
+      <c r="I370" s="3">
+        <v>55</v>
+      </c>
       <c r="J370" s="3" t="s">
-        <v>471</v>
-      </c>
-      <c r="K370" s="3"/>
-      <c r="L370" s="3"/>
+        <v>21</v>
+      </c>
+      <c r="K370" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="L370" s="3" t="s">
+        <v>1338</v>
+      </c>
       <c r="M370" s="3"/>
     </row>
     <row r="371" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A371" s="3" t="s">
-        <v>1317</v>
+        <v>1339</v>
       </c>
       <c r="B371" s="3" t="s">
-        <v>1318</v>
+        <v>781</v>
       </c>
       <c r="C371" s="3" t="s">
-        <v>77</v>
+        <v>782</v>
       </c>
       <c r="D371" s="3" t="s">
-        <v>1319</v>
+        <v>1340</v>
       </c>
       <c r="E371" s="3" t="s">
-        <v>19</v>
+        <v>123</v>
       </c>
       <c r="F371" s="3" t="s">
-        <v>1311</v>
-      </c>
-      <c r="G371" s="3"/>
+        <v>1341</v>
+      </c>
+      <c r="G371" s="3" t="s">
+        <v>748</v>
+      </c>
       <c r="H371" s="3">
-        <v>11</v>
-      </c>
-      <c r="I371" s="3"/>
+        <v>34</v>
+      </c>
+      <c r="I371" s="3">
+        <v>55</v>
+      </c>
       <c r="J371" s="3" t="s">
-        <v>471</v>
-      </c>
-      <c r="K371" s="3"/>
-      <c r="L371" s="3"/>
+        <v>21</v>
+      </c>
+      <c r="K371" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="L371" s="3" t="s">
+        <v>1342</v>
+      </c>
       <c r="M371" s="3"/>
     </row>
     <row r="372" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A372" s="3" t="s">
-        <v>1320</v>
+        <v>1343</v>
       </c>
       <c r="B372" s="3" t="s">
-        <v>1321</v>
+        <v>1115</v>
       </c>
       <c r="C372" s="3" t="s">
-        <v>1322</v>
+        <v>1116</v>
       </c>
       <c r="D372" s="3" t="s">
-        <v>1323</v>
+        <v>1344</v>
       </c>
       <c r="E372" s="3" t="s">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="F372" s="3" t="s">
-        <v>1324</v>
-      </c>
-      <c r="G372" s="3"/>
+        <v>1345</v>
+      </c>
+      <c r="G372" s="3" t="s">
+        <v>748</v>
+      </c>
       <c r="H372" s="3">
-        <v>47</v>
+        <v>18</v>
       </c>
       <c r="I372" s="3"/>
       <c r="J372" s="3" t="s">
-        <v>471</v>
-      </c>
-      <c r="K372" s="3"/>
-      <c r="L372" s="3"/>
-      <c r="M372" s="3"/>
+        <v>21</v>
+      </c>
+      <c r="K372" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="L372" s="3" t="s">
+        <v>1346</v>
+      </c>
+      <c r="M372" s="3" t="s">
+        <v>1347</v>
+      </c>
     </row>
     <row r="373" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A373" s="3" t="s">
-        <v>1325</v>
+        <v>1348</v>
       </c>
       <c r="B373" s="3" t="s">
-        <v>153</v>
+        <v>1273</v>
       </c>
       <c r="C373" s="3" t="s">
-        <v>154</v>
+        <v>1274</v>
       </c>
       <c r="D373" s="3" t="s">
-        <v>1326</v>
+        <v>1349</v>
       </c>
       <c r="E373" s="3" t="s">
-        <v>45</v>
+        <v>19</v>
       </c>
       <c r="F373" s="3" t="s">
-        <v>1315</v>
+        <v>108</v>
       </c>
       <c r="G373" s="3"/>
       <c r="H373" s="3">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="I373" s="3"/>
       <c r="J373" s="3" t="s">
@@ -17841,26 +18001,26 @@
     </row>
     <row r="374" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A374" s="3" t="s">
-        <v>1327</v>
+        <v>1350</v>
       </c>
       <c r="B374" s="3" t="s">
-        <v>86</v>
+        <v>805</v>
       </c>
       <c r="C374" s="3" t="s">
-        <v>356</v>
+        <v>806</v>
       </c>
       <c r="D374" s="3" t="s">
-        <v>1328</v>
+        <v>1351</v>
       </c>
       <c r="E374" s="3" t="s">
-        <v>19</v>
+        <v>100</v>
       </c>
       <c r="F374" s="3" t="s">
-        <v>1311</v>
+        <v>1352</v>
       </c>
       <c r="G374" s="3"/>
       <c r="H374" s="3">
-        <v>15</v>
+        <v>50</v>
       </c>
       <c r="I374" s="3"/>
       <c r="J374" s="3" t="s">
@@ -17872,26 +18032,26 @@
     </row>
     <row r="375" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A375" s="3" t="s">
-        <v>1329</v>
+        <v>1353</v>
       </c>
       <c r="B375" s="3" t="s">
-        <v>1330</v>
+        <v>1174</v>
       </c>
       <c r="C375" s="3" t="s">
-        <v>1331</v>
+        <v>1175</v>
       </c>
       <c r="D375" s="3" t="s">
-        <v>1332</v>
+        <v>1354</v>
       </c>
       <c r="E375" s="3" t="s">
         <v>19</v>
       </c>
       <c r="F375" s="3" t="s">
-        <v>53</v>
+        <v>1355</v>
       </c>
       <c r="G375" s="3"/>
       <c r="H375" s="3">
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="I375" s="3"/>
       <c r="J375" s="3" t="s">
@@ -17903,26 +18063,26 @@
     </row>
     <row r="376" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A376" s="3" t="s">
-        <v>1329</v>
+        <v>1356</v>
       </c>
       <c r="B376" s="3" t="s">
-        <v>209</v>
+        <v>1115</v>
       </c>
       <c r="C376" s="3" t="s">
-        <v>210</v>
+        <v>1116</v>
       </c>
       <c r="D376" s="3" t="s">
-        <v>1333</v>
+        <v>1357</v>
       </c>
       <c r="E376" s="3" t="s">
-        <v>45</v>
+        <v>19</v>
       </c>
       <c r="F376" s="3" t="s">
-        <v>1334</v>
+        <v>1358</v>
       </c>
       <c r="G376" s="3"/>
       <c r="H376" s="3">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="I376" s="3"/>
       <c r="J376" s="3" t="s">
@@ -17934,29 +18094,29 @@
     </row>
     <row r="377" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A377" s="3" t="s">
-        <v>1335</v>
+        <v>1359</v>
       </c>
       <c r="B377" s="3" t="s">
-        <v>890</v>
+        <v>1069</v>
       </c>
       <c r="C377" s="3" t="s">
-        <v>891</v>
+        <v>1070</v>
       </c>
       <c r="D377" s="3" t="s">
-        <v>1336</v>
+        <v>1360</v>
       </c>
       <c r="E377" s="3" t="s">
-        <v>123</v>
+        <v>19</v>
       </c>
       <c r="F377" s="3" t="s">
-        <v>1337</v>
+        <v>1361</v>
       </c>
       <c r="G377" s="3"/>
       <c r="H377" s="3">
-        <v>61</v>
+        <v>24</v>
       </c>
       <c r="I377" s="3">
-        <v>75</v>
+        <v>45</v>
       </c>
       <c r="J377" s="3" t="s">
         <v>471</v>
@@ -17967,26 +18127,26 @@
     </row>
     <row r="378" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A378" s="3" t="s">
-        <v>1338</v>
+        <v>1362</v>
       </c>
       <c r="B378" s="3" t="s">
-        <v>896</v>
+        <v>798</v>
       </c>
       <c r="C378" s="3" t="s">
-        <v>897</v>
+        <v>799</v>
       </c>
       <c r="D378" s="3" t="s">
-        <v>1339</v>
+        <v>1363</v>
       </c>
       <c r="E378" s="3" t="s">
-        <v>66</v>
+        <v>19</v>
       </c>
       <c r="F378" s="3" t="s">
-        <v>1340</v>
+        <v>1364</v>
       </c>
       <c r="G378" s="3"/>
       <c r="H378" s="3">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="I378" s="3"/>
       <c r="J378" s="3" t="s">
@@ -17998,28 +18158,30 @@
     </row>
     <row r="379" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A379" s="3" t="s">
-        <v>1341</v>
+        <v>1365</v>
       </c>
       <c r="B379" s="3" t="s">
-        <v>1058</v>
+        <v>1019</v>
       </c>
       <c r="C379" s="3" t="s">
-        <v>1059</v>
+        <v>1020</v>
       </c>
       <c r="D379" s="3" t="s">
-        <v>1342</v>
+        <v>1366</v>
       </c>
       <c r="E379" s="3" t="s">
-        <v>100</v>
+        <v>19</v>
       </c>
       <c r="F379" s="3" t="s">
-        <v>1343</v>
+        <v>1367</v>
       </c>
       <c r="G379" s="3"/>
       <c r="H379" s="3">
-        <v>39</v>
-      </c>
-      <c r="I379" s="3"/>
+        <v>31</v>
+      </c>
+      <c r="I379" s="3">
+        <v>40</v>
+      </c>
       <c r="J379" s="3" t="s">
         <v>471</v>
       </c>
@@ -18029,30 +18191,28 @@
     </row>
     <row r="380" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A380" s="3" t="s">
-        <v>1344</v>
+        <v>1365</v>
       </c>
       <c r="B380" s="3" t="s">
-        <v>890</v>
+        <v>896</v>
       </c>
       <c r="C380" s="3" t="s">
-        <v>891</v>
+        <v>897</v>
       </c>
       <c r="D380" s="3" t="s">
-        <v>1345</v>
+        <v>1368</v>
       </c>
       <c r="E380" s="3" t="s">
         <v>123</v>
       </c>
       <c r="F380" s="3" t="s">
-        <v>1346</v>
+        <v>1369</v>
       </c>
       <c r="G380" s="3"/>
       <c r="H380" s="3">
-        <v>60</v>
-      </c>
-      <c r="I380" s="3">
-        <v>65</v>
-      </c>
+        <v>58</v>
+      </c>
+      <c r="I380" s="3"/>
       <c r="J380" s="3" t="s">
         <v>471</v>
       </c>
@@ -18062,28 +18222,30 @@
     </row>
     <row r="381" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A381" s="3" t="s">
-        <v>1347</v>
+        <v>1370</v>
       </c>
       <c r="B381" s="3" t="s">
-        <v>86</v>
+        <v>1019</v>
       </c>
       <c r="C381" s="3" t="s">
-        <v>356</v>
+        <v>1020</v>
       </c>
       <c r="D381" s="3" t="s">
-        <v>1348</v>
+        <v>1371</v>
       </c>
       <c r="E381" s="3" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="F381" s="3" t="s">
-        <v>1315</v>
+        <v>1372</v>
       </c>
       <c r="G381" s="3"/>
       <c r="H381" s="3">
-        <v>8</v>
-      </c>
-      <c r="I381" s="3"/>
+        <v>13</v>
+      </c>
+      <c r="I381" s="3">
+        <v>40</v>
+      </c>
       <c r="J381" s="3" t="s">
         <v>471</v>
       </c>
@@ -18093,26 +18255,26 @@
     </row>
     <row r="382" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A382" s="3" t="s">
-        <v>1349</v>
+        <v>1373</v>
       </c>
       <c r="B382" s="3" t="s">
-        <v>440</v>
+        <v>835</v>
       </c>
       <c r="C382" s="3" t="s">
-        <v>381</v>
+        <v>836</v>
       </c>
       <c r="D382" s="3" t="s">
-        <v>1350</v>
+        <v>1374</v>
       </c>
       <c r="E382" s="3" t="s">
         <v>19</v>
       </c>
       <c r="F382" s="3" t="s">
-        <v>1315</v>
+        <v>1375</v>
       </c>
       <c r="G382" s="3"/>
       <c r="H382" s="3">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I382" s="3"/>
       <c r="J382" s="3" t="s">
@@ -18124,29 +18286,29 @@
     </row>
     <row r="383" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A383" s="3" t="s">
-        <v>1349</v>
+        <v>1376</v>
       </c>
       <c r="B383" s="3" t="s">
-        <v>1351</v>
+        <v>870</v>
       </c>
       <c r="C383" s="3" t="s">
-        <v>1352</v>
+        <v>871</v>
       </c>
       <c r="D383" s="3" t="s">
-        <v>1353</v>
+        <v>1377</v>
       </c>
       <c r="E383" s="3" t="s">
-        <v>32</v>
+        <v>746</v>
       </c>
       <c r="F383" s="3" t="s">
-        <v>1354</v>
+        <v>1378</v>
       </c>
       <c r="G383" s="3"/>
       <c r="H383" s="3">
-        <v>24</v>
+        <v>69</v>
       </c>
       <c r="I383" s="3">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="J383" s="3" t="s">
         <v>471</v>
@@ -18157,26 +18319,26 @@
     </row>
     <row r="384" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A384" s="3" t="s">
-        <v>1355</v>
+        <v>1379</v>
       </c>
       <c r="B384" s="3" t="s">
-        <v>896</v>
+        <v>835</v>
       </c>
       <c r="C384" s="3" t="s">
-        <v>897</v>
+        <v>836</v>
       </c>
       <c r="D384" s="3" t="s">
-        <v>1356</v>
+        <v>1380</v>
       </c>
       <c r="E384" s="3" t="s">
-        <v>66</v>
+        <v>19</v>
       </c>
       <c r="F384" s="3" t="s">
-        <v>204</v>
+        <v>1381</v>
       </c>
       <c r="G384" s="3"/>
       <c r="H384" s="3">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="I384" s="3"/>
       <c r="J384" s="3" t="s">
@@ -18188,26 +18350,26 @@
     </row>
     <row r="385" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A385" s="3" t="s">
-        <v>1357</v>
+        <v>1382</v>
       </c>
       <c r="B385" s="3" t="s">
-        <v>440</v>
+        <v>1383</v>
       </c>
       <c r="C385" s="3" t="s">
-        <v>381</v>
+        <v>1384</v>
       </c>
       <c r="D385" s="3" t="s">
-        <v>1358</v>
+        <v>1385</v>
       </c>
       <c r="E385" s="3" t="s">
         <v>19</v>
       </c>
       <c r="F385" s="3" t="s">
-        <v>1315</v>
+        <v>1386</v>
       </c>
       <c r="G385" s="3"/>
       <c r="H385" s="3">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="I385" s="3"/>
       <c r="J385" s="3" t="s">
@@ -18219,25 +18381,27 @@
     </row>
     <row r="386" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A386" s="3" t="s">
-        <v>1359</v>
+        <v>1387</v>
       </c>
       <c r="B386" s="3" t="s">
-        <v>1330</v>
+        <v>890</v>
       </c>
       <c r="C386" s="3" t="s">
-        <v>1331</v>
+        <v>891</v>
       </c>
       <c r="D386" s="3" t="s">
-        <v>1360</v>
+        <v>1388</v>
       </c>
       <c r="E386" s="3" t="s">
         <v>19</v>
       </c>
       <c r="F386" s="3" t="s">
-        <v>53</v>
+        <v>1389</v>
       </c>
       <c r="G386" s="3"/>
-      <c r="H386" s="3"/>
+      <c r="H386" s="3">
+        <v>18</v>
+      </c>
       <c r="I386" s="3"/>
       <c r="J386" s="3" t="s">
         <v>471</v>
@@ -18248,25 +18412,27 @@
     </row>
     <row r="387" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A387" s="3" t="s">
-        <v>1361</v>
+        <v>1390</v>
       </c>
       <c r="B387" s="3" t="s">
-        <v>896</v>
+        <v>890</v>
       </c>
       <c r="C387" s="3" t="s">
-        <v>897</v>
+        <v>891</v>
       </c>
       <c r="D387" s="3" t="s">
-        <v>1362</v>
+        <v>1391</v>
       </c>
       <c r="E387" s="3" t="s">
-        <v>123</v>
+        <v>19</v>
       </c>
       <c r="F387" s="3" t="s">
-        <v>1363</v>
+        <v>1392</v>
       </c>
       <c r="G387" s="3"/>
-      <c r="H387" s="3"/>
+      <c r="H387" s="3">
+        <v>24</v>
+      </c>
       <c r="I387" s="3"/>
       <c r="J387" s="3" t="s">
         <v>471</v>
@@ -18277,25 +18443,27 @@
     </row>
     <row r="388" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A388" s="3" t="s">
-        <v>1364</v>
+        <v>1390</v>
       </c>
       <c r="B388" s="3" t="s">
-        <v>1365</v>
+        <v>896</v>
       </c>
       <c r="C388" s="3" t="s">
-        <v>1366</v>
+        <v>897</v>
       </c>
       <c r="D388" s="3" t="s">
-        <v>1367</v>
+        <v>1393</v>
       </c>
       <c r="E388" s="3" t="s">
-        <v>100</v>
+        <v>66</v>
       </c>
       <c r="F388" s="3" t="s">
-        <v>1368</v>
+        <v>1394</v>
       </c>
       <c r="G388" s="3"/>
-      <c r="H388" s="3"/>
+      <c r="H388" s="3">
+        <v>34</v>
+      </c>
       <c r="I388" s="3"/>
       <c r="J388" s="3" t="s">
         <v>471</v>
@@ -18306,26 +18474,30 @@
     </row>
     <row r="389" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A389" s="3" t="s">
-        <v>1369</v>
+        <v>1395</v>
       </c>
       <c r="B389" s="3" t="s">
-        <v>239</v>
+        <v>781</v>
       </c>
       <c r="C389" s="3" t="s">
-        <v>240</v>
+        <v>782</v>
       </c>
       <c r="D389" s="3" t="s">
-        <v>1370</v>
+        <v>1396</v>
       </c>
       <c r="E389" s="3" t="s">
-        <v>26</v>
+        <v>123</v>
       </c>
       <c r="F389" s="3" t="s">
-        <v>1315</v>
+        <v>866</v>
       </c>
       <c r="G389" s="3"/>
-      <c r="H389" s="3"/>
-      <c r="I389" s="3"/>
+      <c r="H389" s="3">
+        <v>31</v>
+      </c>
+      <c r="I389" s="3">
+        <v>45</v>
+      </c>
       <c r="J389" s="3" t="s">
         <v>471</v>
       </c>
@@ -18335,25 +18507,27 @@
     </row>
     <row r="390" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A390" s="3" t="s">
-        <v>1371</v>
+        <v>1397</v>
       </c>
       <c r="B390" s="3" t="s">
-        <v>1019</v>
+        <v>209</v>
       </c>
       <c r="C390" s="3" t="s">
-        <v>1020</v>
+        <v>210</v>
       </c>
       <c r="D390" s="3" t="s">
-        <v>1372</v>
+        <v>1398</v>
       </c>
       <c r="E390" s="3" t="s">
-        <v>19</v>
+        <v>45</v>
       </c>
       <c r="F390" s="3" t="s">
-        <v>1373</v>
+        <v>212</v>
       </c>
       <c r="G390" s="3"/>
-      <c r="H390" s="3"/>
+      <c r="H390" s="3">
+        <v>5</v>
+      </c>
       <c r="I390" s="3"/>
       <c r="J390" s="3" t="s">
         <v>471</v>
@@ -18364,28 +18538,30 @@
     </row>
     <row r="391" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A391" s="3" t="s">
-        <v>1374</v>
+        <v>1399</v>
       </c>
       <c r="B391" s="3" t="s">
-        <v>896</v>
+        <v>180</v>
       </c>
       <c r="C391" s="3" t="s">
-        <v>897</v>
+        <v>1321</v>
       </c>
       <c r="D391" s="3" t="s">
-        <v>1375</v>
+        <v>1400</v>
       </c>
       <c r="E391" s="3" t="s">
-        <v>123</v>
+        <v>746</v>
       </c>
       <c r="F391" s="3" t="s">
-        <v>899</v>
+        <v>1401</v>
       </c>
       <c r="G391" s="3"/>
       <c r="H391" s="3">
-        <v>47</v>
-      </c>
-      <c r="I391" s="3"/>
+        <v>72</v>
+      </c>
+      <c r="I391" s="3">
+        <v>65</v>
+      </c>
       <c r="J391" s="3" t="s">
         <v>471</v>
       </c>
@@ -18395,30 +18571,28 @@
     </row>
     <row r="392" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A392" s="3" t="s">
-        <v>1376</v>
+        <v>1402</v>
       </c>
       <c r="B392" s="3" t="s">
-        <v>781</v>
+        <v>811</v>
       </c>
       <c r="C392" s="3" t="s">
-        <v>782</v>
+        <v>812</v>
       </c>
       <c r="D392" s="3" t="s">
-        <v>1377</v>
+        <v>1403</v>
       </c>
       <c r="E392" s="3" t="s">
-        <v>123</v>
+        <v>19</v>
       </c>
       <c r="F392" s="3" t="s">
-        <v>1378</v>
+        <v>1404</v>
       </c>
       <c r="G392" s="3"/>
       <c r="H392" s="3">
-        <v>74</v>
-      </c>
-      <c r="I392" s="3">
-        <v>75</v>
-      </c>
+        <v>21</v>
+      </c>
+      <c r="I392" s="3"/>
       <c r="J392" s="3" t="s">
         <v>471</v>
       </c>
@@ -18428,30 +18602,28 @@
     </row>
     <row r="393" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A393" s="3" t="s">
-        <v>1379</v>
+        <v>1405</v>
       </c>
       <c r="B393" s="3" t="s">
-        <v>1260</v>
+        <v>811</v>
       </c>
       <c r="C393" s="3" t="s">
-        <v>1261</v>
+        <v>812</v>
       </c>
       <c r="D393" s="3" t="s">
-        <v>1380</v>
+        <v>1406</v>
       </c>
       <c r="E393" s="3" t="s">
-        <v>123</v>
+        <v>19</v>
       </c>
       <c r="F393" s="3" t="s">
-        <v>1381</v>
+        <v>1404</v>
       </c>
       <c r="G393" s="3"/>
       <c r="H393" s="3">
-        <v>31</v>
-      </c>
-      <c r="I393" s="3">
-        <v>75</v>
-      </c>
+        <v>16</v>
+      </c>
+      <c r="I393" s="3"/>
       <c r="J393" s="3" t="s">
         <v>471</v>
       </c>
@@ -18461,28 +18633,30 @@
     </row>
     <row r="394" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A394" s="3" t="s">
-        <v>1382</v>
+        <v>1407</v>
       </c>
       <c r="B394" s="3" t="s">
-        <v>137</v>
+        <v>1019</v>
       </c>
       <c r="C394" s="3" t="s">
-        <v>138</v>
+        <v>1020</v>
       </c>
       <c r="D394" s="3" t="s">
-        <v>1383</v>
+        <v>1408</v>
       </c>
       <c r="E394" s="3" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="F394" s="3" t="s">
-        <v>1384</v>
+        <v>1409</v>
       </c>
       <c r="G394" s="3"/>
       <c r="H394" s="3">
-        <v>23</v>
-      </c>
-      <c r="I394" s="3"/>
+        <v>35</v>
+      </c>
+      <c r="I394" s="3">
+        <v>40</v>
+      </c>
       <c r="J394" s="3" t="s">
         <v>471</v>
       </c>
@@ -18492,28 +18666,30 @@
     </row>
     <row r="395" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A395" s="3" t="s">
-        <v>1385</v>
+        <v>1410</v>
       </c>
       <c r="B395" s="3" t="s">
-        <v>1019</v>
+        <v>751</v>
       </c>
       <c r="C395" s="3" t="s">
-        <v>1020</v>
+        <v>752</v>
       </c>
       <c r="D395" s="3" t="s">
-        <v>1386</v>
+        <v>1411</v>
       </c>
       <c r="E395" s="3" t="s">
         <v>100</v>
       </c>
       <c r="F395" s="3" t="s">
-        <v>323</v>
+        <v>1412</v>
       </c>
       <c r="G395" s="3"/>
       <c r="H395" s="3">
-        <v>47</v>
-      </c>
-      <c r="I395" s="3"/>
+        <v>69</v>
+      </c>
+      <c r="I395" s="3">
+        <v>65</v>
+      </c>
       <c r="J395" s="3" t="s">
         <v>471</v>
       </c>
@@ -18523,26 +18699,26 @@
     </row>
     <row r="396" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A396" s="3" t="s">
-        <v>1387</v>
+        <v>1413</v>
       </c>
       <c r="B396" s="3" t="s">
-        <v>1058</v>
+        <v>791</v>
       </c>
       <c r="C396" s="3" t="s">
-        <v>1059</v>
+        <v>792</v>
       </c>
       <c r="D396" s="3" t="s">
-        <v>1388</v>
+        <v>1414</v>
       </c>
       <c r="E396" s="3" t="s">
-        <v>19</v>
+        <v>45</v>
       </c>
       <c r="F396" s="3" t="s">
-        <v>1389</v>
+        <v>1415</v>
       </c>
       <c r="G396" s="3"/>
       <c r="H396" s="3">
-        <v>21</v>
+        <v>36</v>
       </c>
       <c r="I396" s="3"/>
       <c r="J396" s="3" t="s">
@@ -18554,26 +18730,26 @@
     </row>
     <row r="397" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A397" s="3" t="s">
-        <v>1390</v>
+        <v>1416</v>
       </c>
       <c r="B397" s="3" t="s">
-        <v>1163</v>
+        <v>1115</v>
       </c>
       <c r="C397" s="3" t="s">
-        <v>1164</v>
+        <v>1116</v>
       </c>
       <c r="D397" s="3" t="s">
-        <v>1391</v>
+        <v>1417</v>
       </c>
       <c r="E397" s="3" t="s">
-        <v>45</v>
+        <v>19</v>
       </c>
       <c r="F397" s="3" t="s">
-        <v>1392</v>
+        <v>1345</v>
       </c>
       <c r="G397" s="3"/>
       <c r="H397" s="3">
-        <v>42</v>
+        <v>18</v>
       </c>
       <c r="I397" s="3"/>
       <c r="J397" s="3" t="s">
@@ -18585,28 +18761,30 @@
     </row>
     <row r="398" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A398" s="3" t="s">
-        <v>1393</v>
+        <v>1418</v>
       </c>
       <c r="B398" s="3" t="s">
-        <v>798</v>
+        <v>1069</v>
       </c>
       <c r="C398" s="3" t="s">
-        <v>799</v>
+        <v>1070</v>
       </c>
       <c r="D398" s="3" t="s">
-        <v>1394</v>
+        <v>1419</v>
       </c>
       <c r="E398" s="3" t="s">
         <v>19</v>
       </c>
       <c r="F398" s="3" t="s">
-        <v>1395</v>
+        <v>1420</v>
       </c>
       <c r="G398" s="3"/>
       <c r="H398" s="3">
-        <v>20</v>
-      </c>
-      <c r="I398" s="3"/>
+        <v>29</v>
+      </c>
+      <c r="I398" s="3">
+        <v>45</v>
+      </c>
       <c r="J398" s="3" t="s">
         <v>471</v>
       </c>
@@ -18616,30 +18794,28 @@
     </row>
     <row r="399" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A399" s="3" t="s">
-        <v>1396</v>
+        <v>1421</v>
       </c>
       <c r="B399" s="3" t="s">
-        <v>1397</v>
+        <v>1422</v>
       </c>
       <c r="C399" s="3" t="s">
-        <v>1398</v>
+        <v>1423</v>
       </c>
       <c r="D399" s="3" t="s">
-        <v>1399</v>
+        <v>1424</v>
       </c>
       <c r="E399" s="3" t="s">
-        <v>100</v>
+        <v>26</v>
       </c>
       <c r="F399" s="3" t="s">
-        <v>1400</v>
+        <v>1425</v>
       </c>
       <c r="G399" s="3"/>
       <c r="H399" s="3">
-        <v>52</v>
-      </c>
-      <c r="I399" s="3">
-        <v>55</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="I399" s="3"/>
       <c r="J399" s="3" t="s">
         <v>471</v>
       </c>
@@ -18649,30 +18825,28 @@
     </row>
     <row r="400" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A400" s="3" t="s">
-        <v>1401</v>
+        <v>1426</v>
       </c>
       <c r="B400" s="3" t="s">
-        <v>1058</v>
+        <v>791</v>
       </c>
       <c r="C400" s="3" t="s">
-        <v>1059</v>
+        <v>792</v>
       </c>
       <c r="D400" s="3" t="s">
-        <v>1402</v>
+        <v>1427</v>
       </c>
       <c r="E400" s="3" t="s">
-        <v>123</v>
+        <v>19</v>
       </c>
       <c r="F400" s="3" t="s">
-        <v>1403</v>
+        <v>1428</v>
       </c>
       <c r="G400" s="3"/>
       <c r="H400" s="3">
-        <v>65</v>
-      </c>
-      <c r="I400" s="3">
-        <v>65</v>
-      </c>
+        <v>22</v>
+      </c>
+      <c r="I400" s="3"/>
       <c r="J400" s="3" t="s">
         <v>471</v>
       </c>
@@ -18682,28 +18856,30 @@
     </row>
     <row r="401" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A401" s="3" t="s">
-        <v>1404</v>
+        <v>1429</v>
       </c>
       <c r="B401" s="3" t="s">
-        <v>890</v>
+        <v>870</v>
       </c>
       <c r="C401" s="3" t="s">
-        <v>891</v>
+        <v>871</v>
       </c>
       <c r="D401" s="3" t="s">
-        <v>1405</v>
+        <v>1430</v>
       </c>
       <c r="E401" s="3" t="s">
-        <v>19</v>
+        <v>746</v>
       </c>
       <c r="F401" s="3" t="s">
-        <v>1406</v>
+        <v>1431</v>
       </c>
       <c r="G401" s="3"/>
       <c r="H401" s="3">
-        <v>8</v>
-      </c>
-      <c r="I401" s="3"/>
+        <v>81</v>
+      </c>
+      <c r="I401" s="3">
+        <v>75</v>
+      </c>
       <c r="J401" s="3" t="s">
         <v>471</v>
       </c>
@@ -18713,26 +18889,26 @@
     </row>
     <row r="402" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A402" s="3" t="s">
-        <v>1407</v>
+        <v>1432</v>
       </c>
       <c r="B402" s="3" t="s">
-        <v>890</v>
+        <v>775</v>
       </c>
       <c r="C402" s="3" t="s">
-        <v>891</v>
+        <v>776</v>
       </c>
       <c r="D402" s="3" t="s">
-        <v>1408</v>
+        <v>1433</v>
       </c>
       <c r="E402" s="3" t="s">
         <v>19</v>
       </c>
       <c r="F402" s="3" t="s">
-        <v>1273</v>
+        <v>557</v>
       </c>
       <c r="G402" s="3"/>
       <c r="H402" s="3">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="I402" s="3"/>
       <c r="J402" s="3" t="s">
@@ -18744,26 +18920,26 @@
     </row>
     <row r="403" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A403" s="3" t="s">
-        <v>1409</v>
+        <v>1432</v>
       </c>
       <c r="B403" s="3" t="s">
-        <v>1330</v>
+        <v>775</v>
       </c>
       <c r="C403" s="3" t="s">
-        <v>1331</v>
+        <v>776</v>
       </c>
       <c r="D403" s="3" t="s">
-        <v>1410</v>
+        <v>1434</v>
       </c>
       <c r="E403" s="3" t="s">
         <v>19</v>
       </c>
       <c r="F403" s="3" t="s">
-        <v>1411</v>
+        <v>1435</v>
       </c>
       <c r="G403" s="3"/>
       <c r="H403" s="3">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="I403" s="3"/>
       <c r="J403" s="3" t="s">
@@ -18775,26 +18951,26 @@
     </row>
     <row r="404" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A404" s="3" t="s">
-        <v>1412</v>
+        <v>1436</v>
       </c>
       <c r="B404" s="3" t="s">
-        <v>1397</v>
+        <v>775</v>
       </c>
       <c r="C404" s="3" t="s">
-        <v>1398</v>
+        <v>776</v>
       </c>
       <c r="D404" s="3" t="s">
-        <v>1413</v>
+        <v>1437</v>
       </c>
       <c r="E404" s="3" t="s">
         <v>19</v>
       </c>
       <c r="F404" s="3" t="s">
-        <v>1414</v>
+        <v>1438</v>
       </c>
       <c r="G404" s="3"/>
       <c r="H404" s="3">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="I404" s="3"/>
       <c r="J404" s="3" t="s">
@@ -18806,28 +18982,30 @@
     </row>
     <row r="405" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A405" s="3" t="s">
-        <v>1415</v>
+        <v>1439</v>
       </c>
       <c r="B405" s="3" t="s">
-        <v>906</v>
+        <v>775</v>
       </c>
       <c r="C405" s="3" t="s">
-        <v>907</v>
+        <v>776</v>
       </c>
       <c r="D405" s="3" t="s">
-        <v>1416</v>
+        <v>1440</v>
       </c>
       <c r="E405" s="3" t="s">
-        <v>45</v>
+        <v>123</v>
       </c>
       <c r="F405" s="3" t="s">
-        <v>1417</v>
+        <v>1441</v>
       </c>
       <c r="G405" s="3"/>
       <c r="H405" s="3">
-        <v>22</v>
-      </c>
-      <c r="I405" s="3"/>
+        <v>62</v>
+      </c>
+      <c r="I405" s="3">
+        <v>65</v>
+      </c>
       <c r="J405" s="3" t="s">
         <v>471</v>
       </c>
@@ -18837,26 +19015,26 @@
     </row>
     <row r="406" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A406" s="3" t="s">
-        <v>1418</v>
+        <v>1442</v>
       </c>
       <c r="B406" s="3" t="s">
-        <v>1163</v>
+        <v>1115</v>
       </c>
       <c r="C406" s="3" t="s">
-        <v>1164</v>
+        <v>1116</v>
       </c>
       <c r="D406" s="3" t="s">
-        <v>1419</v>
+        <v>1443</v>
       </c>
       <c r="E406" s="3" t="s">
-        <v>45</v>
+        <v>19</v>
       </c>
       <c r="F406" s="3" t="s">
-        <v>1420</v>
+        <v>1444</v>
       </c>
       <c r="G406" s="3"/>
       <c r="H406" s="3">
-        <v>57</v>
+        <v>18</v>
       </c>
       <c r="I406" s="3"/>
       <c r="J406" s="3" t="s">
@@ -18868,26 +19046,26 @@
     </row>
     <row r="407" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A407" s="3" t="s">
-        <v>1421</v>
+        <v>1445</v>
       </c>
       <c r="B407" s="3" t="s">
-        <v>781</v>
+        <v>835</v>
       </c>
       <c r="C407" s="3" t="s">
-        <v>782</v>
+        <v>836</v>
       </c>
       <c r="D407" s="3" t="s">
-        <v>1422</v>
+        <v>1446</v>
       </c>
       <c r="E407" s="3" t="s">
-        <v>100</v>
+        <v>19</v>
       </c>
       <c r="F407" s="3" t="s">
-        <v>1423</v>
+        <v>1447</v>
       </c>
       <c r="G407" s="3"/>
       <c r="H407" s="3">
-        <v>45</v>
+        <v>16</v>
       </c>
       <c r="I407" s="3"/>
       <c r="J407" s="3" t="s">
@@ -18899,193 +19077,34 @@
     </row>
     <row r="408" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A408" s="3" t="s">
-        <v>1424</v>
+        <v>1448</v>
       </c>
       <c r="B408" s="3" t="s">
-        <v>775</v>
+        <v>1449</v>
       </c>
       <c r="C408" s="3" t="s">
-        <v>776</v>
+        <v>1450</v>
       </c>
       <c r="D408" s="3" t="s">
-        <v>1425</v>
+        <v>1451</v>
       </c>
       <c r="E408" s="3" t="s">
         <v>19</v>
       </c>
       <c r="F408" s="3" t="s">
-        <v>1426</v>
+        <v>1452</v>
       </c>
       <c r="G408" s="3"/>
       <c r="H408" s="3">
-        <v>27</v>
-      </c>
-      <c r="I408" s="3">
-        <v>35</v>
-      </c>
+        <v>23</v>
+      </c>
+      <c r="I408" s="3"/>
       <c r="J408" s="3" t="s">
         <v>471</v>
       </c>
       <c r="K408" s="3"/>
       <c r="L408" s="3"/>
       <c r="M408" s="3"/>
-    </row>
-    <row r="409" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A409" s="3" t="s">
-        <v>1427</v>
-      </c>
-      <c r="B409" s="3" t="s">
-        <v>811</v>
-      </c>
-      <c r="C409" s="3" t="s">
-        <v>812</v>
-      </c>
-      <c r="D409" s="3" t="s">
-        <v>1428</v>
-      </c>
-      <c r="E409" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="F409" s="3" t="s">
-        <v>1279</v>
-      </c>
-      <c r="G409" s="3"/>
-      <c r="H409" s="3">
-        <v>22</v>
-      </c>
-      <c r="I409" s="3"/>
-      <c r="J409" s="3" t="s">
-        <v>471</v>
-      </c>
-      <c r="K409" s="3"/>
-      <c r="L409" s="3"/>
-      <c r="M409" s="3"/>
-    </row>
-    <row r="410" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A410" s="3" t="s">
-        <v>1429</v>
-      </c>
-      <c r="B410" s="3" t="s">
-        <v>1397</v>
-      </c>
-      <c r="C410" s="3" t="s">
-        <v>1398</v>
-      </c>
-      <c r="D410" s="3" t="s">
-        <v>1430</v>
-      </c>
-      <c r="E410" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="F410" s="3" t="s">
-        <v>1414</v>
-      </c>
-      <c r="G410" s="3"/>
-      <c r="H410" s="3">
-        <v>5</v>
-      </c>
-      <c r="I410" s="3"/>
-      <c r="J410" s="3" t="s">
-        <v>471</v>
-      </c>
-      <c r="K410" s="3"/>
-      <c r="L410" s="3"/>
-      <c r="M410" s="3"/>
-    </row>
-    <row r="411" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A411" s="3" t="s">
-        <v>1431</v>
-      </c>
-      <c r="B411" s="3" t="s">
-        <v>1163</v>
-      </c>
-      <c r="C411" s="3" t="s">
-        <v>1164</v>
-      </c>
-      <c r="D411" s="3" t="s">
-        <v>1432</v>
-      </c>
-      <c r="E411" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="F411" s="3" t="s">
-        <v>1420</v>
-      </c>
-      <c r="G411" s="3"/>
-      <c r="H411" s="3">
-        <v>63</v>
-      </c>
-      <c r="I411" s="3"/>
-      <c r="J411" s="3" t="s">
-        <v>471</v>
-      </c>
-      <c r="K411" s="3"/>
-      <c r="L411" s="3"/>
-      <c r="M411" s="3"/>
-    </row>
-    <row r="412" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A412" s="3" t="s">
-        <v>1433</v>
-      </c>
-      <c r="B412" s="3" t="s">
-        <v>1115</v>
-      </c>
-      <c r="C412" s="3" t="s">
-        <v>1116</v>
-      </c>
-      <c r="D412" s="3" t="s">
-        <v>1434</v>
-      </c>
-      <c r="E412" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="F412" s="3" t="s">
-        <v>1435</v>
-      </c>
-      <c r="G412" s="3"/>
-      <c r="H412" s="3">
-        <v>14</v>
-      </c>
-      <c r="I412" s="3">
-        <v>45</v>
-      </c>
-      <c r="J412" s="3" t="s">
-        <v>471</v>
-      </c>
-      <c r="K412" s="3"/>
-      <c r="L412" s="3"/>
-      <c r="M412" s="3"/>
-    </row>
-    <row r="413" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A413" s="3" t="s">
-        <v>1436</v>
-      </c>
-      <c r="B413" s="3" t="s">
-        <v>1115</v>
-      </c>
-      <c r="C413" s="3" t="s">
-        <v>1116</v>
-      </c>
-      <c r="D413" s="3" t="s">
-        <v>1437</v>
-      </c>
-      <c r="E413" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="F413" s="3" t="s">
-        <v>1438</v>
-      </c>
-      <c r="G413" s="3"/>
-      <c r="H413" s="3">
-        <v>19</v>
-      </c>
-      <c r="I413" s="3"/>
-      <c r="J413" s="3" t="s">
-        <v>471</v>
-      </c>
-      <c r="K413" s="3"/>
-      <c r="L413" s="3"/>
-      <c r="M413" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/camera_events.xlsx
+++ b/camera_events.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\Synergy Safety Group\DEN\Dashboard\DEN Camera System\Fiore and Sons\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{4E7B70DD-3959-4495-9D32-9138EA3A4DB1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{CBF1F161-ECB8-403C-A751-370482E68761}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5820" yWindow="1515" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="57840" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DRIVE-ALERTS" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3672" uniqueCount="1453">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3474" uniqueCount="1370">
   <si>
     <t>DRIVE ALERTS</t>
   </si>
@@ -4066,247 +4066,16 @@
     <t>03/20/26 12:01 EDT</t>
   </si>
   <si>
-    <t>03/20/26 07:10 EDT</t>
-  </si>
-  <si>
-    <t>281474988538017-1774005052987</t>
-  </si>
-  <si>
-    <t>03/20/26 07:54 EDT</t>
-  </si>
-  <si>
-    <t>281474988469578-1774007652169</t>
-  </si>
-  <si>
-    <t>0.6mi W of Todd Creek CO</t>
-  </si>
-  <si>
-    <t>03/20/26 07:58 EDT</t>
-  </si>
-  <si>
-    <t>281474988535988-1774007880017</t>
-  </si>
-  <si>
-    <t>0.7mi N of Frederick CO</t>
-  </si>
-  <si>
-    <t>03/20/26 08:26 EDT</t>
-  </si>
-  <si>
-    <t>281474988055427-1774009578183</t>
-  </si>
-  <si>
-    <t>0.7mi W of Firestone CO</t>
-  </si>
-  <si>
-    <t>03/20/26 08:32 EDT</t>
-  </si>
-  <si>
-    <t>281474994873792-1774009940963</t>
-  </si>
-  <si>
-    <t>3.5mi NW of Firestone CO</t>
-  </si>
-  <si>
-    <t>03/20/26 08:33 EDT</t>
-  </si>
-  <si>
-    <t>281474988330103-1774009991973</t>
-  </si>
-  <si>
-    <t>2.5mi W of Dakota Ridge CO</t>
-  </si>
-  <si>
     <t>03/20/26 08:39 EDT</t>
   </si>
   <si>
-    <t>281474995127998-1774010353015</t>
-  </si>
-  <si>
-    <t>8.8mi E of The Pinery CO</t>
-  </si>
-  <si>
     <t>281474988147905-1774010375425</t>
   </si>
   <si>
     <t>2.6mi E of Denver CO</t>
   </si>
   <si>
-    <t>03/20/26 08:44 EDT</t>
-  </si>
-  <si>
-    <t>281474995127998-1774010640965</t>
-  </si>
-  <si>
-    <t>9.1mi E of Parker CO</t>
-  </si>
-  <si>
-    <t>03/20/26 08:56 EDT</t>
-  </si>
-  <si>
-    <t>281474985934443-1774011415974</t>
-  </si>
-  <si>
-    <t>4.4mi NW of Four Square Mile CO</t>
-  </si>
-  <si>
-    <t>03/20/26 09:24 EDT</t>
-  </si>
-  <si>
-    <t>281474988414844-1774013049524</t>
-  </si>
-  <si>
-    <t>2.4mi W of Four Square Mile CO</t>
-  </si>
-  <si>
-    <t>03/20/26 11:44 EDT</t>
-  </si>
-  <si>
-    <t>281474985934443-1774021461981</t>
-  </si>
-  <si>
-    <t>4.5mi NW of Four Square Mile CO</t>
-  </si>
-  <si>
-    <t>03/20/26 11:45 EDT</t>
-  </si>
-  <si>
-    <t>Pedro Esparza</t>
-  </si>
-  <si>
-    <t>PU4330PedroEsparza</t>
-  </si>
-  <si>
-    <t>281474994772182-1774021516974</t>
-  </si>
-  <si>
-    <t>3.2mi W of Sheridan CO</t>
-  </si>
-  <si>
-    <t>03/20/26 12:10 EDT</t>
-  </si>
-  <si>
-    <t>281474998210375-1774023025978</t>
-  </si>
-  <si>
-    <t>1.3mi W of Parker CO</t>
-  </si>
-  <si>
-    <t>03/20/26 12:23 EDT</t>
-  </si>
-  <si>
-    <t>281474998210375-1774023802962</t>
-  </si>
-  <si>
-    <t>1.2mi W of Parker CO</t>
-  </si>
-  <si>
-    <t>281474988147905-1774023829800</t>
-  </si>
-  <si>
-    <t>4.2mi NW of Aurora CO</t>
-  </si>
-  <si>
-    <t>03/20/26 12:40 EDT</t>
-  </si>
-  <si>
-    <t>281474989384378-1774024811419</t>
-  </si>
-  <si>
-    <t>03/20/26 14:05 EDT</t>
-  </si>
-  <si>
-    <t>281474982930732-1774029943642</t>
-  </si>
-  <si>
-    <t>03/20/26 16:25 EDT</t>
-  </si>
-  <si>
-    <t>281474982930719-1774038336540</t>
-  </si>
-  <si>
-    <t>1.6mi SE of Columbine CO</t>
-  </si>
-  <si>
-    <t>03/20/26 16:54 EDT</t>
-  </si>
-  <si>
-    <t>281474988302231-1774040096962</t>
-  </si>
-  <si>
-    <t>2.8mi NW of Commerce City CO</t>
-  </si>
-  <si>
-    <t>03/20/26 16:55 EDT</t>
-  </si>
-  <si>
-    <t>281474988302231-1774040110964</t>
-  </si>
-  <si>
-    <t>03/20/26 17:09 EDT</t>
-  </si>
-  <si>
-    <t>281474995127998-1774040997967</t>
-  </si>
-  <si>
-    <t>10.6mi E of The Pinery CO</t>
-  </si>
-  <si>
-    <t>03/20/26 17:14 EDT</t>
-  </si>
-  <si>
-    <t>281474989363431-1774041269893</t>
-  </si>
-  <si>
-    <t>2.8mi W of Louisville CO</t>
-  </si>
-  <si>
-    <t>03/20/26 17:17 EDT</t>
-  </si>
-  <si>
-    <t>281474989365899-1774041425722</t>
-  </si>
-  <si>
-    <t>2.8mi NW of Four Square Mile CO</t>
-  </si>
-  <si>
-    <t>03/20/26 17:32 EDT</t>
-  </si>
-  <si>
-    <t>281474988055427-1774042377981</t>
-  </si>
-  <si>
-    <t>03/20/26 17:45 EDT</t>
-  </si>
-  <si>
-    <t>281474994873792-1774043157966</t>
-  </si>
-  <si>
-    <t>3.4mi NW of Firestone CO</t>
-  </si>
-  <si>
-    <t>03/20/26 18:11 EDT</t>
-  </si>
-  <si>
-    <t>Arturo Amaya</t>
-  </si>
-  <si>
-    <t>PU7134ArturoAmaya</t>
-  </si>
-  <si>
-    <t>281474988848879-1774044713499</t>
-  </si>
-  <si>
-    <t>2.9mi E of Edgewater CO</t>
-  </si>
-  <si>
-    <t>03/20/26 18:16 EDT</t>
-  </si>
-  <si>
-    <t>281474989365899-1774044993976</t>
-  </si>
-  <si>
-    <t>4.1mi E of Edgewater CO</t>
+    <t>03/23/26 09:50 EDT</t>
   </si>
   <si>
     <t>03/20/26 18:57 EDT</t>
@@ -4318,25 +4087,7 @@
     <t>1.4mi S of Aurora CO</t>
   </si>
   <si>
-    <t>03/21/26 09:41 EDT</t>
-  </si>
-  <si>
-    <t>281474988148287-1774100474024</t>
-  </si>
-  <si>
-    <t>281474988148287-1774100514024</t>
-  </si>
-  <si>
-    <t>2.5mi SE of Edgewater CO</t>
-  </si>
-  <si>
-    <t>03/21/26 13:12 EDT</t>
-  </si>
-  <si>
-    <t>281474988148287-1774113130980</t>
-  </si>
-  <si>
-    <t>4.8mi NW of Aurora CO</t>
+    <t>03/23/26 09:37 EDT</t>
   </si>
   <si>
     <t>03/21/26 13:50 EDT</t>
@@ -4348,37 +4099,37 @@
     <t>1.9mi NE of Cherry Hills Village CO</t>
   </si>
   <si>
-    <t>03/21/26 13:55 EDT</t>
-  </si>
-  <si>
-    <t>281474988055427-1774115702975</t>
-  </si>
-  <si>
-    <t>2mi NW of Four Square Mile CO</t>
-  </si>
-  <si>
-    <t>03/21/26 14:01 EDT</t>
-  </si>
-  <si>
-    <t>281474985934443-1774116077975</t>
-  </si>
-  <si>
-    <t>4.8mi N of Aurora CO</t>
-  </si>
-  <si>
-    <t>03/21/26 16:16 EDT</t>
-  </si>
-  <si>
-    <t>Luis Hernandez</t>
-  </si>
-  <si>
-    <t>PU7791LuisHernandez</t>
-  </si>
-  <si>
-    <t>281474988794180-1774124216971</t>
-  </si>
-  <si>
-    <t>4.7mi N of Aurora CO</t>
+    <t>03/23/26 09:53 EDT</t>
+  </si>
+  <si>
+    <t>03/21/26 20:02 EDT</t>
+  </si>
+  <si>
+    <t>281474988596947-1774137731480</t>
+  </si>
+  <si>
+    <t>7.3mi E of Evans CO</t>
+  </si>
+  <si>
+    <t>03/23/26 09:55 EDT</t>
+  </si>
+  <si>
+    <t>03/23/26 09:46 EDT</t>
+  </si>
+  <si>
+    <t>281474982930704-1774273608370</t>
+  </si>
+  <si>
+    <t>8.4mi NW of Evergreen CO</t>
+  </si>
+  <si>
+    <t>03/23/26 09:49 EDT</t>
+  </si>
+  <si>
+    <t>281474982930703-1774273757676</t>
+  </si>
+  <si>
+    <t>9.3mi NW of Evergreen CO</t>
   </si>
 </sst>
 </file>
@@ -4396,6 +4147,7 @@
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -4740,10 +4492,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M408"/>
+  <dimension ref="A1:M378"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="13" width="15" customWidth="1"/>
+    <col min="1" max="1" width="42.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="13" width="15" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -17973,151 +17726,177 @@
         <v>1348</v>
       </c>
       <c r="B373" s="3" t="s">
-        <v>1273</v>
+        <v>896</v>
       </c>
       <c r="C373" s="3" t="s">
-        <v>1274</v>
+        <v>897</v>
       </c>
       <c r="D373" s="3" t="s">
         <v>1349</v>
       </c>
       <c r="E373" s="3" t="s">
-        <v>19</v>
+        <v>123</v>
       </c>
       <c r="F373" s="3" t="s">
-        <v>108</v>
-      </c>
-      <c r="G373" s="3"/>
+        <v>1350</v>
+      </c>
+      <c r="G373" s="3" t="s">
+        <v>748</v>
+      </c>
       <c r="H373" s="3">
-        <v>14</v>
+        <v>58</v>
       </c>
       <c r="I373" s="3"/>
       <c r="J373" s="3" t="s">
-        <v>471</v>
-      </c>
-      <c r="K373" s="3"/>
-      <c r="L373" s="3"/>
+        <v>21</v>
+      </c>
+      <c r="K373" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="L373" s="3" t="s">
+        <v>1351</v>
+      </c>
       <c r="M373" s="3"/>
     </row>
     <row r="374" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A374" s="3" t="s">
-        <v>1350</v>
+        <v>1352</v>
       </c>
       <c r="B374" s="3" t="s">
-        <v>805</v>
+        <v>870</v>
       </c>
       <c r="C374" s="3" t="s">
-        <v>806</v>
+        <v>871</v>
       </c>
       <c r="D374" s="3" t="s">
-        <v>1351</v>
+        <v>1353</v>
       </c>
       <c r="E374" s="3" t="s">
-        <v>100</v>
+        <v>746</v>
       </c>
       <c r="F374" s="3" t="s">
-        <v>1352</v>
-      </c>
-      <c r="G374" s="3"/>
+        <v>1354</v>
+      </c>
+      <c r="G374" s="3" t="s">
+        <v>748</v>
+      </c>
       <c r="H374" s="3">
-        <v>50</v>
-      </c>
-      <c r="I374" s="3"/>
+        <v>81</v>
+      </c>
+      <c r="I374" s="3">
+        <v>75</v>
+      </c>
       <c r="J374" s="3" t="s">
-        <v>471</v>
-      </c>
-      <c r="K374" s="3"/>
-      <c r="L374" s="3"/>
+        <v>21</v>
+      </c>
+      <c r="K374" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="L374" s="3" t="s">
+        <v>1355</v>
+      </c>
       <c r="M374" s="3"/>
     </row>
     <row r="375" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A375" s="3" t="s">
-        <v>1353</v>
+        <v>1356</v>
       </c>
       <c r="B375" s="3" t="s">
-        <v>1174</v>
+        <v>775</v>
       </c>
       <c r="C375" s="3" t="s">
-        <v>1175</v>
+        <v>776</v>
       </c>
       <c r="D375" s="3" t="s">
-        <v>1354</v>
+        <v>1357</v>
       </c>
       <c r="E375" s="3" t="s">
-        <v>19</v>
+        <v>123</v>
       </c>
       <c r="F375" s="3" t="s">
-        <v>1355</v>
-      </c>
-      <c r="G375" s="3"/>
+        <v>1358</v>
+      </c>
+      <c r="G375" s="3" t="s">
+        <v>748</v>
+      </c>
       <c r="H375" s="3">
-        <v>14</v>
-      </c>
-      <c r="I375" s="3"/>
+        <v>62</v>
+      </c>
+      <c r="I375" s="3">
+        <v>65</v>
+      </c>
       <c r="J375" s="3" t="s">
-        <v>471</v>
-      </c>
-      <c r="K375" s="3"/>
-      <c r="L375" s="3"/>
+        <v>21</v>
+      </c>
+      <c r="K375" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="L375" s="3" t="s">
+        <v>1359</v>
+      </c>
       <c r="M375" s="3"/>
     </row>
     <row r="376" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A376" s="3" t="s">
-        <v>1356</v>
+        <v>1360</v>
       </c>
       <c r="B376" s="3" t="s">
-        <v>1115</v>
+        <v>1058</v>
       </c>
       <c r="C376" s="3" t="s">
-        <v>1116</v>
+        <v>1059</v>
       </c>
       <c r="D376" s="3" t="s">
-        <v>1357</v>
+        <v>1361</v>
       </c>
       <c r="E376" s="3" t="s">
-        <v>19</v>
+        <v>123</v>
       </c>
       <c r="F376" s="3" t="s">
-        <v>1358</v>
-      </c>
-      <c r="G376" s="3"/>
+        <v>1362</v>
+      </c>
+      <c r="G376" s="3" t="s">
+        <v>748</v>
+      </c>
       <c r="H376" s="3">
-        <v>13</v>
+        <v>64</v>
       </c>
       <c r="I376" s="3"/>
       <c r="J376" s="3" t="s">
-        <v>471</v>
-      </c>
-      <c r="K376" s="3"/>
-      <c r="L376" s="3"/>
+        <v>21</v>
+      </c>
+      <c r="K376" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="L376" s="3" t="s">
+        <v>1363</v>
+      </c>
       <c r="M376" s="3"/>
     </row>
     <row r="377" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A377" s="3" t="s">
-        <v>1359</v>
+        <v>1364</v>
       </c>
       <c r="B377" s="3" t="s">
-        <v>1069</v>
+        <v>137</v>
       </c>
       <c r="C377" s="3" t="s">
-        <v>1070</v>
+        <v>412</v>
       </c>
       <c r="D377" s="3" t="s">
-        <v>1360</v>
+        <v>1365</v>
       </c>
       <c r="E377" s="3" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="F377" s="3" t="s">
-        <v>1361</v>
+        <v>1366</v>
       </c>
       <c r="G377" s="3"/>
       <c r="H377" s="3">
-        <v>24</v>
-      </c>
-      <c r="I377" s="3">
-        <v>45</v>
-      </c>
+        <v>36</v>
+      </c>
+      <c r="I377" s="3"/>
       <c r="J377" s="3" t="s">
         <v>471</v>
       </c>
@@ -18127,26 +17906,26 @@
     </row>
     <row r="378" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A378" s="3" t="s">
-        <v>1362</v>
+        <v>1367</v>
       </c>
       <c r="B378" s="3" t="s">
-        <v>798</v>
+        <v>175</v>
       </c>
       <c r="C378" s="3" t="s">
-        <v>799</v>
+        <v>176</v>
       </c>
       <c r="D378" s="3" t="s">
-        <v>1363</v>
+        <v>1368</v>
       </c>
       <c r="E378" s="3" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="F378" s="3" t="s">
-        <v>1364</v>
+        <v>1369</v>
       </c>
       <c r="G378" s="3"/>
       <c r="H378" s="3">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="I378" s="3"/>
       <c r="J378" s="3" t="s">
@@ -18155,956 +17934,6 @@
       <c r="K378" s="3"/>
       <c r="L378" s="3"/>
       <c r="M378" s="3"/>
-    </row>
-    <row r="379" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A379" s="3" t="s">
-        <v>1365</v>
-      </c>
-      <c r="B379" s="3" t="s">
-        <v>1019</v>
-      </c>
-      <c r="C379" s="3" t="s">
-        <v>1020</v>
-      </c>
-      <c r="D379" s="3" t="s">
-        <v>1366</v>
-      </c>
-      <c r="E379" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="F379" s="3" t="s">
-        <v>1367</v>
-      </c>
-      <c r="G379" s="3"/>
-      <c r="H379" s="3">
-        <v>31</v>
-      </c>
-      <c r="I379" s="3">
-        <v>40</v>
-      </c>
-      <c r="J379" s="3" t="s">
-        <v>471</v>
-      </c>
-      <c r="K379" s="3"/>
-      <c r="L379" s="3"/>
-      <c r="M379" s="3"/>
-    </row>
-    <row r="380" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A380" s="3" t="s">
-        <v>1365</v>
-      </c>
-      <c r="B380" s="3" t="s">
-        <v>896</v>
-      </c>
-      <c r="C380" s="3" t="s">
-        <v>897</v>
-      </c>
-      <c r="D380" s="3" t="s">
-        <v>1368</v>
-      </c>
-      <c r="E380" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="F380" s="3" t="s">
-        <v>1369</v>
-      </c>
-      <c r="G380" s="3"/>
-      <c r="H380" s="3">
-        <v>58</v>
-      </c>
-      <c r="I380" s="3"/>
-      <c r="J380" s="3" t="s">
-        <v>471</v>
-      </c>
-      <c r="K380" s="3"/>
-      <c r="L380" s="3"/>
-      <c r="M380" s="3"/>
-    </row>
-    <row r="381" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A381" s="3" t="s">
-        <v>1370</v>
-      </c>
-      <c r="B381" s="3" t="s">
-        <v>1019</v>
-      </c>
-      <c r="C381" s="3" t="s">
-        <v>1020</v>
-      </c>
-      <c r="D381" s="3" t="s">
-        <v>1371</v>
-      </c>
-      <c r="E381" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="F381" s="3" t="s">
-        <v>1372</v>
-      </c>
-      <c r="G381" s="3"/>
-      <c r="H381" s="3">
-        <v>13</v>
-      </c>
-      <c r="I381" s="3">
-        <v>40</v>
-      </c>
-      <c r="J381" s="3" t="s">
-        <v>471</v>
-      </c>
-      <c r="K381" s="3"/>
-      <c r="L381" s="3"/>
-      <c r="M381" s="3"/>
-    </row>
-    <row r="382" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A382" s="3" t="s">
-        <v>1373</v>
-      </c>
-      <c r="B382" s="3" t="s">
-        <v>835</v>
-      </c>
-      <c r="C382" s="3" t="s">
-        <v>836</v>
-      </c>
-      <c r="D382" s="3" t="s">
-        <v>1374</v>
-      </c>
-      <c r="E382" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="F382" s="3" t="s">
-        <v>1375</v>
-      </c>
-      <c r="G382" s="3"/>
-      <c r="H382" s="3">
-        <v>10</v>
-      </c>
-      <c r="I382" s="3"/>
-      <c r="J382" s="3" t="s">
-        <v>471</v>
-      </c>
-      <c r="K382" s="3"/>
-      <c r="L382" s="3"/>
-      <c r="M382" s="3"/>
-    </row>
-    <row r="383" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A383" s="3" t="s">
-        <v>1376</v>
-      </c>
-      <c r="B383" s="3" t="s">
-        <v>870</v>
-      </c>
-      <c r="C383" s="3" t="s">
-        <v>871</v>
-      </c>
-      <c r="D383" s="3" t="s">
-        <v>1377</v>
-      </c>
-      <c r="E383" s="3" t="s">
-        <v>746</v>
-      </c>
-      <c r="F383" s="3" t="s">
-        <v>1378</v>
-      </c>
-      <c r="G383" s="3"/>
-      <c r="H383" s="3">
-        <v>69</v>
-      </c>
-      <c r="I383" s="3">
-        <v>65</v>
-      </c>
-      <c r="J383" s="3" t="s">
-        <v>471</v>
-      </c>
-      <c r="K383" s="3"/>
-      <c r="L383" s="3"/>
-      <c r="M383" s="3"/>
-    </row>
-    <row r="384" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A384" s="3" t="s">
-        <v>1379</v>
-      </c>
-      <c r="B384" s="3" t="s">
-        <v>835</v>
-      </c>
-      <c r="C384" s="3" t="s">
-        <v>836</v>
-      </c>
-      <c r="D384" s="3" t="s">
-        <v>1380</v>
-      </c>
-      <c r="E384" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="F384" s="3" t="s">
-        <v>1381</v>
-      </c>
-      <c r="G384" s="3"/>
-      <c r="H384" s="3">
-        <v>18</v>
-      </c>
-      <c r="I384" s="3"/>
-      <c r="J384" s="3" t="s">
-        <v>471</v>
-      </c>
-      <c r="K384" s="3"/>
-      <c r="L384" s="3"/>
-      <c r="M384" s="3"/>
-    </row>
-    <row r="385" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A385" s="3" t="s">
-        <v>1382</v>
-      </c>
-      <c r="B385" s="3" t="s">
-        <v>1383</v>
-      </c>
-      <c r="C385" s="3" t="s">
-        <v>1384</v>
-      </c>
-      <c r="D385" s="3" t="s">
-        <v>1385</v>
-      </c>
-      <c r="E385" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="F385" s="3" t="s">
-        <v>1386</v>
-      </c>
-      <c r="G385" s="3"/>
-      <c r="H385" s="3">
-        <v>17</v>
-      </c>
-      <c r="I385" s="3"/>
-      <c r="J385" s="3" t="s">
-        <v>471</v>
-      </c>
-      <c r="K385" s="3"/>
-      <c r="L385" s="3"/>
-      <c r="M385" s="3"/>
-    </row>
-    <row r="386" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A386" s="3" t="s">
-        <v>1387</v>
-      </c>
-      <c r="B386" s="3" t="s">
-        <v>890</v>
-      </c>
-      <c r="C386" s="3" t="s">
-        <v>891</v>
-      </c>
-      <c r="D386" s="3" t="s">
-        <v>1388</v>
-      </c>
-      <c r="E386" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="F386" s="3" t="s">
-        <v>1389</v>
-      </c>
-      <c r="G386" s="3"/>
-      <c r="H386" s="3">
-        <v>18</v>
-      </c>
-      <c r="I386" s="3"/>
-      <c r="J386" s="3" t="s">
-        <v>471</v>
-      </c>
-      <c r="K386" s="3"/>
-      <c r="L386" s="3"/>
-      <c r="M386" s="3"/>
-    </row>
-    <row r="387" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A387" s="3" t="s">
-        <v>1390</v>
-      </c>
-      <c r="B387" s="3" t="s">
-        <v>890</v>
-      </c>
-      <c r="C387" s="3" t="s">
-        <v>891</v>
-      </c>
-      <c r="D387" s="3" t="s">
-        <v>1391</v>
-      </c>
-      <c r="E387" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="F387" s="3" t="s">
-        <v>1392</v>
-      </c>
-      <c r="G387" s="3"/>
-      <c r="H387" s="3">
-        <v>24</v>
-      </c>
-      <c r="I387" s="3"/>
-      <c r="J387" s="3" t="s">
-        <v>471</v>
-      </c>
-      <c r="K387" s="3"/>
-      <c r="L387" s="3"/>
-      <c r="M387" s="3"/>
-    </row>
-    <row r="388" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A388" s="3" t="s">
-        <v>1390</v>
-      </c>
-      <c r="B388" s="3" t="s">
-        <v>896</v>
-      </c>
-      <c r="C388" s="3" t="s">
-        <v>897</v>
-      </c>
-      <c r="D388" s="3" t="s">
-        <v>1393</v>
-      </c>
-      <c r="E388" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="F388" s="3" t="s">
-        <v>1394</v>
-      </c>
-      <c r="G388" s="3"/>
-      <c r="H388" s="3">
-        <v>34</v>
-      </c>
-      <c r="I388" s="3"/>
-      <c r="J388" s="3" t="s">
-        <v>471</v>
-      </c>
-      <c r="K388" s="3"/>
-      <c r="L388" s="3"/>
-      <c r="M388" s="3"/>
-    </row>
-    <row r="389" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A389" s="3" t="s">
-        <v>1395</v>
-      </c>
-      <c r="B389" s="3" t="s">
-        <v>781</v>
-      </c>
-      <c r="C389" s="3" t="s">
-        <v>782</v>
-      </c>
-      <c r="D389" s="3" t="s">
-        <v>1396</v>
-      </c>
-      <c r="E389" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="F389" s="3" t="s">
-        <v>866</v>
-      </c>
-      <c r="G389" s="3"/>
-      <c r="H389" s="3">
-        <v>31</v>
-      </c>
-      <c r="I389" s="3">
-        <v>45</v>
-      </c>
-      <c r="J389" s="3" t="s">
-        <v>471</v>
-      </c>
-      <c r="K389" s="3"/>
-      <c r="L389" s="3"/>
-      <c r="M389" s="3"/>
-    </row>
-    <row r="390" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A390" s="3" t="s">
-        <v>1397</v>
-      </c>
-      <c r="B390" s="3" t="s">
-        <v>209</v>
-      </c>
-      <c r="C390" s="3" t="s">
-        <v>210</v>
-      </c>
-      <c r="D390" s="3" t="s">
-        <v>1398</v>
-      </c>
-      <c r="E390" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="F390" s="3" t="s">
-        <v>212</v>
-      </c>
-      <c r="G390" s="3"/>
-      <c r="H390" s="3">
-        <v>5</v>
-      </c>
-      <c r="I390" s="3"/>
-      <c r="J390" s="3" t="s">
-        <v>471</v>
-      </c>
-      <c r="K390" s="3"/>
-      <c r="L390" s="3"/>
-      <c r="M390" s="3"/>
-    </row>
-    <row r="391" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A391" s="3" t="s">
-        <v>1399</v>
-      </c>
-      <c r="B391" s="3" t="s">
-        <v>180</v>
-      </c>
-      <c r="C391" s="3" t="s">
-        <v>1321</v>
-      </c>
-      <c r="D391" s="3" t="s">
-        <v>1400</v>
-      </c>
-      <c r="E391" s="3" t="s">
-        <v>746</v>
-      </c>
-      <c r="F391" s="3" t="s">
-        <v>1401</v>
-      </c>
-      <c r="G391" s="3"/>
-      <c r="H391" s="3">
-        <v>72</v>
-      </c>
-      <c r="I391" s="3">
-        <v>65</v>
-      </c>
-      <c r="J391" s="3" t="s">
-        <v>471</v>
-      </c>
-      <c r="K391" s="3"/>
-      <c r="L391" s="3"/>
-      <c r="M391" s="3"/>
-    </row>
-    <row r="392" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A392" s="3" t="s">
-        <v>1402</v>
-      </c>
-      <c r="B392" s="3" t="s">
-        <v>811</v>
-      </c>
-      <c r="C392" s="3" t="s">
-        <v>812</v>
-      </c>
-      <c r="D392" s="3" t="s">
-        <v>1403</v>
-      </c>
-      <c r="E392" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="F392" s="3" t="s">
-        <v>1404</v>
-      </c>
-      <c r="G392" s="3"/>
-      <c r="H392" s="3">
-        <v>21</v>
-      </c>
-      <c r="I392" s="3"/>
-      <c r="J392" s="3" t="s">
-        <v>471</v>
-      </c>
-      <c r="K392" s="3"/>
-      <c r="L392" s="3"/>
-      <c r="M392" s="3"/>
-    </row>
-    <row r="393" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A393" s="3" t="s">
-        <v>1405</v>
-      </c>
-      <c r="B393" s="3" t="s">
-        <v>811</v>
-      </c>
-      <c r="C393" s="3" t="s">
-        <v>812</v>
-      </c>
-      <c r="D393" s="3" t="s">
-        <v>1406</v>
-      </c>
-      <c r="E393" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="F393" s="3" t="s">
-        <v>1404</v>
-      </c>
-      <c r="G393" s="3"/>
-      <c r="H393" s="3">
-        <v>16</v>
-      </c>
-      <c r="I393" s="3"/>
-      <c r="J393" s="3" t="s">
-        <v>471</v>
-      </c>
-      <c r="K393" s="3"/>
-      <c r="L393" s="3"/>
-      <c r="M393" s="3"/>
-    </row>
-    <row r="394" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A394" s="3" t="s">
-        <v>1407</v>
-      </c>
-      <c r="B394" s="3" t="s">
-        <v>1019</v>
-      </c>
-      <c r="C394" s="3" t="s">
-        <v>1020</v>
-      </c>
-      <c r="D394" s="3" t="s">
-        <v>1408</v>
-      </c>
-      <c r="E394" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="F394" s="3" t="s">
-        <v>1409</v>
-      </c>
-      <c r="G394" s="3"/>
-      <c r="H394" s="3">
-        <v>35</v>
-      </c>
-      <c r="I394" s="3">
-        <v>40</v>
-      </c>
-      <c r="J394" s="3" t="s">
-        <v>471</v>
-      </c>
-      <c r="K394" s="3"/>
-      <c r="L394" s="3"/>
-      <c r="M394" s="3"/>
-    </row>
-    <row r="395" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A395" s="3" t="s">
-        <v>1410</v>
-      </c>
-      <c r="B395" s="3" t="s">
-        <v>751</v>
-      </c>
-      <c r="C395" s="3" t="s">
-        <v>752</v>
-      </c>
-      <c r="D395" s="3" t="s">
-        <v>1411</v>
-      </c>
-      <c r="E395" s="3" t="s">
-        <v>100</v>
-      </c>
-      <c r="F395" s="3" t="s">
-        <v>1412</v>
-      </c>
-      <c r="G395" s="3"/>
-      <c r="H395" s="3">
-        <v>69</v>
-      </c>
-      <c r="I395" s="3">
-        <v>65</v>
-      </c>
-      <c r="J395" s="3" t="s">
-        <v>471</v>
-      </c>
-      <c r="K395" s="3"/>
-      <c r="L395" s="3"/>
-      <c r="M395" s="3"/>
-    </row>
-    <row r="396" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A396" s="3" t="s">
-        <v>1413</v>
-      </c>
-      <c r="B396" s="3" t="s">
-        <v>791</v>
-      </c>
-      <c r="C396" s="3" t="s">
-        <v>792</v>
-      </c>
-      <c r="D396" s="3" t="s">
-        <v>1414</v>
-      </c>
-      <c r="E396" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="F396" s="3" t="s">
-        <v>1415</v>
-      </c>
-      <c r="G396" s="3"/>
-      <c r="H396" s="3">
-        <v>36</v>
-      </c>
-      <c r="I396" s="3"/>
-      <c r="J396" s="3" t="s">
-        <v>471</v>
-      </c>
-      <c r="K396" s="3"/>
-      <c r="L396" s="3"/>
-      <c r="M396" s="3"/>
-    </row>
-    <row r="397" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A397" s="3" t="s">
-        <v>1416</v>
-      </c>
-      <c r="B397" s="3" t="s">
-        <v>1115</v>
-      </c>
-      <c r="C397" s="3" t="s">
-        <v>1116</v>
-      </c>
-      <c r="D397" s="3" t="s">
-        <v>1417</v>
-      </c>
-      <c r="E397" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="F397" s="3" t="s">
-        <v>1345</v>
-      </c>
-      <c r="G397" s="3"/>
-      <c r="H397" s="3">
-        <v>18</v>
-      </c>
-      <c r="I397" s="3"/>
-      <c r="J397" s="3" t="s">
-        <v>471</v>
-      </c>
-      <c r="K397" s="3"/>
-      <c r="L397" s="3"/>
-      <c r="M397" s="3"/>
-    </row>
-    <row r="398" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A398" s="3" t="s">
-        <v>1418</v>
-      </c>
-      <c r="B398" s="3" t="s">
-        <v>1069</v>
-      </c>
-      <c r="C398" s="3" t="s">
-        <v>1070</v>
-      </c>
-      <c r="D398" s="3" t="s">
-        <v>1419</v>
-      </c>
-      <c r="E398" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="F398" s="3" t="s">
-        <v>1420</v>
-      </c>
-      <c r="G398" s="3"/>
-      <c r="H398" s="3">
-        <v>29</v>
-      </c>
-      <c r="I398" s="3">
-        <v>45</v>
-      </c>
-      <c r="J398" s="3" t="s">
-        <v>471</v>
-      </c>
-      <c r="K398" s="3"/>
-      <c r="L398" s="3"/>
-      <c r="M398" s="3"/>
-    </row>
-    <row r="399" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A399" s="3" t="s">
-        <v>1421</v>
-      </c>
-      <c r="B399" s="3" t="s">
-        <v>1422</v>
-      </c>
-      <c r="C399" s="3" t="s">
-        <v>1423</v>
-      </c>
-      <c r="D399" s="3" t="s">
-        <v>1424</v>
-      </c>
-      <c r="E399" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="F399" s="3" t="s">
-        <v>1425</v>
-      </c>
-      <c r="G399" s="3"/>
-      <c r="H399" s="3">
-        <v>26</v>
-      </c>
-      <c r="I399" s="3"/>
-      <c r="J399" s="3" t="s">
-        <v>471</v>
-      </c>
-      <c r="K399" s="3"/>
-      <c r="L399" s="3"/>
-      <c r="M399" s="3"/>
-    </row>
-    <row r="400" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A400" s="3" t="s">
-        <v>1426</v>
-      </c>
-      <c r="B400" s="3" t="s">
-        <v>791</v>
-      </c>
-      <c r="C400" s="3" t="s">
-        <v>792</v>
-      </c>
-      <c r="D400" s="3" t="s">
-        <v>1427</v>
-      </c>
-      <c r="E400" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="F400" s="3" t="s">
-        <v>1428</v>
-      </c>
-      <c r="G400" s="3"/>
-      <c r="H400" s="3">
-        <v>22</v>
-      </c>
-      <c r="I400" s="3"/>
-      <c r="J400" s="3" t="s">
-        <v>471</v>
-      </c>
-      <c r="K400" s="3"/>
-      <c r="L400" s="3"/>
-      <c r="M400" s="3"/>
-    </row>
-    <row r="401" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A401" s="3" t="s">
-        <v>1429</v>
-      </c>
-      <c r="B401" s="3" t="s">
-        <v>870</v>
-      </c>
-      <c r="C401" s="3" t="s">
-        <v>871</v>
-      </c>
-      <c r="D401" s="3" t="s">
-        <v>1430</v>
-      </c>
-      <c r="E401" s="3" t="s">
-        <v>746</v>
-      </c>
-      <c r="F401" s="3" t="s">
-        <v>1431</v>
-      </c>
-      <c r="G401" s="3"/>
-      <c r="H401" s="3">
-        <v>81</v>
-      </c>
-      <c r="I401" s="3">
-        <v>75</v>
-      </c>
-      <c r="J401" s="3" t="s">
-        <v>471</v>
-      </c>
-      <c r="K401" s="3"/>
-      <c r="L401" s="3"/>
-      <c r="M401" s="3"/>
-    </row>
-    <row r="402" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A402" s="3" t="s">
-        <v>1432</v>
-      </c>
-      <c r="B402" s="3" t="s">
-        <v>775</v>
-      </c>
-      <c r="C402" s="3" t="s">
-        <v>776</v>
-      </c>
-      <c r="D402" s="3" t="s">
-        <v>1433</v>
-      </c>
-      <c r="E402" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="F402" s="3" t="s">
-        <v>557</v>
-      </c>
-      <c r="G402" s="3"/>
-      <c r="H402" s="3">
-        <v>30</v>
-      </c>
-      <c r="I402" s="3"/>
-      <c r="J402" s="3" t="s">
-        <v>471</v>
-      </c>
-      <c r="K402" s="3"/>
-      <c r="L402" s="3"/>
-      <c r="M402" s="3"/>
-    </row>
-    <row r="403" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A403" s="3" t="s">
-        <v>1432</v>
-      </c>
-      <c r="B403" s="3" t="s">
-        <v>775</v>
-      </c>
-      <c r="C403" s="3" t="s">
-        <v>776</v>
-      </c>
-      <c r="D403" s="3" t="s">
-        <v>1434</v>
-      </c>
-      <c r="E403" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="F403" s="3" t="s">
-        <v>1435</v>
-      </c>
-      <c r="G403" s="3"/>
-      <c r="H403" s="3">
-        <v>22</v>
-      </c>
-      <c r="I403" s="3"/>
-      <c r="J403" s="3" t="s">
-        <v>471</v>
-      </c>
-      <c r="K403" s="3"/>
-      <c r="L403" s="3"/>
-      <c r="M403" s="3"/>
-    </row>
-    <row r="404" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A404" s="3" t="s">
-        <v>1436</v>
-      </c>
-      <c r="B404" s="3" t="s">
-        <v>775</v>
-      </c>
-      <c r="C404" s="3" t="s">
-        <v>776</v>
-      </c>
-      <c r="D404" s="3" t="s">
-        <v>1437</v>
-      </c>
-      <c r="E404" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="F404" s="3" t="s">
-        <v>1438</v>
-      </c>
-      <c r="G404" s="3"/>
-      <c r="H404" s="3">
-        <v>13</v>
-      </c>
-      <c r="I404" s="3"/>
-      <c r="J404" s="3" t="s">
-        <v>471</v>
-      </c>
-      <c r="K404" s="3"/>
-      <c r="L404" s="3"/>
-      <c r="M404" s="3"/>
-    </row>
-    <row r="405" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A405" s="3" t="s">
-        <v>1439</v>
-      </c>
-      <c r="B405" s="3" t="s">
-        <v>775</v>
-      </c>
-      <c r="C405" s="3" t="s">
-        <v>776</v>
-      </c>
-      <c r="D405" s="3" t="s">
-        <v>1440</v>
-      </c>
-      <c r="E405" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="F405" s="3" t="s">
-        <v>1441</v>
-      </c>
-      <c r="G405" s="3"/>
-      <c r="H405" s="3">
-        <v>62</v>
-      </c>
-      <c r="I405" s="3">
-        <v>65</v>
-      </c>
-      <c r="J405" s="3" t="s">
-        <v>471</v>
-      </c>
-      <c r="K405" s="3"/>
-      <c r="L405" s="3"/>
-      <c r="M405" s="3"/>
-    </row>
-    <row r="406" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A406" s="3" t="s">
-        <v>1442</v>
-      </c>
-      <c r="B406" s="3" t="s">
-        <v>1115</v>
-      </c>
-      <c r="C406" s="3" t="s">
-        <v>1116</v>
-      </c>
-      <c r="D406" s="3" t="s">
-        <v>1443</v>
-      </c>
-      <c r="E406" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="F406" s="3" t="s">
-        <v>1444</v>
-      </c>
-      <c r="G406" s="3"/>
-      <c r="H406" s="3">
-        <v>18</v>
-      </c>
-      <c r="I406" s="3"/>
-      <c r="J406" s="3" t="s">
-        <v>471</v>
-      </c>
-      <c r="K406" s="3"/>
-      <c r="L406" s="3"/>
-      <c r="M406" s="3"/>
-    </row>
-    <row r="407" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A407" s="3" t="s">
-        <v>1445</v>
-      </c>
-      <c r="B407" s="3" t="s">
-        <v>835</v>
-      </c>
-      <c r="C407" s="3" t="s">
-        <v>836</v>
-      </c>
-      <c r="D407" s="3" t="s">
-        <v>1446</v>
-      </c>
-      <c r="E407" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="F407" s="3" t="s">
-        <v>1447</v>
-      </c>
-      <c r="G407" s="3"/>
-      <c r="H407" s="3">
-        <v>16</v>
-      </c>
-      <c r="I407" s="3"/>
-      <c r="J407" s="3" t="s">
-        <v>471</v>
-      </c>
-      <c r="K407" s="3"/>
-      <c r="L407" s="3"/>
-      <c r="M407" s="3"/>
-    </row>
-    <row r="408" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A408" s="3" t="s">
-        <v>1448</v>
-      </c>
-      <c r="B408" s="3" t="s">
-        <v>1449</v>
-      </c>
-      <c r="C408" s="3" t="s">
-        <v>1450</v>
-      </c>
-      <c r="D408" s="3" t="s">
-        <v>1451</v>
-      </c>
-      <c r="E408" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="F408" s="3" t="s">
-        <v>1452</v>
-      </c>
-      <c r="G408" s="3"/>
-      <c r="H408" s="3">
-        <v>23</v>
-      </c>
-      <c r="I408" s="3"/>
-      <c r="J408" s="3" t="s">
-        <v>471</v>
-      </c>
-      <c r="K408" s="3"/>
-      <c r="L408" s="3"/>
-      <c r="M408" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/camera_events.xlsx
+++ b/camera_events.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30131"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{7B6D2C41-31EA-4D43-8E20-11775BC1C696}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{CC9F920B-D726-4CF4-BA82-ECA6257C1568}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="57840" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="sheet1" sheetId="1" r:id="rId1"/>
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="960" uniqueCount="342">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="840" uniqueCount="315">
   <si>
     <t>Time</t>
   </si>
@@ -62,6 +62,111 @@
     <t>Event URL</t>
   </si>
   <si>
+    <t>07/01/2026 12:19:17 PM</t>
+  </si>
+  <si>
+    <t>TT. 5362</t>
+  </si>
+  <si>
+    <t>RICHARD FLECKENSTEIN #2038</t>
+  </si>
+  <si>
+    <t>TT DRIVERS, Truck Drivers Pay Roll</t>
+  </si>
+  <si>
+    <t>Mobile Usage</t>
+  </si>
+  <si>
+    <t>Light Traffic</t>
+  </si>
+  <si>
+    <t>Needs Coaching</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>County Road 59, 17.0 mi ENE Fort Lupton, Weld County, CO</t>
+  </si>
+  <si>
+    <t>43</t>
+  </si>
+  <si>
+    <t>https://cloud.samsara.com/o/9002774/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54451eb1-35c4-5ffa-ba61-6e9a365ede0b</t>
+  </si>
+  <si>
+    <t>06/29/2026 12:48:21 PM</t>
+  </si>
+  <si>
+    <t>TT. 9326</t>
+  </si>
+  <si>
+    <t>TROY RAMIREZ  #1988</t>
+  </si>
+  <si>
+    <t>Harsh Brake</t>
+  </si>
+  <si>
+    <t>Coached</t>
+  </si>
+  <si>
+    <t>Sheridan Boulevard, Arvada, CO, 80003</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>0.59</t>
+  </si>
+  <si>
+    <t>https://cloud.samsara.com/o/9002774/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445147f-1983-5a9f-9bfc-185fe4e8ea47</t>
+  </si>
+  <si>
+    <t>06/29/2026 8:59:17 AM</t>
+  </si>
+  <si>
+    <t>TT. 5353</t>
+  </si>
+  <si>
+    <t>BRAD CRAIG #2053</t>
+  </si>
+  <si>
+    <t>Moderate Traffic</t>
+  </si>
+  <si>
+    <t>Dwight D. Eisenhower Highway, Mead, CO, 80542</t>
+  </si>
+  <si>
+    <t>17</t>
+  </si>
+  <si>
+    <t>0.54</t>
+  </si>
+  <si>
+    <t>https://cloud.samsara.com/o/9002774/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=544513ad-62db-5561-a244-d43ae8157a15</t>
+  </si>
+  <si>
+    <t>06/26/2026 5:00:15 PM</t>
+  </si>
+  <si>
+    <t>TT. 5358</t>
+  </si>
+  <si>
+    <t>CLEMENTE CHAVEZ  #1971</t>
+  </si>
+  <si>
+    <t>Obstructed Camera</t>
+  </si>
+  <si>
+    <t>Heartland Expressway, Brighton, CO, 80601</t>
+  </si>
+  <si>
+    <t>67</t>
+  </si>
+  <si>
+    <t>https://cloud.samsara.com/o/9002774/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=544505f2-a2be-50d1-93b9-1384ccc8fbc7</t>
+  </si>
+  <si>
     <t>06/26/2026 11:57:57 AM</t>
   </si>
   <si>
@@ -71,21 +176,9 @@
     <t>SAMANTHA HERNANDEZ #0945</t>
   </si>
   <si>
-    <t>TT DRIVERS, Truck Drivers Pay Roll</t>
-  </si>
-  <si>
     <t>Following Distance</t>
   </si>
   <si>
-    <t>Light Traffic</t>
-  </si>
-  <si>
-    <t>Coached</t>
-  </si>
-  <si>
-    <t>-</t>
-  </si>
-  <si>
     <t>Dwight D. Eisenhower Highway, Otto, WY</t>
   </si>
   <si>
@@ -104,9 +197,6 @@
     <t>WENDY COLTON  #1939</t>
   </si>
   <si>
-    <t>Needs Coaching</t>
-  </si>
-  <si>
     <t>Dwight D. Eisenhower Highway, 3.3 mi WSW Cheyenne, Laramie County, WY, 82005</t>
   </si>
   <si>
@@ -143,15 +233,6 @@
     <t>06/25/2026 8:04:24 AM</t>
   </si>
   <si>
-    <t>TT. 5358</t>
-  </si>
-  <si>
-    <t>CLEMENTE CHAVEZ  #1971</t>
-  </si>
-  <si>
-    <t>Obstructed Camera</t>
-  </si>
-  <si>
     <t>CanAm Highway, Brighton, CO, 80640</t>
   </si>
   <si>
@@ -170,18 +251,12 @@
     <t>ROBERT PARKER #1072</t>
   </si>
   <si>
-    <t>Harsh Brake</t>
-  </si>
-  <si>
     <t>Construction, Moderate Traffic</t>
   </si>
   <si>
     <t>East Bison Highway, Hudson, CO, 80642</t>
   </si>
   <si>
-    <t>6</t>
-  </si>
-  <si>
     <t>0.73</t>
   </si>
   <si>
@@ -236,9 +311,6 @@
     <t>JASON MILLER #1070</t>
   </si>
   <si>
-    <t>Moderate Traffic</t>
-  </si>
-  <si>
     <t>Grand Army of the Republic Highway;Heartland Expressway, Roy, CO, 80643</t>
   </si>
   <si>
@@ -293,9 +365,6 @@
     <t xml:space="preserve">low boys </t>
   </si>
   <si>
-    <t>Mobile Usage</t>
-  </si>
-  <si>
     <t>Dwight D. Eisenhower Highway, Johnstown, CO, 80534</t>
   </si>
   <si>
@@ -371,9 +440,6 @@
     <t>TT. 1980</t>
   </si>
   <si>
-    <t>BRAD CRAIG #2053</t>
-  </si>
-  <si>
     <t>Passengers, Congested</t>
   </si>
   <si>
@@ -635,9 +701,6 @@
     <t>I 70, Denver, CO, 80010-1425</t>
   </si>
   <si>
-    <t>17</t>
-  </si>
-  <si>
     <t>0.57</t>
   </si>
   <si>
@@ -665,9 +728,6 @@
     <t>04/20/2026 2:23:49 PM</t>
   </si>
   <si>
-    <t>TT. 9326</t>
-  </si>
-  <si>
     <t>Construction, Pedestrians, Moderate Traffic</t>
   </si>
   <si>
@@ -740,9 +800,6 @@
     <t>South Valley Highway, Denver, CO, 80201</t>
   </si>
   <si>
-    <t>43</t>
-  </si>
-  <si>
     <t>https://cloud.samsara.com/o/9002774/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445794b-0fb9-5061-961c-e1cfe40d139f</t>
   </si>
   <si>
@@ -770,9 +827,6 @@
     <t>E-470, Aurora, CO</t>
   </si>
   <si>
-    <t>67</t>
-  </si>
-  <si>
     <t>https://cloud.samsara.com/o/9002774/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54457424-260d-5707-a598-be8e6f6e7e47</t>
   </si>
   <si>
@@ -906,141 +960,6 @@
   </si>
   <si>
     <t>https://cloud.samsara.com/o/9002774/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=544562c8-e2cc-58e4-989c-2a5834953d73</t>
-  </si>
-  <si>
-    <t>04/03/2026 9:04:33 AM</t>
-  </si>
-  <si>
-    <t>TT. 5354</t>
-  </si>
-  <si>
-    <t>RUBEN MARTINEZ #0641</t>
-  </si>
-  <si>
-    <t>No Seat Belt</t>
-  </si>
-  <si>
-    <t>Peña Boulevard, Denver, CO, 80011-3316</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/9002774/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=544553a8-ee0f-5f08-b9db-4c097f8c9654</t>
-  </si>
-  <si>
-    <t>04/02/2026 4:02:41 PM</t>
-  </si>
-  <si>
-    <t>United States Highway 285, Lakewood, CO, 80235</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/9002774/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54455001-6524-5a30-945f-8e4c4449e9fd</t>
-  </si>
-  <si>
-    <t>04/01/2026 12:16:02 PM</t>
-  </si>
-  <si>
-    <t>I 25, Johnstown, CO, 80537</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/9002774/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54454a0b-881f-5c19-95a5-3f9baadbcd84</t>
-  </si>
-  <si>
-    <t>04/01/2026 9:47:06 AM</t>
-  </si>
-  <si>
-    <t>West I 25 Frontage Road, Del Camino, CO, 80504-5510</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/9002774/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54454983-2d81-59f6-93f3-7d27816fdd9c</t>
-  </si>
-  <si>
-    <t>04/01/2026 7:30:47 AM</t>
-  </si>
-  <si>
-    <t>I 76, Zuni, CO, 80221</t>
-  </si>
-  <si>
-    <t>58</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/9002774/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54454906-5fcb-5f56-aa40-542480b6ade2</t>
-  </si>
-  <si>
-    <t>03/31/2026 2:08:40 PM</t>
-  </si>
-  <si>
-    <t>E-470, Thornton, CO, 80602</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/9002774/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445454c-4720-5215-bc05-cca1bd65c86b</t>
-  </si>
-  <si>
-    <t>03/31/2026 9:06:23 AM</t>
-  </si>
-  <si>
-    <t>I 76, Berkley, CO, 80003</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/9002774/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54454437-8787-5a28-97f4-970fec3bf74c</t>
-  </si>
-  <si>
-    <t>03/31/2026 7:58:46 AM</t>
-  </si>
-  <si>
-    <t>Passengers, Light Traffic</t>
-  </si>
-  <si>
-    <t>I 25, 7.3 mi SSW Castle Rock, Douglas County, CO, 80184</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/9002774/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=544543f9-a167-56a3-8287-d159f76e9d60</t>
-  </si>
-  <si>
-    <t>03/30/2026 4:49:29 PM</t>
-  </si>
-  <si>
-    <t>3701 Fox Street, Denver, CO, 80216</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/9002774/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=544540b9-295a-5448-a0a0-341d9690d3df</t>
-  </si>
-  <si>
-    <t>03/30/2026 11:55:36 AM</t>
-  </si>
-  <si>
-    <t>State Highway 257, Greeley, CO</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/9002774/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54453fac-18f3-5cbf-a12b-592fe167bc87</t>
-  </si>
-  <si>
-    <t>03/30/2026 11:19:25 AM</t>
-  </si>
-  <si>
-    <t>LUIS ALVAREZ  #1908</t>
-  </si>
-  <si>
-    <t>26851 United States Highway 24, Peyton, CO, 80808</t>
-  </si>
-  <si>
-    <t>54</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/9002774/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54453f8a-f8c6-54e1-97f0-bacf76ab93b7</t>
-  </si>
-  <si>
-    <t>03/30/2026 9:47:24 AM</t>
-  </si>
-  <si>
-    <t>TT. 5362</t>
-  </si>
-  <si>
-    <t>South Havana Street, Beverly Hills, CO</t>
-  </si>
-  <si>
-    <t>35</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/9002774/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54453f36-ba34-57c3-82c3-2fe04a7e3918</t>
   </si>
 </sst>
 </file>
@@ -1417,10 +1336,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:O64"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:O56"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1467,7 +1386,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>15</v>
       </c>
@@ -1514,7 +1433,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>26</v>
       </c>
@@ -1531,92 +1450,92 @@
         <v>18</v>
       </c>
       <c r="F3" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="G3" t="s">
         <v>20</v>
       </c>
       <c r="H3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I3" t="s">
+        <v>22</v>
+      </c>
+      <c r="J3" t="s">
+        <v>31</v>
+      </c>
+      <c r="K3" t="s">
+        <v>32</v>
+      </c>
+      <c r="L3" t="s">
+        <v>22</v>
+      </c>
+      <c r="M3" t="s">
+        <v>22</v>
+      </c>
+      <c r="N3" t="s">
+        <v>33</v>
+      </c>
+      <c r="O3" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>35</v>
+      </c>
+      <c r="B4" t="s">
+        <v>36</v>
+      </c>
+      <c r="C4" t="s">
+        <v>37</v>
+      </c>
+      <c r="D4" t="s">
+        <v>18</v>
+      </c>
+      <c r="E4" t="s">
+        <v>18</v>
+      </c>
+      <c r="F4" t="s">
         <v>29</v>
       </c>
-      <c r="I3" t="s">
-        <v>22</v>
-      </c>
-      <c r="J3" t="s">
-        <v>30</v>
-      </c>
-      <c r="K3" t="s">
-        <v>24</v>
-      </c>
-      <c r="L3" t="s">
-        <v>22</v>
-      </c>
-      <c r="M3" t="s">
-        <v>22</v>
-      </c>
-      <c r="N3" t="s">
-        <v>22</v>
-      </c>
-      <c r="O3" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>32</v>
-      </c>
-      <c r="B4" t="s">
-        <v>33</v>
-      </c>
-      <c r="C4" t="s">
-        <v>34</v>
-      </c>
-      <c r="D4" t="s">
-        <v>18</v>
-      </c>
-      <c r="E4" t="s">
-        <v>18</v>
-      </c>
-      <c r="F4" t="s">
-        <v>35</v>
-      </c>
       <c r="G4" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="H4" t="s">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="I4" t="s">
         <v>22</v>
       </c>
       <c r="J4" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="K4" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="L4" t="s">
         <v>22</v>
       </c>
       <c r="M4" t="s">
-        <v>39</v>
+        <v>22</v>
       </c>
       <c r="N4" t="s">
-        <v>22</v>
+        <v>41</v>
       </c>
       <c r="O4" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B5" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="C5" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="D5" t="s">
         <v>18</v>
@@ -1625,7 +1544,7 @@
         <v>18</v>
       </c>
       <c r="F5" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="G5" t="s">
         <v>22</v>
@@ -1637,10 +1556,10 @@
         <v>22</v>
       </c>
       <c r="J5" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="K5" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="L5" t="s">
         <v>22</v>
@@ -1652,18 +1571,18 @@
         <v>22</v>
       </c>
       <c r="O5" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="B6" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C6" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D6" t="s">
         <v>18</v>
@@ -1672,22 +1591,22 @@
         <v>18</v>
       </c>
       <c r="F6" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="G6" t="s">
-        <v>52</v>
+        <v>20</v>
       </c>
       <c r="H6" t="s">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="I6" t="s">
         <v>22</v>
       </c>
       <c r="J6" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="K6" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="L6" t="s">
         <v>22</v>
@@ -1696,13 +1615,13 @@
         <v>22</v>
       </c>
       <c r="N6" t="s">
-        <v>55</v>
+        <v>22</v>
       </c>
       <c r="O6" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>57</v>
       </c>
@@ -1719,13 +1638,13 @@
         <v>18</v>
       </c>
       <c r="F7" t="s">
-        <v>35</v>
+        <v>53</v>
       </c>
       <c r="G7" t="s">
         <v>20</v>
       </c>
       <c r="H7" t="s">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="I7" t="s">
         <v>22</v>
@@ -1734,45 +1653,45 @@
         <v>60</v>
       </c>
       <c r="K7" t="s">
+        <v>55</v>
+      </c>
+      <c r="L7" t="s">
+        <v>22</v>
+      </c>
+      <c r="M7" t="s">
+        <v>22</v>
+      </c>
+      <c r="N7" t="s">
+        <v>22</v>
+      </c>
+      <c r="O7" t="s">
         <v>61</v>
       </c>
-      <c r="L7" t="s">
-        <v>22</v>
-      </c>
-      <c r="M7" t="s">
-        <v>39</v>
-      </c>
-      <c r="N7" t="s">
-        <v>22</v>
-      </c>
-      <c r="O7" t="s">
+    </row>
+    <row r="8" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
         <v>62</v>
       </c>
-    </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
+      <c r="B8" t="s">
         <v>63</v>
       </c>
-      <c r="B8" t="s">
+      <c r="C8" t="s">
         <v>64</v>
       </c>
-      <c r="C8" t="s">
+      <c r="D8" t="s">
+        <v>18</v>
+      </c>
+      <c r="E8" t="s">
+        <v>18</v>
+      </c>
+      <c r="F8" t="s">
         <v>65</v>
       </c>
-      <c r="D8" t="s">
-        <v>18</v>
-      </c>
-      <c r="E8" t="s">
-        <v>18</v>
-      </c>
-      <c r="F8" t="s">
+      <c r="G8" t="s">
         <v>66</v>
       </c>
-      <c r="G8" t="s">
-        <v>20</v>
-      </c>
       <c r="H8" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="I8" t="s">
         <v>22</v>
@@ -1787,119 +1706,119 @@
         <v>22</v>
       </c>
       <c r="M8" t="s">
-        <v>22</v>
+        <v>69</v>
       </c>
       <c r="N8" t="s">
         <v>22</v>
       </c>
       <c r="O8" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B9" t="s">
-        <v>71</v>
+        <v>44</v>
       </c>
       <c r="C9" t="s">
+        <v>45</v>
+      </c>
+      <c r="D9" t="s">
+        <v>18</v>
+      </c>
+      <c r="E9" t="s">
+        <v>18</v>
+      </c>
+      <c r="F9" t="s">
+        <v>46</v>
+      </c>
+      <c r="G9" t="s">
+        <v>22</v>
+      </c>
+      <c r="H9" t="s">
+        <v>30</v>
+      </c>
+      <c r="I9" t="s">
+        <v>22</v>
+      </c>
+      <c r="J9" t="s">
         <v>72</v>
       </c>
-      <c r="D9" t="s">
-        <v>18</v>
-      </c>
-      <c r="E9" t="s">
-        <v>18</v>
-      </c>
-      <c r="F9" t="s">
-        <v>19</v>
-      </c>
-      <c r="G9" t="s">
+      <c r="K9" t="s">
         <v>73</v>
       </c>
-      <c r="H9" t="s">
-        <v>21</v>
-      </c>
-      <c r="I9" t="s">
-        <v>22</v>
-      </c>
-      <c r="J9" t="s">
+      <c r="L9" t="s">
+        <v>22</v>
+      </c>
+      <c r="M9" t="s">
+        <v>22</v>
+      </c>
+      <c r="N9" t="s">
+        <v>22</v>
+      </c>
+      <c r="O9" t="s">
         <v>74</v>
       </c>
-      <c r="K9" t="s">
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
         <v>75</v>
       </c>
-      <c r="L9" t="s">
-        <v>22</v>
-      </c>
-      <c r="M9" t="s">
-        <v>22</v>
-      </c>
-      <c r="N9" t="s">
-        <v>22</v>
-      </c>
-      <c r="O9" t="s">
+      <c r="B10" t="s">
         <v>76</v>
       </c>
-    </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
+      <c r="C10" t="s">
         <v>77</v>
       </c>
-      <c r="B10" t="s">
+      <c r="D10" t="s">
+        <v>18</v>
+      </c>
+      <c r="E10" t="s">
+        <v>18</v>
+      </c>
+      <c r="F10" t="s">
+        <v>29</v>
+      </c>
+      <c r="G10" t="s">
         <v>78</v>
       </c>
-      <c r="C10" t="s">
+      <c r="H10" t="s">
+        <v>30</v>
+      </c>
+      <c r="I10" t="s">
+        <v>22</v>
+      </c>
+      <c r="J10" t="s">
         <v>79</v>
       </c>
-      <c r="D10" t="s">
-        <v>18</v>
-      </c>
-      <c r="E10" t="s">
-        <v>18</v>
-      </c>
-      <c r="F10" t="s">
-        <v>19</v>
-      </c>
-      <c r="G10" t="s">
-        <v>20</v>
-      </c>
-      <c r="H10" t="s">
-        <v>21</v>
-      </c>
-      <c r="I10" t="s">
+      <c r="K10" t="s">
+        <v>32</v>
+      </c>
+      <c r="L10" t="s">
+        <v>22</v>
+      </c>
+      <c r="M10" t="s">
+        <v>22</v>
+      </c>
+      <c r="N10" t="s">
         <v>80</v>
       </c>
-      <c r="J10" t="s">
+      <c r="O10" t="s">
         <v>81</v>
       </c>
-      <c r="K10" t="s">
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
         <v>82</v>
       </c>
-      <c r="L10" t="s">
-        <v>22</v>
-      </c>
-      <c r="M10" t="s">
-        <v>22</v>
-      </c>
-      <c r="N10" t="s">
-        <v>22</v>
-      </c>
-      <c r="O10" t="s">
+      <c r="B11" t="s">
         <v>83</v>
       </c>
-    </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
+      <c r="C11" t="s">
         <v>84</v>
       </c>
-      <c r="B11" t="s">
-        <v>42</v>
-      </c>
-      <c r="C11" t="s">
-        <v>43</v>
-      </c>
       <c r="D11" t="s">
         <v>18</v>
       </c>
@@ -1907,13 +1826,13 @@
         <v>18</v>
       </c>
       <c r="F11" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G11" t="s">
         <v>20</v>
       </c>
       <c r="H11" t="s">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="I11" t="s">
         <v>22</v>
@@ -1928,7 +1847,7 @@
         <v>22</v>
       </c>
       <c r="M11" t="s">
-        <v>22</v>
+        <v>69</v>
       </c>
       <c r="N11" t="s">
         <v>22</v>
@@ -1937,7 +1856,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>88</v>
       </c>
@@ -1951,48 +1870,48 @@
         <v>18</v>
       </c>
       <c r="E12" t="s">
+        <v>18</v>
+      </c>
+      <c r="F12" t="s">
         <v>91</v>
-      </c>
-      <c r="F12" t="s">
-        <v>92</v>
       </c>
       <c r="G12" t="s">
         <v>20</v>
       </c>
       <c r="H12" t="s">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="I12" t="s">
         <v>22</v>
       </c>
       <c r="J12" t="s">
+        <v>92</v>
+      </c>
+      <c r="K12" t="s">
         <v>93</v>
       </c>
-      <c r="K12" t="s">
+      <c r="L12" t="s">
+        <v>22</v>
+      </c>
+      <c r="M12" t="s">
+        <v>22</v>
+      </c>
+      <c r="N12" t="s">
+        <v>22</v>
+      </c>
+      <c r="O12" t="s">
         <v>94</v>
       </c>
-      <c r="L12" t="s">
-        <v>22</v>
-      </c>
-      <c r="M12" t="s">
-        <v>22</v>
-      </c>
-      <c r="N12" t="s">
-        <v>22</v>
-      </c>
-      <c r="O12" t="s">
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
         <v>95</v>
       </c>
-    </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
+      <c r="B13" t="s">
         <v>96</v>
       </c>
-      <c r="B13" t="s">
-        <v>49</v>
-      </c>
       <c r="C13" t="s">
-        <v>50</v>
+        <v>97</v>
       </c>
       <c r="D13" t="s">
         <v>18</v>
@@ -2001,22 +1920,22 @@
         <v>18</v>
       </c>
       <c r="F13" t="s">
-        <v>19</v>
+        <v>53</v>
       </c>
       <c r="G13" t="s">
-        <v>20</v>
+        <v>38</v>
       </c>
       <c r="H13" t="s">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="I13" t="s">
         <v>22</v>
       </c>
       <c r="J13" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="K13" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="L13" t="s">
         <v>22</v>
@@ -2028,18 +1947,18 @@
         <v>22</v>
       </c>
       <c r="O13" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B14" t="s">
-        <v>58</v>
+        <v>102</v>
       </c>
       <c r="C14" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D14" t="s">
         <v>18</v>
@@ -2048,45 +1967,45 @@
         <v>18</v>
       </c>
       <c r="F14" t="s">
-        <v>35</v>
+        <v>53</v>
       </c>
       <c r="G14" t="s">
         <v>20</v>
       </c>
       <c r="H14" t="s">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="I14" t="s">
-        <v>22</v>
+        <v>104</v>
       </c>
       <c r="J14" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="K14" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="L14" t="s">
         <v>22</v>
       </c>
       <c r="M14" t="s">
-        <v>39</v>
+        <v>22</v>
       </c>
       <c r="N14" t="s">
         <v>22</v>
       </c>
       <c r="O14" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="B15" t="s">
-        <v>106</v>
+        <v>44</v>
       </c>
       <c r="C15" t="s">
-        <v>107</v>
+        <v>45</v>
       </c>
       <c r="D15" t="s">
         <v>18</v>
@@ -2095,107 +2014,107 @@
         <v>18</v>
       </c>
       <c r="F15" t="s">
-        <v>35</v>
+        <v>91</v>
       </c>
       <c r="G15" t="s">
         <v>20</v>
       </c>
       <c r="H15" t="s">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="I15" t="s">
         <v>22</v>
       </c>
       <c r="J15" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="K15" t="s">
-        <v>61</v>
+        <v>110</v>
       </c>
       <c r="L15" t="s">
         <v>22</v>
       </c>
       <c r="M15" t="s">
-        <v>39</v>
+        <v>22</v>
       </c>
       <c r="N15" t="s">
         <v>22</v>
       </c>
       <c r="O15" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.25">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="B16" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="C16" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="D16" t="s">
         <v>18</v>
       </c>
       <c r="E16" t="s">
-        <v>18</v>
+        <v>115</v>
       </c>
       <c r="F16" t="s">
-        <v>35</v>
+        <v>19</v>
       </c>
       <c r="G16" t="s">
         <v>20</v>
       </c>
       <c r="H16" t="s">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="I16" t="s">
         <v>22</v>
       </c>
       <c r="J16" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="K16" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="L16" t="s">
         <v>22</v>
       </c>
       <c r="M16" t="s">
-        <v>39</v>
+        <v>22</v>
       </c>
       <c r="N16" t="s">
         <v>22</v>
       </c>
       <c r="O16" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.25">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="17" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="B17" t="s">
-        <v>117</v>
+        <v>76</v>
       </c>
       <c r="C17" t="s">
-        <v>118</v>
+        <v>77</v>
       </c>
       <c r="D17" t="s">
         <v>18</v>
       </c>
       <c r="E17" t="s">
-        <v>91</v>
+        <v>18</v>
       </c>
       <c r="F17" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="G17" t="s">
-        <v>119</v>
+        <v>20</v>
       </c>
       <c r="H17" t="s">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="I17" t="s">
         <v>22</v>
@@ -2213,22 +2132,22 @@
         <v>22</v>
       </c>
       <c r="N17" t="s">
+        <v>22</v>
+      </c>
+      <c r="O17" t="s">
         <v>122</v>
       </c>
-      <c r="O17" t="s">
+    </row>
+    <row r="18" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
         <v>123</v>
       </c>
-    </row>
-    <row r="18" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
+      <c r="B18" t="s">
+        <v>83</v>
+      </c>
+      <c r="C18" t="s">
         <v>124</v>
       </c>
-      <c r="B18" t="s">
-        <v>125</v>
-      </c>
-      <c r="C18" t="s">
-        <v>28</v>
-      </c>
       <c r="D18" t="s">
         <v>18</v>
       </c>
@@ -2236,45 +2155,45 @@
         <v>18</v>
       </c>
       <c r="F18" t="s">
-        <v>35</v>
+        <v>65</v>
       </c>
       <c r="G18" t="s">
         <v>20</v>
       </c>
       <c r="H18" t="s">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="I18" t="s">
         <v>22</v>
       </c>
       <c r="J18" t="s">
+        <v>125</v>
+      </c>
+      <c r="K18" t="s">
         <v>126</v>
       </c>
-      <c r="K18" t="s">
+      <c r="L18" t="s">
+        <v>22</v>
+      </c>
+      <c r="M18" t="s">
+        <v>69</v>
+      </c>
+      <c r="N18" t="s">
+        <v>22</v>
+      </c>
+      <c r="O18" t="s">
         <v>127</v>
       </c>
-      <c r="L18" t="s">
-        <v>22</v>
-      </c>
-      <c r="M18" t="s">
-        <v>39</v>
-      </c>
-      <c r="N18" t="s">
-        <v>22</v>
-      </c>
-      <c r="O18" t="s">
+    </row>
+    <row r="19" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
         <v>128</v>
       </c>
-    </row>
-    <row r="19" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
+      <c r="B19" t="s">
         <v>129</v>
       </c>
-      <c r="B19" t="s">
-        <v>27</v>
-      </c>
       <c r="C19" t="s">
-        <v>28</v>
+        <v>130</v>
       </c>
       <c r="D19" t="s">
         <v>18</v>
@@ -2283,45 +2202,45 @@
         <v>18</v>
       </c>
       <c r="F19" t="s">
-        <v>19</v>
+        <v>65</v>
       </c>
       <c r="G19" t="s">
         <v>20</v>
       </c>
       <c r="H19" t="s">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="I19" t="s">
         <v>22</v>
       </c>
       <c r="J19" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="K19" t="s">
-        <v>98</v>
+        <v>86</v>
       </c>
       <c r="L19" t="s">
         <v>22</v>
       </c>
       <c r="M19" t="s">
-        <v>22</v>
+        <v>69</v>
       </c>
       <c r="N19" t="s">
         <v>22</v>
       </c>
       <c r="O19" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="20" spans="1:15" x14ac:dyDescent="0.25">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="20" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B20" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C20" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="D20" t="s">
         <v>18</v>
@@ -2330,69 +2249,69 @@
         <v>18</v>
       </c>
       <c r="F20" t="s">
-        <v>19</v>
+        <v>65</v>
       </c>
       <c r="G20" t="s">
-        <v>73</v>
+        <v>20</v>
       </c>
       <c r="H20" t="s">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="I20" t="s">
         <v>22</v>
       </c>
       <c r="J20" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="K20" t="s">
-        <v>94</v>
+        <v>137</v>
       </c>
       <c r="L20" t="s">
         <v>22</v>
       </c>
       <c r="M20" t="s">
-        <v>22</v>
+        <v>69</v>
       </c>
       <c r="N20" t="s">
         <v>22</v>
       </c>
       <c r="O20" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="21" spans="1:15" x14ac:dyDescent="0.25">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="21" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="B21" t="s">
-        <v>89</v>
+        <v>140</v>
       </c>
       <c r="C21" t="s">
-        <v>90</v>
+        <v>37</v>
       </c>
       <c r="D21" t="s">
         <v>18</v>
       </c>
       <c r="E21" t="s">
-        <v>91</v>
+        <v>115</v>
       </c>
       <c r="F21" t="s">
-        <v>66</v>
+        <v>29</v>
       </c>
       <c r="G21" t="s">
-        <v>20</v>
+        <v>141</v>
       </c>
       <c r="H21" t="s">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="I21" t="s">
         <v>22</v>
       </c>
       <c r="J21" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="K21" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="L21" t="s">
         <v>22</v>
@@ -2401,65 +2320,65 @@
         <v>22</v>
       </c>
       <c r="N21" t="s">
-        <v>22</v>
+        <v>144</v>
       </c>
       <c r="O21" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="22" spans="1:15" x14ac:dyDescent="0.25">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="22" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="B22" t="s">
-        <v>89</v>
+        <v>147</v>
       </c>
       <c r="C22" t="s">
-        <v>90</v>
+        <v>59</v>
       </c>
       <c r="D22" t="s">
         <v>18</v>
       </c>
       <c r="E22" t="s">
-        <v>91</v>
+        <v>18</v>
       </c>
       <c r="F22" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G22" t="s">
         <v>20</v>
       </c>
       <c r="H22" t="s">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="I22" t="s">
         <v>22</v>
       </c>
       <c r="J22" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="K22" t="s">
-        <v>68</v>
+        <v>149</v>
       </c>
       <c r="L22" t="s">
         <v>22</v>
       </c>
       <c r="M22" t="s">
-        <v>22</v>
+        <v>69</v>
       </c>
       <c r="N22" t="s">
         <v>22</v>
       </c>
       <c r="O22" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="23" spans="1:15" x14ac:dyDescent="0.25">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="23" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>144</v>
+        <v>151</v>
       </c>
       <c r="B23" t="s">
-        <v>145</v>
+        <v>58</v>
       </c>
       <c r="C23" t="s">
         <v>59</v>
@@ -2471,445 +2390,445 @@
         <v>18</v>
       </c>
       <c r="F23" t="s">
-        <v>35</v>
+        <v>53</v>
       </c>
       <c r="G23" t="s">
-        <v>146</v>
+        <v>20</v>
       </c>
       <c r="H23" t="s">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="I23" t="s">
         <v>22</v>
       </c>
       <c r="J23" t="s">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="K23" t="s">
-        <v>148</v>
+        <v>121</v>
       </c>
       <c r="L23" t="s">
         <v>22</v>
       </c>
       <c r="M23" t="s">
-        <v>39</v>
+        <v>22</v>
       </c>
       <c r="N23" t="s">
         <v>22</v>
       </c>
       <c r="O23" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="24" spans="1:15" x14ac:dyDescent="0.25">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="24" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="B24" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="C24" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="D24" t="s">
-        <v>153</v>
+        <v>18</v>
       </c>
       <c r="E24" t="s">
+        <v>18</v>
+      </c>
+      <c r="F24" t="s">
+        <v>53</v>
+      </c>
+      <c r="G24" t="s">
+        <v>38</v>
+      </c>
+      <c r="H24" t="s">
+        <v>30</v>
+      </c>
+      <c r="I24" t="s">
+        <v>22</v>
+      </c>
+      <c r="J24" t="s">
+        <v>157</v>
+      </c>
+      <c r="K24" t="s">
+        <v>117</v>
+      </c>
+      <c r="L24" t="s">
+        <v>22</v>
+      </c>
+      <c r="M24" t="s">
+        <v>22</v>
+      </c>
+      <c r="N24" t="s">
+        <v>22</v>
+      </c>
+      <c r="O24" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="25" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
+        <v>159</v>
+      </c>
+      <c r="B25" t="s">
+        <v>113</v>
+      </c>
+      <c r="C25" t="s">
+        <v>114</v>
+      </c>
+      <c r="D25" t="s">
+        <v>18</v>
+      </c>
+      <c r="E25" t="s">
+        <v>115</v>
+      </c>
+      <c r="F25" t="s">
         <v>91</v>
       </c>
-      <c r="F24" t="s">
-        <v>35</v>
-      </c>
-      <c r="G24" t="s">
+      <c r="G25" t="s">
         <v>20</v>
       </c>
-      <c r="H24" t="s">
-        <v>21</v>
-      </c>
-      <c r="I24" t="s">
-        <v>22</v>
-      </c>
-      <c r="J24" t="s">
-        <v>154</v>
-      </c>
-      <c r="K24" t="s">
-        <v>155</v>
-      </c>
-      <c r="L24" t="s">
-        <v>22</v>
-      </c>
-      <c r="M24" t="s">
-        <v>39</v>
-      </c>
-      <c r="N24" t="s">
-        <v>22</v>
-      </c>
-      <c r="O24" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="25" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
-        <v>157</v>
-      </c>
-      <c r="B25" t="s">
-        <v>158</v>
-      </c>
-      <c r="C25" t="s">
-        <v>159</v>
-      </c>
-      <c r="D25" t="s">
-        <v>18</v>
-      </c>
-      <c r="E25" t="s">
-        <v>18</v>
-      </c>
-      <c r="F25" t="s">
-        <v>51</v>
-      </c>
-      <c r="G25" t="s">
+      <c r="H25" t="s">
+        <v>30</v>
+      </c>
+      <c r="I25" t="s">
+        <v>22</v>
+      </c>
+      <c r="J25" t="s">
         <v>160</v>
       </c>
-      <c r="H25" t="s">
-        <v>21</v>
-      </c>
-      <c r="I25" t="s">
-        <v>22</v>
-      </c>
-      <c r="J25" t="s">
+      <c r="K25" t="s">
         <v>161</v>
       </c>
-      <c r="K25" t="s">
+      <c r="L25" t="s">
+        <v>22</v>
+      </c>
+      <c r="M25" t="s">
+        <v>22</v>
+      </c>
+      <c r="N25" t="s">
+        <v>22</v>
+      </c>
+      <c r="O25" t="s">
         <v>162</v>
       </c>
-      <c r="L25" t="s">
-        <v>22</v>
-      </c>
-      <c r="M25" t="s">
-        <v>22</v>
-      </c>
-      <c r="N25" t="s">
+    </row>
+    <row r="26" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
         <v>163</v>
       </c>
-      <c r="O25" t="s">
+      <c r="B26" t="s">
+        <v>113</v>
+      </c>
+      <c r="C26" t="s">
+        <v>114</v>
+      </c>
+      <c r="D26" t="s">
+        <v>18</v>
+      </c>
+      <c r="E26" t="s">
+        <v>115</v>
+      </c>
+      <c r="F26" t="s">
+        <v>91</v>
+      </c>
+      <c r="G26" t="s">
+        <v>20</v>
+      </c>
+      <c r="H26" t="s">
+        <v>30</v>
+      </c>
+      <c r="I26" t="s">
+        <v>22</v>
+      </c>
+      <c r="J26" t="s">
         <v>164</v>
       </c>
-    </row>
-    <row r="26" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A26" t="s">
+      <c r="K26" t="s">
+        <v>93</v>
+      </c>
+      <c r="L26" t="s">
+        <v>22</v>
+      </c>
+      <c r="M26" t="s">
+        <v>22</v>
+      </c>
+      <c r="N26" t="s">
+        <v>22</v>
+      </c>
+      <c r="O26" t="s">
         <v>165</v>
       </c>
-      <c r="B26" t="s">
-        <v>89</v>
-      </c>
-      <c r="C26" t="s">
-        <v>90</v>
-      </c>
-      <c r="D26" t="s">
-        <v>18</v>
-      </c>
-      <c r="E26" t="s">
+    </row>
+    <row r="27" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A27" t="s">
+        <v>166</v>
+      </c>
+      <c r="B27" t="s">
+        <v>167</v>
+      </c>
+      <c r="C27" t="s">
+        <v>84</v>
+      </c>
+      <c r="D27" t="s">
+        <v>18</v>
+      </c>
+      <c r="E27" t="s">
+        <v>18</v>
+      </c>
+      <c r="F27" t="s">
+        <v>65</v>
+      </c>
+      <c r="G27" t="s">
+        <v>168</v>
+      </c>
+      <c r="H27" t="s">
+        <v>30</v>
+      </c>
+      <c r="I27" t="s">
+        <v>22</v>
+      </c>
+      <c r="J27" t="s">
+        <v>169</v>
+      </c>
+      <c r="K27" t="s">
+        <v>170</v>
+      </c>
+      <c r="L27" t="s">
+        <v>22</v>
+      </c>
+      <c r="M27" t="s">
+        <v>69</v>
+      </c>
+      <c r="N27" t="s">
+        <v>22</v>
+      </c>
+      <c r="O27" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="28" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A28" t="s">
+        <v>172</v>
+      </c>
+      <c r="B28" t="s">
+        <v>173</v>
+      </c>
+      <c r="C28" t="s">
+        <v>174</v>
+      </c>
+      <c r="D28" t="s">
+        <v>175</v>
+      </c>
+      <c r="E28" t="s">
+        <v>115</v>
+      </c>
+      <c r="F28" t="s">
+        <v>65</v>
+      </c>
+      <c r="G28" t="s">
+        <v>20</v>
+      </c>
+      <c r="H28" t="s">
+        <v>30</v>
+      </c>
+      <c r="I28" t="s">
+        <v>22</v>
+      </c>
+      <c r="J28" t="s">
+        <v>176</v>
+      </c>
+      <c r="K28" t="s">
+        <v>177</v>
+      </c>
+      <c r="L28" t="s">
+        <v>22</v>
+      </c>
+      <c r="M28" t="s">
+        <v>69</v>
+      </c>
+      <c r="N28" t="s">
+        <v>22</v>
+      </c>
+      <c r="O28" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="29" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A29" t="s">
+        <v>179</v>
+      </c>
+      <c r="B29" t="s">
+        <v>180</v>
+      </c>
+      <c r="C29" t="s">
+        <v>181</v>
+      </c>
+      <c r="D29" t="s">
+        <v>18</v>
+      </c>
+      <c r="E29" t="s">
+        <v>18</v>
+      </c>
+      <c r="F29" t="s">
+        <v>29</v>
+      </c>
+      <c r="G29" t="s">
+        <v>182</v>
+      </c>
+      <c r="H29" t="s">
+        <v>30</v>
+      </c>
+      <c r="I29" t="s">
+        <v>22</v>
+      </c>
+      <c r="J29" t="s">
+        <v>183</v>
+      </c>
+      <c r="K29" t="s">
+        <v>184</v>
+      </c>
+      <c r="L29" t="s">
+        <v>22</v>
+      </c>
+      <c r="M29" t="s">
+        <v>22</v>
+      </c>
+      <c r="N29" t="s">
+        <v>185</v>
+      </c>
+      <c r="O29" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="30" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A30" t="s">
+        <v>187</v>
+      </c>
+      <c r="B30" t="s">
+        <v>113</v>
+      </c>
+      <c r="C30" t="s">
+        <v>114</v>
+      </c>
+      <c r="D30" t="s">
+        <v>18</v>
+      </c>
+      <c r="E30" t="s">
+        <v>115</v>
+      </c>
+      <c r="F30" t="s">
+        <v>19</v>
+      </c>
+      <c r="G30" t="s">
+        <v>168</v>
+      </c>
+      <c r="H30" t="s">
+        <v>30</v>
+      </c>
+      <c r="I30" t="s">
+        <v>22</v>
+      </c>
+      <c r="J30" t="s">
+        <v>188</v>
+      </c>
+      <c r="K30" t="s">
+        <v>189</v>
+      </c>
+      <c r="L30" t="s">
+        <v>22</v>
+      </c>
+      <c r="M30" t="s">
+        <v>22</v>
+      </c>
+      <c r="N30" t="s">
+        <v>22</v>
+      </c>
+      <c r="O30" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="31" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A31" t="s">
+        <v>191</v>
+      </c>
+      <c r="B31" t="s">
+        <v>192</v>
+      </c>
+      <c r="C31" t="s">
+        <v>193</v>
+      </c>
+      <c r="D31" t="s">
+        <v>18</v>
+      </c>
+      <c r="E31" t="s">
+        <v>18</v>
+      </c>
+      <c r="F31" t="s">
         <v>91</v>
-      </c>
-      <c r="F26" t="s">
-        <v>92</v>
-      </c>
-      <c r="G26" t="s">
-        <v>146</v>
-      </c>
-      <c r="H26" t="s">
-        <v>21</v>
-      </c>
-      <c r="I26" t="s">
-        <v>22</v>
-      </c>
-      <c r="J26" t="s">
-        <v>166</v>
-      </c>
-      <c r="K26" t="s">
-        <v>167</v>
-      </c>
-      <c r="L26" t="s">
-        <v>22</v>
-      </c>
-      <c r="M26" t="s">
-        <v>22</v>
-      </c>
-      <c r="N26" t="s">
-        <v>22</v>
-      </c>
-      <c r="O26" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="27" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
-        <v>169</v>
-      </c>
-      <c r="B27" t="s">
-        <v>170</v>
-      </c>
-      <c r="C27" t="s">
-        <v>171</v>
-      </c>
-      <c r="D27" t="s">
-        <v>18</v>
-      </c>
-      <c r="E27" t="s">
-        <v>18</v>
-      </c>
-      <c r="F27" t="s">
-        <v>66</v>
-      </c>
-      <c r="G27" t="s">
-        <v>20</v>
-      </c>
-      <c r="H27" t="s">
-        <v>21</v>
-      </c>
-      <c r="I27" t="s">
-        <v>172</v>
-      </c>
-      <c r="J27" t="s">
-        <v>173</v>
-      </c>
-      <c r="K27" t="s">
-        <v>174</v>
-      </c>
-      <c r="L27" t="s">
-        <v>22</v>
-      </c>
-      <c r="M27" t="s">
-        <v>22</v>
-      </c>
-      <c r="N27" t="s">
-        <v>22</v>
-      </c>
-      <c r="O27" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="28" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A28" t="s">
-        <v>176</v>
-      </c>
-      <c r="B28" t="s">
-        <v>117</v>
-      </c>
-      <c r="C28" t="s">
-        <v>177</v>
-      </c>
-      <c r="D28" t="s">
-        <v>18</v>
-      </c>
-      <c r="E28" t="s">
-        <v>91</v>
-      </c>
-      <c r="F28" t="s">
-        <v>66</v>
-      </c>
-      <c r="G28" t="s">
-        <v>178</v>
-      </c>
-      <c r="H28" t="s">
-        <v>21</v>
-      </c>
-      <c r="I28" t="s">
-        <v>22</v>
-      </c>
-      <c r="J28" t="s">
-        <v>179</v>
-      </c>
-      <c r="K28" t="s">
-        <v>139</v>
-      </c>
-      <c r="L28" t="s">
-        <v>22</v>
-      </c>
-      <c r="M28" t="s">
-        <v>22</v>
-      </c>
-      <c r="N28" t="s">
-        <v>22</v>
-      </c>
-      <c r="O28" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="29" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A29" t="s">
-        <v>181</v>
-      </c>
-      <c r="B29" t="s">
-        <v>151</v>
-      </c>
-      <c r="C29" t="s">
-        <v>152</v>
-      </c>
-      <c r="D29" t="s">
-        <v>153</v>
-      </c>
-      <c r="E29" t="s">
-        <v>91</v>
-      </c>
-      <c r="F29" t="s">
-        <v>92</v>
-      </c>
-      <c r="G29" t="s">
-        <v>20</v>
-      </c>
-      <c r="H29" t="s">
-        <v>21</v>
-      </c>
-      <c r="I29" t="s">
-        <v>172</v>
-      </c>
-      <c r="J29" t="s">
-        <v>182</v>
-      </c>
-      <c r="K29" t="s">
-        <v>183</v>
-      </c>
-      <c r="L29" t="s">
-        <v>22</v>
-      </c>
-      <c r="M29" t="s">
-        <v>22</v>
-      </c>
-      <c r="N29" t="s">
-        <v>22</v>
-      </c>
-      <c r="O29" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="30" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A30" t="s">
-        <v>185</v>
-      </c>
-      <c r="B30" t="s">
-        <v>145</v>
-      </c>
-      <c r="C30" t="s">
-        <v>59</v>
-      </c>
-      <c r="D30" t="s">
-        <v>18</v>
-      </c>
-      <c r="E30" t="s">
-        <v>18</v>
-      </c>
-      <c r="F30" t="s">
-        <v>35</v>
-      </c>
-      <c r="G30" t="s">
-        <v>20</v>
-      </c>
-      <c r="H30" t="s">
-        <v>21</v>
-      </c>
-      <c r="I30" t="s">
-        <v>22</v>
-      </c>
-      <c r="J30" t="s">
-        <v>186</v>
-      </c>
-      <c r="K30" t="s">
-        <v>187</v>
-      </c>
-      <c r="L30" t="s">
-        <v>22</v>
-      </c>
-      <c r="M30" t="s">
-        <v>39</v>
-      </c>
-      <c r="N30" t="s">
-        <v>22</v>
-      </c>
-      <c r="O30" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="31" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A31" t="s">
-        <v>189</v>
-      </c>
-      <c r="B31" t="s">
-        <v>111</v>
-      </c>
-      <c r="C31" t="s">
-        <v>112</v>
-      </c>
-      <c r="D31" t="s">
-        <v>18</v>
-      </c>
-      <c r="E31" t="s">
-        <v>18</v>
-      </c>
-      <c r="F31" t="s">
-        <v>35</v>
       </c>
       <c r="G31" t="s">
         <v>20</v>
       </c>
       <c r="H31" t="s">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="I31" t="s">
-        <v>80</v>
+        <v>194</v>
       </c>
       <c r="J31" t="s">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="K31" t="s">
-        <v>191</v>
+        <v>196</v>
       </c>
       <c r="L31" t="s">
         <v>22</v>
       </c>
       <c r="M31" t="s">
-        <v>39</v>
+        <v>22</v>
       </c>
       <c r="N31" t="s">
         <v>22</v>
       </c>
       <c r="O31" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="32" spans="1:15" x14ac:dyDescent="0.25">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="32" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>193</v>
+        <v>198</v>
       </c>
       <c r="B32" t="s">
-        <v>64</v>
+        <v>140</v>
       </c>
       <c r="C32" t="s">
-        <v>65</v>
+        <v>199</v>
       </c>
       <c r="D32" t="s">
         <v>18</v>
       </c>
       <c r="E32" t="s">
-        <v>18</v>
+        <v>115</v>
       </c>
       <c r="F32" t="s">
-        <v>51</v>
+        <v>91</v>
       </c>
       <c r="G32" t="s">
-        <v>20</v>
+        <v>200</v>
       </c>
       <c r="H32" t="s">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="I32" t="s">
-        <v>80</v>
+        <v>22</v>
       </c>
       <c r="J32" t="s">
-        <v>194</v>
+        <v>201</v>
       </c>
       <c r="K32" t="s">
-        <v>39</v>
+        <v>161</v>
       </c>
       <c r="L32" t="s">
         <v>22</v>
@@ -2918,45 +2837,45 @@
         <v>22</v>
       </c>
       <c r="N32" t="s">
-        <v>195</v>
+        <v>22</v>
       </c>
       <c r="O32" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="33" spans="1:15" x14ac:dyDescent="0.25">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="33" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>197</v>
+        <v>203</v>
       </c>
       <c r="B33" t="s">
-        <v>158</v>
+        <v>173</v>
       </c>
       <c r="C33" t="s">
-        <v>159</v>
+        <v>174</v>
       </c>
       <c r="D33" t="s">
-        <v>18</v>
+        <v>175</v>
       </c>
       <c r="E33" t="s">
-        <v>18</v>
+        <v>115</v>
       </c>
       <c r="F33" t="s">
         <v>19</v>
       </c>
       <c r="G33" t="s">
-        <v>73</v>
+        <v>20</v>
       </c>
       <c r="H33" t="s">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="I33" t="s">
-        <v>80</v>
+        <v>194</v>
       </c>
       <c r="J33" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="K33" t="s">
-        <v>199</v>
+        <v>205</v>
       </c>
       <c r="L33" t="s">
         <v>22</v>
@@ -2968,18 +2887,18 @@
         <v>22</v>
       </c>
       <c r="O33" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="34" spans="1:15" x14ac:dyDescent="0.25">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="34" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>201</v>
+        <v>207</v>
       </c>
       <c r="B34" t="s">
-        <v>202</v>
+        <v>167</v>
       </c>
       <c r="C34" t="s">
-        <v>203</v>
+        <v>84</v>
       </c>
       <c r="D34" t="s">
         <v>18</v>
@@ -2988,45 +2907,45 @@
         <v>18</v>
       </c>
       <c r="F34" t="s">
-        <v>51</v>
+        <v>65</v>
       </c>
       <c r="G34" t="s">
-        <v>204</v>
+        <v>20</v>
       </c>
       <c r="H34" t="s">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="I34" t="s">
-        <v>80</v>
+        <v>22</v>
       </c>
       <c r="J34" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="K34" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="L34" t="s">
         <v>22</v>
       </c>
       <c r="M34" t="s">
-        <v>22</v>
+        <v>69</v>
       </c>
       <c r="N34" t="s">
-        <v>207</v>
+        <v>22</v>
       </c>
       <c r="O34" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="35" spans="1:15" x14ac:dyDescent="0.25">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="35" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="B35" t="s">
-        <v>202</v>
+        <v>134</v>
       </c>
       <c r="C35" t="s">
-        <v>203</v>
+        <v>135</v>
       </c>
       <c r="D35" t="s">
         <v>18</v>
@@ -3035,398 +2954,398 @@
         <v>18</v>
       </c>
       <c r="F35" t="s">
-        <v>51</v>
+        <v>65</v>
       </c>
       <c r="G35" t="s">
-        <v>210</v>
+        <v>20</v>
       </c>
       <c r="H35" t="s">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="I35" t="s">
-        <v>80</v>
+        <v>104</v>
       </c>
       <c r="J35" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="K35" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="L35" t="s">
         <v>22</v>
       </c>
       <c r="M35" t="s">
-        <v>22</v>
+        <v>69</v>
       </c>
       <c r="N35" t="s">
-        <v>213</v>
+        <v>22</v>
       </c>
       <c r="O35" t="s">
         <v>214</v>
       </c>
     </row>
-    <row r="36" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>215</v>
       </c>
       <c r="B36" t="s">
+        <v>89</v>
+      </c>
+      <c r="C36" t="s">
+        <v>90</v>
+      </c>
+      <c r="D36" t="s">
+        <v>18</v>
+      </c>
+      <c r="E36" t="s">
+        <v>18</v>
+      </c>
+      <c r="F36" t="s">
+        <v>29</v>
+      </c>
+      <c r="G36" t="s">
+        <v>20</v>
+      </c>
+      <c r="H36" t="s">
+        <v>30</v>
+      </c>
+      <c r="I36" t="s">
+        <v>104</v>
+      </c>
+      <c r="J36" t="s">
         <v>216</v>
       </c>
-      <c r="C36" t="s">
-        <v>171</v>
-      </c>
-      <c r="D36" t="s">
-        <v>18</v>
-      </c>
-      <c r="E36" t="s">
-        <v>18</v>
-      </c>
-      <c r="F36" t="s">
-        <v>51</v>
-      </c>
-      <c r="G36" t="s">
+      <c r="K36" t="s">
+        <v>69</v>
+      </c>
+      <c r="L36" t="s">
+        <v>22</v>
+      </c>
+      <c r="M36" t="s">
+        <v>22</v>
+      </c>
+      <c r="N36" t="s">
         <v>217</v>
       </c>
-      <c r="H36" t="s">
-        <v>21</v>
-      </c>
-      <c r="I36" t="s">
-        <v>80</v>
-      </c>
-      <c r="J36" t="s">
+      <c r="O36" t="s">
         <v>218</v>
       </c>
-      <c r="K36" t="s">
+    </row>
+    <row r="37" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A37" t="s">
         <v>219</v>
       </c>
-      <c r="L36" t="s">
-        <v>22</v>
-      </c>
-      <c r="M36" t="s">
-        <v>22</v>
-      </c>
-      <c r="N36" t="s">
+      <c r="B37" t="s">
+        <v>180</v>
+      </c>
+      <c r="C37" t="s">
+        <v>181</v>
+      </c>
+      <c r="D37" t="s">
+        <v>18</v>
+      </c>
+      <c r="E37" t="s">
+        <v>18</v>
+      </c>
+      <c r="F37" t="s">
+        <v>53</v>
+      </c>
+      <c r="G37" t="s">
+        <v>38</v>
+      </c>
+      <c r="H37" t="s">
+        <v>30</v>
+      </c>
+      <c r="I37" t="s">
+        <v>104</v>
+      </c>
+      <c r="J37" t="s">
         <v>220</v>
       </c>
-      <c r="O36" t="s">
+      <c r="K37" t="s">
         <v>221</v>
       </c>
-    </row>
-    <row r="37" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A37" t="s">
+      <c r="L37" t="s">
+        <v>22</v>
+      </c>
+      <c r="M37" t="s">
+        <v>22</v>
+      </c>
+      <c r="N37" t="s">
+        <v>22</v>
+      </c>
+      <c r="O37" t="s">
         <v>222</v>
       </c>
-      <c r="B37" t="s">
+    </row>
+    <row r="38" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A38" t="s">
         <v>223</v>
       </c>
-      <c r="C37" t="s">
-        <v>101</v>
-      </c>
-      <c r="D37" t="s">
-        <v>18</v>
-      </c>
-      <c r="E37" t="s">
-        <v>18</v>
-      </c>
-      <c r="F37" t="s">
-        <v>51</v>
-      </c>
-      <c r="G37" t="s">
-        <v>73</v>
-      </c>
-      <c r="H37" t="s">
-        <v>21</v>
-      </c>
-      <c r="I37" t="s">
-        <v>80</v>
-      </c>
-      <c r="J37" t="s">
+      <c r="B38" t="s">
         <v>224</v>
       </c>
-      <c r="K37" t="s">
+      <c r="C38" t="s">
         <v>225</v>
       </c>
-      <c r="L37" t="s">
-        <v>22</v>
-      </c>
-      <c r="M37" t="s">
-        <v>22</v>
-      </c>
-      <c r="N37" t="s">
+      <c r="D38" t="s">
+        <v>18</v>
+      </c>
+      <c r="E38" t="s">
+        <v>18</v>
+      </c>
+      <c r="F38" t="s">
+        <v>29</v>
+      </c>
+      <c r="G38" t="s">
         <v>226</v>
       </c>
-      <c r="O37" t="s">
+      <c r="H38" t="s">
+        <v>30</v>
+      </c>
+      <c r="I38" t="s">
+        <v>104</v>
+      </c>
+      <c r="J38" t="s">
         <v>227</v>
       </c>
-    </row>
-    <row r="38" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A38" t="s">
+      <c r="K38" t="s">
+        <v>40</v>
+      </c>
+      <c r="L38" t="s">
+        <v>22</v>
+      </c>
+      <c r="M38" t="s">
+        <v>22</v>
+      </c>
+      <c r="N38" t="s">
         <v>228</v>
       </c>
-      <c r="B38" t="s">
+      <c r="O38" t="s">
         <v>229</v>
       </c>
-      <c r="C38" t="s">
+    </row>
+    <row r="39" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A39" t="s">
         <v>230</v>
       </c>
-      <c r="D38" t="s">
-        <v>18</v>
-      </c>
-      <c r="E38" t="s">
-        <v>18</v>
-      </c>
-      <c r="F38" t="s">
-        <v>51</v>
-      </c>
-      <c r="G38" t="s">
+      <c r="B39" t="s">
+        <v>224</v>
+      </c>
+      <c r="C39" t="s">
+        <v>225</v>
+      </c>
+      <c r="D39" t="s">
+        <v>18</v>
+      </c>
+      <c r="E39" t="s">
+        <v>18</v>
+      </c>
+      <c r="F39" t="s">
+        <v>29</v>
+      </c>
+      <c r="G39" t="s">
         <v>231</v>
       </c>
-      <c r="H38" t="s">
-        <v>21</v>
-      </c>
-      <c r="I38" t="s">
+      <c r="H39" t="s">
+        <v>30</v>
+      </c>
+      <c r="I39" t="s">
+        <v>104</v>
+      </c>
+      <c r="J39" t="s">
         <v>232</v>
       </c>
-      <c r="J38" t="s">
+      <c r="K39" t="s">
         <v>233</v>
       </c>
-      <c r="K38" t="s">
+      <c r="L39" t="s">
+        <v>22</v>
+      </c>
+      <c r="M39" t="s">
+        <v>22</v>
+      </c>
+      <c r="N39" t="s">
         <v>234</v>
       </c>
-      <c r="L38" t="s">
-        <v>22</v>
-      </c>
-      <c r="M38" t="s">
-        <v>22</v>
-      </c>
-      <c r="N38" t="s">
+      <c r="O39" t="s">
         <v>235</v>
       </c>
-      <c r="O38" t="s">
+    </row>
+    <row r="40" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A40" t="s">
         <v>236</v>
       </c>
-    </row>
-    <row r="39" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A39" t="s">
+      <c r="B40" t="s">
+        <v>27</v>
+      </c>
+      <c r="C40" t="s">
+        <v>193</v>
+      </c>
+      <c r="D40" t="s">
+        <v>18</v>
+      </c>
+      <c r="E40" t="s">
+        <v>18</v>
+      </c>
+      <c r="F40" t="s">
+        <v>29</v>
+      </c>
+      <c r="G40" t="s">
         <v>237</v>
       </c>
-      <c r="B39" t="s">
-        <v>229</v>
-      </c>
-      <c r="C39" t="s">
-        <v>230</v>
-      </c>
-      <c r="D39" t="s">
-        <v>18</v>
-      </c>
-      <c r="E39" t="s">
-        <v>18</v>
-      </c>
-      <c r="F39" t="s">
+      <c r="H40" t="s">
+        <v>30</v>
+      </c>
+      <c r="I40" t="s">
+        <v>104</v>
+      </c>
+      <c r="J40" t="s">
         <v>238</v>
       </c>
-      <c r="G39" t="s">
+      <c r="K40" t="s">
         <v>239</v>
       </c>
-      <c r="H39" t="s">
-        <v>21</v>
-      </c>
-      <c r="I39" t="s">
-        <v>232</v>
-      </c>
-      <c r="J39" t="s">
+      <c r="L40" t="s">
+        <v>22</v>
+      </c>
+      <c r="M40" t="s">
+        <v>22</v>
+      </c>
+      <c r="N40" t="s">
         <v>240</v>
       </c>
-      <c r="K39" t="s">
+      <c r="O40" t="s">
         <v>241</v>
       </c>
-      <c r="L39" t="s">
-        <v>22</v>
-      </c>
-      <c r="M39" t="s">
-        <v>22</v>
-      </c>
-      <c r="N39" t="s">
-        <v>22</v>
-      </c>
-      <c r="O39" t="s">
+    </row>
+    <row r="41" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A41" t="s">
         <v>242</v>
       </c>
-    </row>
-    <row r="40" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A40" t="s">
+      <c r="B41" t="s">
         <v>243</v>
       </c>
-      <c r="B40" t="s">
-        <v>145</v>
-      </c>
-      <c r="C40" t="s">
-        <v>59</v>
-      </c>
-      <c r="D40" t="s">
-        <v>18</v>
-      </c>
-      <c r="E40" t="s">
-        <v>18</v>
-      </c>
-      <c r="F40" t="s">
-        <v>51</v>
-      </c>
-      <c r="G40" t="s">
-        <v>160</v>
-      </c>
-      <c r="H40" t="s">
-        <v>21</v>
-      </c>
-      <c r="I40" t="s">
-        <v>80</v>
-      </c>
-      <c r="J40" t="s">
+      <c r="C41" t="s">
+        <v>124</v>
+      </c>
+      <c r="D41" t="s">
+        <v>18</v>
+      </c>
+      <c r="E41" t="s">
+        <v>18</v>
+      </c>
+      <c r="F41" t="s">
+        <v>29</v>
+      </c>
+      <c r="G41" t="s">
+        <v>38</v>
+      </c>
+      <c r="H41" t="s">
+        <v>30</v>
+      </c>
+      <c r="I41" t="s">
+        <v>104</v>
+      </c>
+      <c r="J41" t="s">
         <v>244</v>
       </c>
-      <c r="K40" t="s">
+      <c r="K41" t="s">
         <v>245</v>
       </c>
-      <c r="L40" t="s">
-        <v>22</v>
-      </c>
-      <c r="M40" t="s">
-        <v>22</v>
-      </c>
-      <c r="N40" t="s">
+      <c r="L41" t="s">
+        <v>22</v>
+      </c>
+      <c r="M41" t="s">
+        <v>22</v>
+      </c>
+      <c r="N41" t="s">
         <v>246</v>
       </c>
-      <c r="O40" t="s">
+      <c r="O41" t="s">
         <v>247</v>
       </c>
     </row>
-    <row r="41" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A41" t="s">
+    <row r="42" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A42" t="s">
         <v>248</v>
       </c>
-      <c r="B41" t="s">
-        <v>89</v>
-      </c>
-      <c r="C41" t="s">
-        <v>90</v>
-      </c>
-      <c r="D41" t="s">
-        <v>18</v>
-      </c>
-      <c r="E41" t="s">
-        <v>91</v>
-      </c>
-      <c r="F41" t="s">
-        <v>238</v>
-      </c>
-      <c r="G41" t="s">
+      <c r="B42" t="s">
         <v>249</v>
       </c>
-      <c r="H41" t="s">
-        <v>21</v>
-      </c>
-      <c r="I41" t="s">
-        <v>80</v>
-      </c>
-      <c r="J41" t="s">
+      <c r="C42" t="s">
         <v>250</v>
       </c>
-      <c r="K41" t="s">
+      <c r="D42" t="s">
+        <v>18</v>
+      </c>
+      <c r="E42" t="s">
+        <v>18</v>
+      </c>
+      <c r="F42" t="s">
+        <v>29</v>
+      </c>
+      <c r="G42" t="s">
         <v>251</v>
       </c>
-      <c r="L41" t="s">
-        <v>22</v>
-      </c>
-      <c r="M41" t="s">
-        <v>22</v>
-      </c>
-      <c r="N41" t="s">
-        <v>22</v>
-      </c>
-      <c r="O41" t="s">
+      <c r="H42" t="s">
+        <v>30</v>
+      </c>
+      <c r="I42" t="s">
         <v>252</v>
       </c>
-    </row>
-    <row r="42" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A42" t="s">
+      <c r="J42" t="s">
         <v>253</v>
       </c>
-      <c r="B42" t="s">
-        <v>89</v>
-      </c>
-      <c r="C42" t="s">
-        <v>90</v>
-      </c>
-      <c r="D42" t="s">
-        <v>18</v>
-      </c>
-      <c r="E42" t="s">
-        <v>91</v>
-      </c>
-      <c r="F42" t="s">
-        <v>35</v>
-      </c>
-      <c r="G42" t="s">
-        <v>20</v>
-      </c>
-      <c r="H42" t="s">
-        <v>21</v>
-      </c>
-      <c r="I42" t="s">
-        <v>80</v>
-      </c>
-      <c r="J42" t="s">
+      <c r="K42" t="s">
         <v>254</v>
       </c>
-      <c r="K42" t="s">
+      <c r="L42" t="s">
+        <v>22</v>
+      </c>
+      <c r="M42" t="s">
+        <v>22</v>
+      </c>
+      <c r="N42" t="s">
         <v>255</v>
-      </c>
-      <c r="L42" t="s">
-        <v>22</v>
-      </c>
-      <c r="M42" t="s">
-        <v>39</v>
-      </c>
-      <c r="N42" t="s">
-        <v>22</v>
       </c>
       <c r="O42" t="s">
         <v>256</v>
       </c>
     </row>
-    <row r="43" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>257</v>
       </c>
       <c r="B43" t="s">
+        <v>249</v>
+      </c>
+      <c r="C43" t="s">
+        <v>250</v>
+      </c>
+      <c r="D43" t="s">
+        <v>18</v>
+      </c>
+      <c r="E43" t="s">
+        <v>18</v>
+      </c>
+      <c r="F43" t="s">
         <v>258</v>
       </c>
-      <c r="C43" t="s">
-        <v>28</v>
-      </c>
-      <c r="D43" t="s">
-        <v>18</v>
-      </c>
-      <c r="E43" t="s">
+      <c r="G43" t="s">
         <v>259</v>
       </c>
-      <c r="F43" t="s">
-        <v>92</v>
-      </c>
-      <c r="G43" t="s">
-        <v>20</v>
-      </c>
       <c r="H43" t="s">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="I43" t="s">
-        <v>80</v>
+        <v>252</v>
       </c>
       <c r="J43" t="s">
         <v>260</v>
       </c>
       <c r="K43" t="s">
-        <v>255</v>
+        <v>24</v>
       </c>
       <c r="L43" t="s">
         <v>22</v>
@@ -3441,15 +3360,15 @@
         <v>261</v>
       </c>
     </row>
-    <row r="44" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>262</v>
       </c>
       <c r="B44" t="s">
-        <v>202</v>
+        <v>167</v>
       </c>
       <c r="C44" t="s">
-        <v>203</v>
+        <v>84</v>
       </c>
       <c r="D44" t="s">
         <v>18</v>
@@ -3458,22 +3377,22 @@
         <v>18</v>
       </c>
       <c r="F44" t="s">
-        <v>51</v>
+        <v>29</v>
       </c>
       <c r="G44" t="s">
-        <v>160</v>
+        <v>182</v>
       </c>
       <c r="H44" t="s">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="I44" t="s">
-        <v>80</v>
+        <v>104</v>
       </c>
       <c r="J44" t="s">
         <v>263</v>
       </c>
       <c r="K44" t="s">
-        <v>68</v>
+        <v>264</v>
       </c>
       <c r="L44" t="s">
         <v>22</v>
@@ -3482,445 +3401,445 @@
         <v>22</v>
       </c>
       <c r="N44" t="s">
-        <v>226</v>
+        <v>265</v>
       </c>
       <c r="O44" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="45" spans="1:15" x14ac:dyDescent="0.25">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="45" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="B45" t="s">
-        <v>266</v>
+        <v>113</v>
       </c>
       <c r="C45" t="s">
-        <v>267</v>
+        <v>114</v>
       </c>
       <c r="D45" t="s">
         <v>18</v>
       </c>
       <c r="E45" t="s">
-        <v>18</v>
+        <v>115</v>
       </c>
       <c r="F45" t="s">
-        <v>51</v>
+        <v>258</v>
       </c>
       <c r="G45" t="s">
-        <v>160</v>
+        <v>268</v>
       </c>
       <c r="H45" t="s">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="I45" t="s">
-        <v>80</v>
+        <v>104</v>
       </c>
       <c r="J45" t="s">
+        <v>269</v>
+      </c>
+      <c r="K45" t="s">
+        <v>48</v>
+      </c>
+      <c r="L45" t="s">
+        <v>22</v>
+      </c>
+      <c r="M45" t="s">
+        <v>22</v>
+      </c>
+      <c r="N45" t="s">
+        <v>22</v>
+      </c>
+      <c r="O45" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="46" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A46" t="s">
+        <v>271</v>
+      </c>
+      <c r="B46" t="s">
+        <v>113</v>
+      </c>
+      <c r="C46" t="s">
+        <v>114</v>
+      </c>
+      <c r="D46" t="s">
+        <v>18</v>
+      </c>
+      <c r="E46" t="s">
+        <v>115</v>
+      </c>
+      <c r="F46" t="s">
+        <v>65</v>
+      </c>
+      <c r="G46" t="s">
+        <v>20</v>
+      </c>
+      <c r="H46" t="s">
+        <v>30</v>
+      </c>
+      <c r="I46" t="s">
+        <v>104</v>
+      </c>
+      <c r="J46" t="s">
+        <v>272</v>
+      </c>
+      <c r="K46" t="s">
+        <v>273</v>
+      </c>
+      <c r="L46" t="s">
+        <v>22</v>
+      </c>
+      <c r="M46" t="s">
+        <v>69</v>
+      </c>
+      <c r="N46" t="s">
+        <v>22</v>
+      </c>
+      <c r="O46" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="47" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A47" t="s">
+        <v>275</v>
+      </c>
+      <c r="B47" t="s">
+        <v>276</v>
+      </c>
+      <c r="C47" t="s">
+        <v>59</v>
+      </c>
+      <c r="D47" t="s">
+        <v>18</v>
+      </c>
+      <c r="E47" t="s">
+        <v>277</v>
+      </c>
+      <c r="F47" t="s">
+        <v>19</v>
+      </c>
+      <c r="G47" t="s">
+        <v>20</v>
+      </c>
+      <c r="H47" t="s">
+        <v>30</v>
+      </c>
+      <c r="I47" t="s">
+        <v>104</v>
+      </c>
+      <c r="J47" t="s">
+        <v>278</v>
+      </c>
+      <c r="K47" t="s">
+        <v>273</v>
+      </c>
+      <c r="L47" t="s">
+        <v>22</v>
+      </c>
+      <c r="M47" t="s">
+        <v>22</v>
+      </c>
+      <c r="N47" t="s">
+        <v>22</v>
+      </c>
+      <c r="O47" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="48" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A48" t="s">
+        <v>280</v>
+      </c>
+      <c r="B48" t="s">
+        <v>224</v>
+      </c>
+      <c r="C48" t="s">
+        <v>225</v>
+      </c>
+      <c r="D48" t="s">
+        <v>18</v>
+      </c>
+      <c r="E48" t="s">
+        <v>18</v>
+      </c>
+      <c r="F48" t="s">
+        <v>29</v>
+      </c>
+      <c r="G48" t="s">
+        <v>182</v>
+      </c>
+      <c r="H48" t="s">
+        <v>30</v>
+      </c>
+      <c r="I48" t="s">
+        <v>104</v>
+      </c>
+      <c r="J48" t="s">
+        <v>281</v>
+      </c>
+      <c r="K48" t="s">
+        <v>93</v>
+      </c>
+      <c r="L48" t="s">
+        <v>22</v>
+      </c>
+      <c r="M48" t="s">
+        <v>22</v>
+      </c>
+      <c r="N48" t="s">
+        <v>246</v>
+      </c>
+      <c r="O48" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="49" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A49" t="s">
+        <v>283</v>
+      </c>
+      <c r="B49" t="s">
+        <v>284</v>
+      </c>
+      <c r="C49" t="s">
+        <v>285</v>
+      </c>
+      <c r="D49" t="s">
+        <v>18</v>
+      </c>
+      <c r="E49" t="s">
+        <v>18</v>
+      </c>
+      <c r="F49" t="s">
+        <v>29</v>
+      </c>
+      <c r="G49" t="s">
+        <v>182</v>
+      </c>
+      <c r="H49" t="s">
+        <v>30</v>
+      </c>
+      <c r="I49" t="s">
+        <v>104</v>
+      </c>
+      <c r="J49" t="s">
+        <v>286</v>
+      </c>
+      <c r="K49" t="s">
+        <v>287</v>
+      </c>
+      <c r="L49" t="s">
+        <v>22</v>
+      </c>
+      <c r="M49" t="s">
+        <v>22</v>
+      </c>
+      <c r="N49" t="s">
+        <v>288</v>
+      </c>
+      <c r="O49" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="50" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A50" t="s">
+        <v>290</v>
+      </c>
+      <c r="B50" t="s">
+        <v>102</v>
+      </c>
+      <c r="C50" t="s">
+        <v>291</v>
+      </c>
+      <c r="D50" t="s">
+        <v>18</v>
+      </c>
+      <c r="E50" t="s">
+        <v>18</v>
+      </c>
+      <c r="F50" t="s">
+        <v>258</v>
+      </c>
+      <c r="G50" t="s">
         <v>268</v>
       </c>
-      <c r="K45" t="s">
-        <v>269</v>
-      </c>
-      <c r="L45" t="s">
-        <v>22</v>
-      </c>
-      <c r="M45" t="s">
-        <v>22</v>
-      </c>
-      <c r="N45" t="s">
-        <v>270</v>
-      </c>
-      <c r="O45" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="46" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A46" t="s">
-        <v>272</v>
-      </c>
-      <c r="B46" t="s">
-        <v>78</v>
-      </c>
-      <c r="C46" t="s">
-        <v>273</v>
-      </c>
-      <c r="D46" t="s">
-        <v>18</v>
-      </c>
-      <c r="E46" t="s">
-        <v>18</v>
-      </c>
-      <c r="F46" t="s">
-        <v>238</v>
-      </c>
-      <c r="G46" t="s">
-        <v>249</v>
-      </c>
-      <c r="H46" t="s">
-        <v>21</v>
-      </c>
-      <c r="I46" t="s">
-        <v>80</v>
-      </c>
-      <c r="J46" t="s">
-        <v>274</v>
-      </c>
-      <c r="K46" t="s">
-        <v>275</v>
-      </c>
-      <c r="L46" t="s">
-        <v>22</v>
-      </c>
-      <c r="M46" t="s">
-        <v>22</v>
-      </c>
-      <c r="N46" t="s">
-        <v>22</v>
-      </c>
-      <c r="O46" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="47" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A47" t="s">
-        <v>277</v>
-      </c>
-      <c r="B47" t="s">
-        <v>78</v>
-      </c>
-      <c r="C47" t="s">
-        <v>273</v>
-      </c>
-      <c r="D47" t="s">
-        <v>18</v>
-      </c>
-      <c r="E47" t="s">
-        <v>18</v>
-      </c>
-      <c r="F47" t="s">
-        <v>238</v>
-      </c>
-      <c r="G47" t="s">
-        <v>278</v>
-      </c>
-      <c r="H47" t="s">
-        <v>21</v>
-      </c>
-      <c r="I47" t="s">
-        <v>80</v>
-      </c>
-      <c r="J47" t="s">
-        <v>279</v>
-      </c>
-      <c r="K47" t="s">
-        <v>167</v>
-      </c>
-      <c r="L47" t="s">
-        <v>22</v>
-      </c>
-      <c r="M47" t="s">
-        <v>22</v>
-      </c>
-      <c r="N47" t="s">
-        <v>22</v>
-      </c>
-      <c r="O47" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="48" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A48" t="s">
-        <v>281</v>
-      </c>
-      <c r="B48" t="s">
-        <v>78</v>
-      </c>
-      <c r="C48" t="s">
-        <v>273</v>
-      </c>
-      <c r="D48" t="s">
-        <v>18</v>
-      </c>
-      <c r="E48" t="s">
-        <v>18</v>
-      </c>
-      <c r="F48" t="s">
-        <v>51</v>
-      </c>
-      <c r="G48" t="s">
-        <v>146</v>
-      </c>
-      <c r="H48" t="s">
-        <v>21</v>
-      </c>
-      <c r="I48" t="s">
-        <v>80</v>
-      </c>
-      <c r="J48" t="s">
-        <v>282</v>
-      </c>
-      <c r="K48" t="s">
-        <v>39</v>
-      </c>
-      <c r="L48" t="s">
-        <v>22</v>
-      </c>
-      <c r="M48" t="s">
-        <v>22</v>
-      </c>
-      <c r="N48" t="s">
-        <v>207</v>
-      </c>
-      <c r="O48" t="s">
-        <v>283</v>
-      </c>
-    </row>
-    <row r="49" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A49" t="s">
-        <v>284</v>
-      </c>
-      <c r="B49" t="s">
-        <v>27</v>
-      </c>
-      <c r="C49" t="s">
-        <v>72</v>
-      </c>
-      <c r="D49" t="s">
-        <v>18</v>
-      </c>
-      <c r="E49" t="s">
-        <v>18</v>
-      </c>
-      <c r="F49" t="s">
-        <v>92</v>
-      </c>
-      <c r="G49" t="s">
+      <c r="H50" t="s">
+        <v>30</v>
+      </c>
+      <c r="I50" t="s">
+        <v>104</v>
+      </c>
+      <c r="J50" t="s">
+        <v>292</v>
+      </c>
+      <c r="K50" t="s">
+        <v>293</v>
+      </c>
+      <c r="L50" t="s">
+        <v>22</v>
+      </c>
+      <c r="M50" t="s">
+        <v>22</v>
+      </c>
+      <c r="N50" t="s">
+        <v>22</v>
+      </c>
+      <c r="O50" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="51" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A51" t="s">
+        <v>295</v>
+      </c>
+      <c r="B51" t="s">
+        <v>102</v>
+      </c>
+      <c r="C51" t="s">
+        <v>291</v>
+      </c>
+      <c r="D51" t="s">
+        <v>18</v>
+      </c>
+      <c r="E51" t="s">
+        <v>18</v>
+      </c>
+      <c r="F51" t="s">
+        <v>258</v>
+      </c>
+      <c r="G51" t="s">
+        <v>296</v>
+      </c>
+      <c r="H51" t="s">
+        <v>30</v>
+      </c>
+      <c r="I51" t="s">
+        <v>104</v>
+      </c>
+      <c r="J51" t="s">
+        <v>297</v>
+      </c>
+      <c r="K51" t="s">
+        <v>189</v>
+      </c>
+      <c r="L51" t="s">
+        <v>22</v>
+      </c>
+      <c r="M51" t="s">
+        <v>22</v>
+      </c>
+      <c r="N51" t="s">
+        <v>22</v>
+      </c>
+      <c r="O51" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="52" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A52" t="s">
+        <v>299</v>
+      </c>
+      <c r="B52" t="s">
+        <v>102</v>
+      </c>
+      <c r="C52" t="s">
+        <v>291</v>
+      </c>
+      <c r="D52" t="s">
+        <v>18</v>
+      </c>
+      <c r="E52" t="s">
+        <v>18</v>
+      </c>
+      <c r="F52" t="s">
+        <v>29</v>
+      </c>
+      <c r="G52" t="s">
+        <v>168</v>
+      </c>
+      <c r="H52" t="s">
+        <v>30</v>
+      </c>
+      <c r="I52" t="s">
+        <v>104</v>
+      </c>
+      <c r="J52" t="s">
+        <v>300</v>
+      </c>
+      <c r="K52" t="s">
+        <v>69</v>
+      </c>
+      <c r="L52" t="s">
+        <v>22</v>
+      </c>
+      <c r="M52" t="s">
+        <v>22</v>
+      </c>
+      <c r="N52" t="s">
+        <v>228</v>
+      </c>
+      <c r="O52" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="53" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A53" t="s">
+        <v>302</v>
+      </c>
+      <c r="B53" t="s">
+        <v>58</v>
+      </c>
+      <c r="C53" t="s">
+        <v>97</v>
+      </c>
+      <c r="D53" t="s">
+        <v>18</v>
+      </c>
+      <c r="E53" t="s">
+        <v>18</v>
+      </c>
+      <c r="F53" t="s">
+        <v>19</v>
+      </c>
+      <c r="G53" t="s">
         <v>20</v>
       </c>
-      <c r="H49" t="s">
-        <v>21</v>
-      </c>
-      <c r="I49" t="s">
-        <v>80</v>
-      </c>
-      <c r="J49" t="s">
-        <v>285</v>
-      </c>
-      <c r="K49" t="s">
-        <v>155</v>
-      </c>
-      <c r="L49" t="s">
-        <v>22</v>
-      </c>
-      <c r="M49" t="s">
-        <v>22</v>
-      </c>
-      <c r="N49" t="s">
-        <v>22</v>
-      </c>
-      <c r="O49" t="s">
-        <v>286</v>
-      </c>
-    </row>
-    <row r="50" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A50" t="s">
-        <v>287</v>
-      </c>
-      <c r="B50" t="s">
-        <v>58</v>
-      </c>
-      <c r="C50" t="s">
-        <v>65</v>
-      </c>
-      <c r="D50" t="s">
-        <v>18</v>
-      </c>
-      <c r="E50" t="s">
-        <v>18</v>
-      </c>
-      <c r="F50" t="s">
-        <v>51</v>
-      </c>
-      <c r="G50" t="s">
-        <v>20</v>
-      </c>
-      <c r="H50" t="s">
-        <v>21</v>
-      </c>
-      <c r="I50" t="s">
-        <v>80</v>
-      </c>
-      <c r="J50" t="s">
-        <v>288</v>
-      </c>
-      <c r="K50" t="s">
-        <v>139</v>
-      </c>
-      <c r="L50" t="s">
-        <v>22</v>
-      </c>
-      <c r="M50" t="s">
-        <v>22</v>
-      </c>
-      <c r="N50" t="s">
-        <v>289</v>
-      </c>
-      <c r="O50" t="s">
-        <v>290</v>
-      </c>
-    </row>
-    <row r="51" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A51" t="s">
-        <v>291</v>
-      </c>
-      <c r="B51" t="s">
-        <v>89</v>
-      </c>
-      <c r="C51" t="s">
+      <c r="H53" t="s">
+        <v>30</v>
+      </c>
+      <c r="I53" t="s">
+        <v>104</v>
+      </c>
+      <c r="J53" t="s">
+        <v>303</v>
+      </c>
+      <c r="K53" t="s">
+        <v>177</v>
+      </c>
+      <c r="L53" t="s">
+        <v>22</v>
+      </c>
+      <c r="M53" t="s">
+        <v>22</v>
+      </c>
+      <c r="N53" t="s">
+        <v>22</v>
+      </c>
+      <c r="O53" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="54" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A54" t="s">
+        <v>305</v>
+      </c>
+      <c r="B54" t="s">
+        <v>83</v>
+      </c>
+      <c r="C54" t="s">
         <v>90</v>
       </c>
-      <c r="D51" t="s">
-        <v>18</v>
-      </c>
-      <c r="E51" t="s">
-        <v>91</v>
-      </c>
-      <c r="F51" t="s">
-        <v>35</v>
-      </c>
-      <c r="G51" t="s">
-        <v>73</v>
-      </c>
-      <c r="H51" t="s">
-        <v>21</v>
-      </c>
-      <c r="I51" t="s">
-        <v>80</v>
-      </c>
-      <c r="J51" t="s">
-        <v>292</v>
-      </c>
-      <c r="K51" t="s">
-        <v>127</v>
-      </c>
-      <c r="L51" t="s">
-        <v>22</v>
-      </c>
-      <c r="M51" t="s">
-        <v>39</v>
-      </c>
-      <c r="N51" t="s">
-        <v>22</v>
-      </c>
-      <c r="O51" t="s">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="52" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A52" t="s">
-        <v>294</v>
-      </c>
-      <c r="B52" t="s">
-        <v>89</v>
-      </c>
-      <c r="C52" t="s">
-        <v>90</v>
-      </c>
-      <c r="D52" t="s">
-        <v>18</v>
-      </c>
-      <c r="E52" t="s">
-        <v>91</v>
-      </c>
-      <c r="F52" t="s">
-        <v>92</v>
-      </c>
-      <c r="G52" t="s">
-        <v>20</v>
-      </c>
-      <c r="H52" t="s">
-        <v>21</v>
-      </c>
-      <c r="I52" t="s">
-        <v>80</v>
-      </c>
-      <c r="J52" t="s">
-        <v>292</v>
-      </c>
-      <c r="K52" t="s">
-        <v>295</v>
-      </c>
-      <c r="L52" t="s">
-        <v>22</v>
-      </c>
-      <c r="M52" t="s">
-        <v>22</v>
-      </c>
-      <c r="N52" t="s">
-        <v>22</v>
-      </c>
-      <c r="O52" t="s">
-        <v>296</v>
-      </c>
-    </row>
-    <row r="53" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A53" t="s">
-        <v>297</v>
-      </c>
-      <c r="B53" t="s">
-        <v>298</v>
-      </c>
-      <c r="C53" t="s">
-        <v>299</v>
-      </c>
-      <c r="D53" t="s">
-        <v>18</v>
-      </c>
-      <c r="E53" t="s">
-        <v>18</v>
-      </c>
-      <c r="F53" t="s">
-        <v>300</v>
-      </c>
-      <c r="G53" t="s">
-        <v>52</v>
-      </c>
-      <c r="H53" t="s">
-        <v>21</v>
-      </c>
-      <c r="I53" t="s">
-        <v>80</v>
-      </c>
-      <c r="J53" t="s">
-        <v>301</v>
-      </c>
-      <c r="K53" t="s">
-        <v>295</v>
-      </c>
-      <c r="L53" t="s">
-        <v>22</v>
-      </c>
-      <c r="M53" t="s">
-        <v>22</v>
-      </c>
-      <c r="N53" t="s">
-        <v>22</v>
-      </c>
-      <c r="O53" t="s">
-        <v>302</v>
-      </c>
-    </row>
-    <row r="54" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A54" t="s">
-        <v>303</v>
-      </c>
-      <c r="B54" t="s">
-        <v>145</v>
-      </c>
-      <c r="C54" t="s">
-        <v>59</v>
-      </c>
       <c r="D54" t="s">
         <v>18</v>
       </c>
@@ -3928,116 +3847,116 @@
         <v>18</v>
       </c>
       <c r="F54" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="G54" t="s">
         <v>20</v>
       </c>
       <c r="H54" t="s">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="I54" t="s">
-        <v>80</v>
+        <v>104</v>
       </c>
       <c r="J54" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="K54" t="s">
-        <v>61</v>
+        <v>161</v>
       </c>
       <c r="L54" t="s">
         <v>22</v>
       </c>
       <c r="M54" t="s">
-        <v>39</v>
+        <v>22</v>
       </c>
       <c r="N54" t="s">
-        <v>22</v>
+        <v>307</v>
       </c>
       <c r="O54" t="s">
-        <v>305</v>
-      </c>
-    </row>
-    <row r="55" spans="1:15" x14ac:dyDescent="0.25">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="55" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="B55" t="s">
-        <v>266</v>
+        <v>113</v>
       </c>
       <c r="C55" t="s">
-        <v>267</v>
+        <v>114</v>
       </c>
       <c r="D55" t="s">
         <v>18</v>
       </c>
       <c r="E55" t="s">
-        <v>18</v>
+        <v>115</v>
       </c>
       <c r="F55" t="s">
-        <v>238</v>
+        <v>65</v>
       </c>
       <c r="G55" t="s">
-        <v>239</v>
+        <v>38</v>
       </c>
       <c r="H55" t="s">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="I55" t="s">
-        <v>80</v>
+        <v>104</v>
       </c>
       <c r="J55" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="K55" t="s">
-        <v>24</v>
+        <v>149</v>
       </c>
       <c r="L55" t="s">
         <v>22</v>
       </c>
       <c r="M55" t="s">
-        <v>22</v>
+        <v>69</v>
       </c>
       <c r="N55" t="s">
         <v>22</v>
       </c>
       <c r="O55" t="s">
-        <v>308</v>
-      </c>
-    </row>
-    <row r="56" spans="1:15" x14ac:dyDescent="0.25">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="56" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="B56" t="s">
-        <v>89</v>
+        <v>113</v>
       </c>
       <c r="C56" t="s">
-        <v>90</v>
+        <v>114</v>
       </c>
       <c r="D56" t="s">
         <v>18</v>
       </c>
       <c r="E56" t="s">
-        <v>91</v>
+        <v>115</v>
       </c>
       <c r="F56" t="s">
-        <v>300</v>
+        <v>19</v>
       </c>
       <c r="G56" t="s">
         <v>20</v>
       </c>
       <c r="H56" t="s">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="I56" t="s">
-        <v>80</v>
+        <v>104</v>
       </c>
       <c r="J56" t="s">
         <v>310</v>
       </c>
       <c r="K56" t="s">
-        <v>148</v>
+        <v>313</v>
       </c>
       <c r="L56" t="s">
         <v>22</v>
@@ -4049,383 +3968,7 @@
         <v>22</v>
       </c>
       <c r="O56" t="s">
-        <v>311</v>
-      </c>
-    </row>
-    <row r="57" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A57" t="s">
-        <v>312</v>
-      </c>
-      <c r="B57" t="s">
-        <v>216</v>
-      </c>
-      <c r="C57" t="s">
-        <v>34</v>
-      </c>
-      <c r="D57" t="s">
-        <v>18</v>
-      </c>
-      <c r="E57" t="s">
-        <v>18</v>
-      </c>
-      <c r="F57" t="s">
-        <v>35</v>
-      </c>
-      <c r="G57" t="s">
-        <v>73</v>
-      </c>
-      <c r="H57" t="s">
-        <v>21</v>
-      </c>
-      <c r="I57" t="s">
-        <v>80</v>
-      </c>
-      <c r="J57" t="s">
-        <v>313</v>
-      </c>
-      <c r="K57" t="s">
         <v>314</v>
-      </c>
-      <c r="L57" t="s">
-        <v>22</v>
-      </c>
-      <c r="M57" t="s">
-        <v>39</v>
-      </c>
-      <c r="N57" t="s">
-        <v>22</v>
-      </c>
-      <c r="O57" t="s">
-        <v>315</v>
-      </c>
-    </row>
-    <row r="58" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A58" t="s">
-        <v>316</v>
-      </c>
-      <c r="B58" t="s">
-        <v>151</v>
-      </c>
-      <c r="C58" t="s">
-        <v>152</v>
-      </c>
-      <c r="D58" t="s">
-        <v>153</v>
-      </c>
-      <c r="E58" t="s">
-        <v>91</v>
-      </c>
-      <c r="F58" t="s">
-        <v>238</v>
-      </c>
-      <c r="G58" t="s">
-        <v>249</v>
-      </c>
-      <c r="H58" t="s">
-        <v>21</v>
-      </c>
-      <c r="I58" t="s">
-        <v>80</v>
-      </c>
-      <c r="J58" t="s">
-        <v>317</v>
-      </c>
-      <c r="K58" t="s">
-        <v>82</v>
-      </c>
-      <c r="L58" t="s">
-        <v>22</v>
-      </c>
-      <c r="M58" t="s">
-        <v>22</v>
-      </c>
-      <c r="N58" t="s">
-        <v>22</v>
-      </c>
-      <c r="O58" t="s">
-        <v>318</v>
-      </c>
-    </row>
-    <row r="59" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A59" t="s">
-        <v>319</v>
-      </c>
-      <c r="B59" t="s">
-        <v>27</v>
-      </c>
-      <c r="C59" t="s">
-        <v>28</v>
-      </c>
-      <c r="D59" t="s">
-        <v>18</v>
-      </c>
-      <c r="E59" t="s">
-        <v>18</v>
-      </c>
-      <c r="F59" t="s">
-        <v>92</v>
-      </c>
-      <c r="G59" t="s">
-        <v>73</v>
-      </c>
-      <c r="H59" t="s">
-        <v>21</v>
-      </c>
-      <c r="I59" t="s">
-        <v>80</v>
-      </c>
-      <c r="J59" t="s">
-        <v>320</v>
-      </c>
-      <c r="K59" t="s">
-        <v>155</v>
-      </c>
-      <c r="L59" t="s">
-        <v>22</v>
-      </c>
-      <c r="M59" t="s">
-        <v>22</v>
-      </c>
-      <c r="N59" t="s">
-        <v>22</v>
-      </c>
-      <c r="O59" t="s">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="60" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A60" t="s">
-        <v>322</v>
-      </c>
-      <c r="B60" t="s">
-        <v>223</v>
-      </c>
-      <c r="C60" t="s">
-        <v>101</v>
-      </c>
-      <c r="D60" t="s">
-        <v>18</v>
-      </c>
-      <c r="E60" t="s">
-        <v>18</v>
-      </c>
-      <c r="F60" t="s">
-        <v>35</v>
-      </c>
-      <c r="G60" t="s">
-        <v>323</v>
-      </c>
-      <c r="H60" t="s">
-        <v>21</v>
-      </c>
-      <c r="I60" t="s">
-        <v>80</v>
-      </c>
-      <c r="J60" t="s">
-        <v>324</v>
-      </c>
-      <c r="K60" t="s">
-        <v>167</v>
-      </c>
-      <c r="L60" t="s">
-        <v>22</v>
-      </c>
-      <c r="M60" t="s">
-        <v>39</v>
-      </c>
-      <c r="N60" t="s">
-        <v>22</v>
-      </c>
-      <c r="O60" t="s">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="61" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A61" t="s">
-        <v>326</v>
-      </c>
-      <c r="B61" t="s">
-        <v>258</v>
-      </c>
-      <c r="C61" t="s">
-        <v>28</v>
-      </c>
-      <c r="D61" t="s">
-        <v>18</v>
-      </c>
-      <c r="E61" t="s">
-        <v>259</v>
-      </c>
-      <c r="F61" t="s">
-        <v>92</v>
-      </c>
-      <c r="G61" t="s">
-        <v>73</v>
-      </c>
-      <c r="H61" t="s">
-        <v>21</v>
-      </c>
-      <c r="I61" t="s">
-        <v>80</v>
-      </c>
-      <c r="J61" t="s">
-        <v>327</v>
-      </c>
-      <c r="K61" t="s">
-        <v>295</v>
-      </c>
-      <c r="L61" t="s">
-        <v>22</v>
-      </c>
-      <c r="M61" t="s">
-        <v>22</v>
-      </c>
-      <c r="N61" t="s">
-        <v>22</v>
-      </c>
-      <c r="O61" t="s">
-        <v>328</v>
-      </c>
-    </row>
-    <row r="62" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A62" t="s">
-        <v>329</v>
-      </c>
-      <c r="B62" t="s">
-        <v>145</v>
-      </c>
-      <c r="C62" t="s">
-        <v>59</v>
-      </c>
-      <c r="D62" t="s">
-        <v>18</v>
-      </c>
-      <c r="E62" t="s">
-        <v>18</v>
-      </c>
-      <c r="F62" t="s">
-        <v>35</v>
-      </c>
-      <c r="G62" t="s">
-        <v>20</v>
-      </c>
-      <c r="H62" t="s">
-        <v>21</v>
-      </c>
-      <c r="I62" t="s">
-        <v>80</v>
-      </c>
-      <c r="J62" t="s">
-        <v>330</v>
-      </c>
-      <c r="K62" t="s">
-        <v>234</v>
-      </c>
-      <c r="L62" t="s">
-        <v>22</v>
-      </c>
-      <c r="M62" t="s">
-        <v>39</v>
-      </c>
-      <c r="N62" t="s">
-        <v>22</v>
-      </c>
-      <c r="O62" t="s">
-        <v>331</v>
-      </c>
-    </row>
-    <row r="63" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A63" t="s">
-        <v>332</v>
-      </c>
-      <c r="B63" t="s">
-        <v>64</v>
-      </c>
-      <c r="C63" t="s">
-        <v>333</v>
-      </c>
-      <c r="D63" t="s">
-        <v>18</v>
-      </c>
-      <c r="E63" t="s">
-        <v>18</v>
-      </c>
-      <c r="F63" t="s">
-        <v>35</v>
-      </c>
-      <c r="G63" t="s">
-        <v>20</v>
-      </c>
-      <c r="H63" t="s">
-        <v>21</v>
-      </c>
-      <c r="I63" t="s">
-        <v>80</v>
-      </c>
-      <c r="J63" t="s">
-        <v>334</v>
-      </c>
-      <c r="K63" t="s">
-        <v>335</v>
-      </c>
-      <c r="L63" t="s">
-        <v>22</v>
-      </c>
-      <c r="M63" t="s">
-        <v>39</v>
-      </c>
-      <c r="N63" t="s">
-        <v>22</v>
-      </c>
-      <c r="O63" t="s">
-        <v>336</v>
-      </c>
-    </row>
-    <row r="64" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A64" t="s">
-        <v>337</v>
-      </c>
-      <c r="B64" t="s">
-        <v>338</v>
-      </c>
-      <c r="C64" t="s">
-        <v>112</v>
-      </c>
-      <c r="D64" t="s">
-        <v>18</v>
-      </c>
-      <c r="E64" t="s">
-        <v>18</v>
-      </c>
-      <c r="F64" t="s">
-        <v>300</v>
-      </c>
-      <c r="G64" t="s">
-        <v>20</v>
-      </c>
-      <c r="H64" t="s">
-        <v>21</v>
-      </c>
-      <c r="I64" t="s">
-        <v>80</v>
-      </c>
-      <c r="J64" t="s">
-        <v>339</v>
-      </c>
-      <c r="K64" t="s">
-        <v>340</v>
-      </c>
-      <c r="L64" t="s">
-        <v>22</v>
-      </c>
-      <c r="M64" t="s">
-        <v>22</v>
-      </c>
-      <c r="N64" t="s">
-        <v>22</v>
-      </c>
-      <c r="O64" t="s">
-        <v>341</v>
       </c>
     </row>
   </sheetData>

--- a/camera_events.xlsx
+++ b/camera_events.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30131"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{CC9F920B-D726-4CF4-BA82-ECA6257C1568}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{E48DAFA0-21C7-4693-AF87-08F99BB60636}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="840" uniqueCount="315">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="765" uniqueCount="291">
   <si>
     <t>Time</t>
   </si>
@@ -62,40 +62,211 @@
     <t>Event URL</t>
   </si>
   <si>
-    <t>07/01/2026 12:19:17 PM</t>
-  </si>
-  <si>
-    <t>TT. 5362</t>
-  </si>
-  <si>
-    <t>RICHARD FLECKENSTEIN #2038</t>
+    <t>07/10/2026 10:35:28 AM</t>
+  </si>
+  <si>
+    <t>TT. 5359</t>
+  </si>
+  <si>
+    <t>GLEDIE BAIRES  #1958</t>
   </si>
   <si>
     <t>TT DRIVERS, Truck Drivers Pay Roll</t>
   </si>
   <si>
+    <t>Rolling Stop</t>
+  </si>
+  <si>
+    <t>Light Traffic</t>
+  </si>
+  <si>
+    <t>Coached</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>CO 52, Erie, CO</t>
+  </si>
+  <si>
+    <t>13</t>
+  </si>
+  <si>
+    <t>https://cloud.samsara.com/o/9002774/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54454ce2-544c-5caa-b606-45984b6d5a4d</t>
+  </si>
+  <si>
+    <t>07/08/2026 10:00:14 AM</t>
+  </si>
+  <si>
+    <t>TT. 5372</t>
+  </si>
+  <si>
+    <t>NICK TRUJILLO  #1947</t>
+  </si>
+  <si>
+    <t>Uravan Court, Commerce City, CO</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>https://cloud.samsara.com/o/9002774/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54454275-5a79-5164-86f5-9c44489a042a</t>
+  </si>
+  <si>
+    <t>07/08/2026 6:21:36 AM</t>
+  </si>
+  <si>
+    <t>TT. 9329</t>
+  </si>
+  <si>
+    <t>GILBERT NAVA  #1690</t>
+  </si>
+  <si>
+    <t>Harsh Brake</t>
+  </si>
+  <si>
+    <t>Moderate Traffic</t>
+  </si>
+  <si>
+    <t>Needs Coaching</t>
+  </si>
+  <si>
+    <t>Pecos Street, Zuni, CO, 80221</t>
+  </si>
+  <si>
+    <t>12</t>
+  </si>
+  <si>
+    <t>0.64</t>
+  </si>
+  <si>
+    <t>https://cloud.samsara.com/o/9002774/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=544541ad-3032-50ba-9c67-845ed6e1535f</t>
+  </si>
+  <si>
+    <t>07/07/2026 7:21:20 AM</t>
+  </si>
+  <si>
     <t>Mobile Usage</t>
   </si>
   <si>
-    <t>Light Traffic</t>
-  </si>
-  <si>
-    <t>Needs Coaching</t>
-  </si>
-  <si>
-    <t>-</t>
-  </si>
-  <si>
-    <t>County Road 59, 17.0 mi ENE Fort Lupton, Weld County, CO</t>
-  </si>
-  <si>
-    <t>43</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/9002774/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54451eb1-35c4-5ffa-ba61-6e9a365ede0b</t>
-  </si>
-  <si>
-    <t>06/29/2026 12:48:21 PM</t>
+    <t>Mineral Road, 2.7 mi NNW Erie, Boulder County, CO</t>
+  </si>
+  <si>
+    <t>47</t>
+  </si>
+  <si>
+    <t>https://cloud.samsara.com/o/9002774/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54453cbd-82d6-5896-b6a6-d96a5e8bd29d</t>
+  </si>
+  <si>
+    <t>07/07/2026 6:58:16 AM</t>
+  </si>
+  <si>
+    <t>TT. 5358</t>
+  </si>
+  <si>
+    <t>LUIS ALVAREZ  #1908</t>
+  </si>
+  <si>
+    <t>Construction, Moderate Traffic</t>
+  </si>
+  <si>
+    <t>North Colorado Boulevard, Denver, CO, 80206</t>
+  </si>
+  <si>
+    <t>8</t>
+  </si>
+  <si>
+    <t>0.62</t>
+  </si>
+  <si>
+    <t>https://cloud.samsara.com/o/9002774/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54453ca8-6279-5f86-9f80-51b20b742830</t>
+  </si>
+  <si>
+    <t>07/06/2026 4:31:00 PM</t>
+  </si>
+  <si>
+    <t>TT. 5375</t>
+  </si>
+  <si>
+    <t>JAIME CALDERON  #1787</t>
+  </si>
+  <si>
+    <t>Inattentive Driving</t>
+  </si>
+  <si>
+    <t>South Santa Fe Drive, Denver, CO, 80223</t>
+  </si>
+  <si>
+    <t>35</t>
+  </si>
+  <si>
+    <t>0</t>
+  </si>
+  <si>
+    <t>https://cloud.samsara.com/o/9002774/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445398e-6485-5668-8f9b-63b208140062</t>
+  </si>
+  <si>
+    <t>07/03/2026 1:23:33 PM</t>
+  </si>
+  <si>
+    <t>TT. 5377</t>
+  </si>
+  <si>
+    <t>ROBERT PARKER #1072</t>
+  </si>
+  <si>
+    <t>Peña Boulevard, Denver, CO, 80019</t>
+  </si>
+  <si>
+    <t>40</t>
+  </si>
+  <si>
+    <t>https://cloud.samsara.com/o/9002774/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445296f-b046-55ba-9f74-39f65872c9be</t>
+  </si>
+  <si>
+    <t>07/02/2026 3:34:53 PM</t>
+  </si>
+  <si>
+    <t>https://cloud.samsara.com/o/9002774/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=544524c1-9404-5552-8212-417f235256e2</t>
+  </si>
+  <si>
+    <t>07/02/2026 10:41:49 AM</t>
+  </si>
+  <si>
+    <t>TT. 0432</t>
+  </si>
+  <si>
+    <t>DANIEL REMPE #1585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TT DRIVERS, Trailers , Truck Drivers Pay Roll, low boys </t>
+  </si>
+  <si>
+    <t xml:space="preserve">low boys </t>
+  </si>
+  <si>
+    <t>Dwight D. Eisenhower Highway, Dacono, CO, 80514</t>
+  </si>
+  <si>
+    <t>62</t>
+  </si>
+  <si>
+    <t>https://cloud.samsara.com/o/9002774/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=544523b5-421c-5092-ac54-ba9d8dac2b1b</t>
+  </si>
+  <si>
+    <t>07/02/2026 10:19:56 AM</t>
+  </si>
+  <si>
+    <t>Dwight D. Eisenhower Highway, 0.9 mi SSW Welby, Adams County, CO, 80229</t>
+  </si>
+  <si>
+    <t>46</t>
+  </si>
+  <si>
+    <t>https://cloud.samsara.com/o/9002774/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=544523a1-3857-5ae0-b04a-d0f0ad10f5a4</t>
+  </si>
+  <si>
+    <t>06/29/2026 11:48:21 AM</t>
   </si>
   <si>
     <t>TT. 9326</t>
@@ -104,25 +275,16 @@
     <t>TROY RAMIREZ  #1988</t>
   </si>
   <si>
-    <t>Harsh Brake</t>
-  </si>
-  <si>
-    <t>Coached</t>
-  </si>
-  <si>
     <t>Sheridan Boulevard, Arvada, CO, 80003</t>
   </si>
   <si>
-    <t>6</t>
-  </si>
-  <si>
     <t>0.59</t>
   </si>
   <si>
     <t>https://cloud.samsara.com/o/9002774/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445147f-1983-5a9f-9bfc-185fe4e8ea47</t>
   </si>
   <si>
-    <t>06/29/2026 8:59:17 AM</t>
+    <t>06/29/2026 7:59:17 AM</t>
   </si>
   <si>
     <t>TT. 5353</t>
@@ -131,9 +293,6 @@
     <t>BRAD CRAIG #2053</t>
   </si>
   <si>
-    <t>Moderate Traffic</t>
-  </si>
-  <si>
     <t>Dwight D. Eisenhower Highway, Mead, CO, 80542</t>
   </si>
   <si>
@@ -146,10 +305,7 @@
     <t>https://cloud.samsara.com/o/9002774/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=544513ad-62db-5561-a244-d43ae8157a15</t>
   </si>
   <si>
-    <t>06/26/2026 5:00:15 PM</t>
-  </si>
-  <si>
-    <t>TT. 5358</t>
+    <t>06/26/2026 4:00:15 PM</t>
   </si>
   <si>
     <t>CLEMENTE CHAVEZ  #1971</t>
@@ -167,7 +323,7 @@
     <t>https://cloud.samsara.com/o/9002774/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=544505f2-a2be-50d1-93b9-1384ccc8fbc7</t>
   </si>
   <si>
-    <t>06/26/2026 11:57:57 AM</t>
+    <t>06/26/2026 10:57:57 AM</t>
   </si>
   <si>
     <t>TT. 5367</t>
@@ -188,7 +344,7 @@
     <t>https://cloud.samsara.com/o/9002774/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=544504dd-e117-5eec-a034-b1368775e800</t>
   </si>
   <si>
-    <t>06/25/2026 3:55:44 PM</t>
+    <t>06/25/2026 2:55:44 PM</t>
   </si>
   <si>
     <t>TT. 5374</t>
@@ -203,7 +359,7 @@
     <t>https://cloud.samsara.com/o/9002774/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54450091-3597-536d-8a33-5f6b262edcec</t>
   </si>
   <si>
-    <t>06/25/2026 8:12:06 AM</t>
+    <t>06/25/2026 7:12:06 AM</t>
   </si>
   <si>
     <t>TT. 6230</t>
@@ -212,9 +368,6 @@
     <t>ROBERT JACOBS  #0017</t>
   </si>
   <si>
-    <t>Inattentive Driving</t>
-  </si>
-  <si>
     <t>Wet Road, Light Traffic</t>
   </si>
   <si>
@@ -224,13 +377,10 @@
     <t>66</t>
   </si>
   <si>
-    <t>0</t>
-  </si>
-  <si>
     <t>https://cloud.samsara.com/o/9002774/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445fee8-bf5c-594e-a928-efe1dacd6d8d</t>
   </si>
   <si>
-    <t>06/25/2026 8:04:24 AM</t>
+    <t>06/25/2026 7:04:24 AM</t>
   </si>
   <si>
     <t>CanAm Highway, Brighton, CO, 80640</t>
@@ -242,18 +392,12 @@
     <t>https://cloud.samsara.com/o/9002774/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445fee1-b387-59de-a5d7-cab0a9af97c6</t>
   </si>
   <si>
-    <t>06/23/2026 11:34:19 AM</t>
+    <t>06/23/2026 10:34:19 AM</t>
   </si>
   <si>
     <t>TT. 5376</t>
   </si>
   <si>
-    <t>ROBERT PARKER #1072</t>
-  </si>
-  <si>
-    <t>Construction, Moderate Traffic</t>
-  </si>
-  <si>
     <t>East Bison Highway, Hudson, CO, 80642</t>
   </si>
   <si>
@@ -263,13 +407,7 @@
     <t>https://cloud.samsara.com/o/9002774/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445f555-2954-5359-8910-664351a54e5f</t>
   </si>
   <si>
-    <t>06/23/2026 9:38:58 AM</t>
-  </si>
-  <si>
-    <t>TT. 5375</t>
-  </si>
-  <si>
-    <t>JAIME CALDERON  #1787</t>
+    <t>06/23/2026 8:38:58 AM</t>
   </si>
   <si>
     <t>CO 52, 8.2 mi E Fort Lupton, Weld County, CO, 80642</t>
@@ -281,7 +419,7 @@
     <t>https://cloud.samsara.com/o/9002774/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445f4eb-8e2c-5c6e-8ae6-604f38484e09</t>
   </si>
   <si>
-    <t>06/22/2026 11:21:34 AM</t>
+    <t>06/22/2026 10:21:34 AM</t>
   </si>
   <si>
     <t>TT. 5355</t>
@@ -290,9 +428,6 @@
     <t>JOHN STENSRUD #0169</t>
   </si>
   <si>
-    <t>Rolling Stop</t>
-  </si>
-  <si>
     <t>Hickory Street, Hudson, CO, 80642</t>
   </si>
   <si>
@@ -302,10 +437,7 @@
     <t>https://cloud.samsara.com/o/9002774/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445f023-2279-5dd6-b604-45d862b5d353</t>
   </si>
   <si>
-    <t>06/17/2026 2:18:58 PM</t>
-  </si>
-  <si>
-    <t>TT. 5377</t>
+    <t>06/17/2026 1:18:58 PM</t>
   </si>
   <si>
     <t>JASON MILLER #1070</t>
@@ -320,7 +452,7 @@
     <t>https://cloud.samsara.com/o/9002774/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445d705-bf34-57e1-a74d-ee8af43cd52d</t>
   </si>
   <si>
-    <t>06/16/2026 2:40:43 PM</t>
+    <t>06/16/2026 1:40:43 PM</t>
   </si>
   <si>
     <t>TT. 5371</t>
@@ -341,10 +473,7 @@
     <t>https://cloud.samsara.com/o/9002774/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445d1f3-4dbd-51fd-a920-c9ee9625f923</t>
   </si>
   <si>
-    <t>06/11/2026 10:10:05 AM</t>
-  </si>
-  <si>
-    <t>CO 52, Erie, CO</t>
+    <t>06/11/2026 9:10:05 AM</t>
   </si>
   <si>
     <t>11</t>
@@ -353,7 +482,7 @@
     <t>https://cloud.samsara.com/o/9002774/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445b73b-bc8f-5fb3-aece-34388ee9f5c6</t>
   </si>
   <si>
-    <t>06/11/2026 10:05:33 AM</t>
+    <t>06/11/2026 9:05:33 AM</t>
   </si>
   <si>
     <t>TT. 4629</t>
@@ -362,9 +491,6 @@
     <t>DAVID LOPEZ  #1973</t>
   </si>
   <si>
-    <t xml:space="preserve">low boys </t>
-  </si>
-  <si>
     <t>Dwight D. Eisenhower Highway, Johnstown, CO, 80534</t>
   </si>
   <si>
@@ -374,7 +500,7 @@
     <t>https://cloud.samsara.com/o/9002774/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445b737-95fb-5ca2-8a2e-8ebf8c778c3d</t>
   </si>
   <si>
-    <t>06/10/2026 6:59:44 AM</t>
+    <t>06/10/2026 5:59:44 AM</t>
   </si>
   <si>
     <t>Dwight D. Eisenhower Highway, Broomfield, CO, 80514</t>
@@ -386,7 +512,7 @@
     <t>https://cloud.samsara.com/o/9002774/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445b167-18bc-51a3-80ec-8e025cbc91fb</t>
   </si>
   <si>
-    <t>06/09/2026 1:45:32 PM</t>
+    <t>06/09/2026 12:45:32 PM</t>
   </si>
   <si>
     <t>JAMES GARDNER  #1774</t>
@@ -401,7 +527,7 @@
     <t>https://cloud.samsara.com/o/9002774/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445adb4-4445-560e-bd6d-bdf48ae640be</t>
   </si>
   <si>
-    <t>06/09/2026 12:26:27 PM</t>
+    <t>06/09/2026 11:26:27 AM</t>
   </si>
   <si>
     <t>TT. 5357</t>
@@ -416,25 +542,16 @@
     <t>https://cloud.samsara.com/o/9002774/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445ad6b-db05-521a-97e6-9c89e0791c72</t>
   </si>
   <si>
-    <t>06/08/2026 1:46:57 PM</t>
-  </si>
-  <si>
-    <t>TT. 5372</t>
-  </si>
-  <si>
-    <t>NICK TRUJILLO  #1947</t>
+    <t>06/08/2026 12:46:57 PM</t>
   </si>
   <si>
     <t>North County Road 9, Wellington, CO, 80549</t>
   </si>
   <si>
-    <t>47</t>
-  </si>
-  <si>
     <t>https://cloud.samsara.com/o/9002774/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445a88f-3127-5bb0-9de9-39140ddf78eb</t>
   </si>
   <si>
-    <t>06/08/2026 12:05:47 PM</t>
+    <t>06/08/2026 11:05:47 AM</t>
   </si>
   <si>
     <t>TT. 1980</t>
@@ -455,7 +572,7 @@
     <t>https://cloud.samsara.com/o/9002774/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445a832-9440-52b6-8151-4d89c4dbfc40</t>
   </si>
   <si>
-    <t>06/08/2026 8:25:31 AM</t>
+    <t>06/08/2026 7:25:31 AM</t>
   </si>
   <si>
     <t>TT. 5368</t>
@@ -470,7 +587,7 @@
     <t>https://cloud.samsara.com/o/9002774/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445a768-e949-545f-9703-0d26dc9d9854</t>
   </si>
   <si>
-    <t>06/03/2026 4:39:19 PM</t>
+    <t>06/03/2026 3:39:19 PM</t>
   </si>
   <si>
     <t>Dwight D. Eisenhower Highway, 3.1 mi WSW Cheyenne, Laramie County, WY, 82005</t>
@@ -479,7 +596,7 @@
     <t>https://cloud.samsara.com/o/9002774/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54458f6d-3454-5a55-9e24-c47dfcd01ba9</t>
   </si>
   <si>
-    <t>06/03/2026 3:21:31 PM</t>
+    <t>06/03/2026 2:21:31 PM</t>
   </si>
   <si>
     <t>TT. 5373</t>
@@ -494,7 +611,7 @@
     <t>https://cloud.samsara.com/o/9002774/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54458f25-fc4b-5dd6-b477-3a18d91dbe6c</t>
   </si>
   <si>
-    <t>05/30/2026 7:43:45 AM</t>
+    <t>05/30/2026 6:43:45 AM</t>
   </si>
   <si>
     <t>East Smith Road, Aurora, CO, 80249</t>
@@ -506,7 +623,7 @@
     <t>https://cloud.samsara.com/o/9002774/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=544578e9-73b1-5beb-95c7-8c0049fd42cb</t>
   </si>
   <si>
-    <t>05/30/2026 7:24:41 AM</t>
+    <t>05/30/2026 6:24:41 AM</t>
   </si>
   <si>
     <t>East 88th Avenue, Commerce City, CO</t>
@@ -515,7 +632,7 @@
     <t>https://cloud.samsara.com/o/9002774/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=544578d7-fef9-58a8-a0c5-53ef894757d0</t>
   </si>
   <si>
-    <t>05/26/2026 4:17:38 PM</t>
+    <t>05/26/2026 3:17:38 PM</t>
   </si>
   <si>
     <t>TT. 9328</t>
@@ -533,16 +650,7 @@
     <t>https://cloud.samsara.com/o/9002774/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54456626-7ab4-5362-9bb7-bb45aef506c8</t>
   </si>
   <si>
-    <t>05/20/2026 7:36:17 AM</t>
-  </si>
-  <si>
-    <t>TT. 0432</t>
-  </si>
-  <si>
-    <t>DANIEL REMPE #1585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TT DRIVERS, Trailers , Truck Drivers Pay Roll, low boys </t>
+    <t>05/20/2026 6:36:17 AM</t>
   </si>
   <si>
     <t>E-470, Aurora, CO, 80019</t>
@@ -554,7 +662,7 @@
     <t>https://cloud.samsara.com/o/9002774/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54454563-04e6-554f-b719-2b448dbbdcb2</t>
   </si>
   <si>
-    <t>05/15/2026 5:55:47 PM</t>
+    <t>05/15/2026 4:55:47 PM</t>
   </si>
   <si>
     <t>TT. 9332</t>
@@ -572,13 +680,10 @@
     <t>2</t>
   </si>
   <si>
-    <t>0.62</t>
-  </si>
-  <si>
     <t>https://cloud.samsara.com/o/9002774/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54452dda-6168-5a12-877e-d6e4192cdaab</t>
   </si>
   <si>
-    <t>05/15/2026 2:54:11 PM</t>
+    <t>05/15/2026 1:54:11 PM</t>
   </si>
   <si>
     <t>I 25, 4.5 mi SSW Castle Rock, Douglas County, CO, 80184</t>
@@ -590,7 +695,7 @@
     <t>https://cloud.samsara.com/o/9002774/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54452d34-2034-52bf-b34f-0c720ef0a1c2</t>
   </si>
   <si>
-    <t>05/07/2026 3:19:10 PM</t>
+    <t>05/07/2026 2:19:10 PM</t>
   </si>
   <si>
     <t>TT. 5370</t>
@@ -611,7 +716,7 @@
     <t>https://cloud.samsara.com/o/9002774/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54450418-21fc-50d1-aa9f-0d13db96491b</t>
   </si>
   <si>
-    <t>05/05/2026 11:14:39 AM</t>
+    <t>05/05/2026 10:14:39 AM</t>
   </si>
   <si>
     <t>ERIC ROMERO  #1767</t>
@@ -626,7 +731,7 @@
     <t>https://cloud.samsara.com/o/9002774/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445f8eb-8d5b-51a5-89f4-65cc294cda4a</t>
   </si>
   <si>
-    <t>05/05/2026 7:48:14 AM</t>
+    <t>05/05/2026 6:48:14 AM</t>
   </si>
   <si>
     <t>South Academy Boulevard, Colorado Springs, CO, 80911</t>
@@ -638,7 +743,7 @@
     <t>https://cloud.samsara.com/o/9002774/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445f82e-9291-537a-8682-a95956a525bf</t>
   </si>
   <si>
-    <t>04/28/2026 2:16:42 PM</t>
+    <t>04/28/2026 1:16:42 PM</t>
   </si>
   <si>
     <t>5197 State Highway 93, 2.5 mi NNW Golden, Jefferson County, CO, 80403</t>
@@ -650,7 +755,7 @@
     <t>https://cloud.samsara.com/o/9002774/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445d585-b23b-55c7-96ef-fff8645a86de</t>
   </si>
   <si>
-    <t>04/22/2026 12:09:18 PM</t>
+    <t>04/22/2026 11:09:18 AM</t>
   </si>
   <si>
     <t>Peak Innovation Pkwy, Colorado Springs, CO, 80911</t>
@@ -662,7 +767,7 @@
     <t>https://cloud.samsara.com/o/9002774/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445b62a-e662-51fc-b81d-85173553523d</t>
   </si>
   <si>
-    <t>04/22/2026 8:51:55 AM</t>
+    <t>04/22/2026 7:51:55 AM</t>
   </si>
   <si>
     <t>North County Line Road, Johnstown, CO, 80534-6438</t>
@@ -674,7 +779,7 @@
     <t>https://cloud.samsara.com/o/9002774/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445b576-30b5-5349-a524-9cbcbd57e09f</t>
   </si>
   <si>
-    <t>04/22/2026 7:44:10 AM</t>
+    <t>04/22/2026 6:44:10 AM</t>
   </si>
   <si>
     <t>I 25, Dacono, CO, 80514-8502</t>
@@ -686,7 +791,7 @@
     <t>https://cloud.samsara.com/o/9002774/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445b538-2a02-5a30-b901-1be9e4cf0884</t>
   </si>
   <si>
-    <t>04/21/2026 2:56:37 PM</t>
+    <t>04/21/2026 1:56:37 PM</t>
   </si>
   <si>
     <t>TT. 5361</t>
@@ -707,7 +812,7 @@
     <t>https://cloud.samsara.com/o/9002774/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445b19d-ba77-57a9-935d-7f3e926455c4</t>
   </si>
   <si>
-    <t>04/21/2026 10:45:49 AM</t>
+    <t>04/21/2026 9:45:49 AM</t>
   </si>
   <si>
     <t>Pedestrians, Light Traffic</t>
@@ -725,7 +830,7 @@
     <t>https://cloud.samsara.com/o/9002774/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445b0b8-1c53-5993-9e2f-b340080f24e9</t>
   </si>
   <si>
-    <t>04/20/2026 2:23:49 PM</t>
+    <t>04/20/2026 1:23:49 PM</t>
   </si>
   <si>
     <t>Construction, Pedestrians, Moderate Traffic</t>
@@ -737,13 +842,10 @@
     <t>16</t>
   </si>
   <si>
-    <t>0.64</t>
-  </si>
-  <si>
     <t>https://cloud.samsara.com/o/9002774/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445ac59-5922-511c-83cb-c2a92ff0e2de</t>
   </si>
   <si>
-    <t>04/15/2026 3:42:17 PM</t>
+    <t>04/15/2026 2:42:17 PM</t>
   </si>
   <si>
     <t>TT. 9330</t>
@@ -761,7 +863,7 @@
     <t>https://cloud.samsara.com/o/9002774/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=544592e1-63d2-52ed-8700-11f8b144ef1e</t>
   </si>
   <si>
-    <t>04/13/2026 3:33:43 PM</t>
+    <t>04/13/2026 2:33:43 PM</t>
   </si>
   <si>
     <t>TT. 9331</t>
@@ -786,180 +888,6 @@
   </si>
   <si>
     <t>https://cloud.samsara.com/o/9002774/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445888c-d0f8-569a-9a1d-1fdce77a1180</t>
-  </si>
-  <si>
-    <t>04/10/2026 4:27:35 PM</t>
-  </si>
-  <si>
-    <t>Drowsiness</t>
-  </si>
-  <si>
-    <t>Very Drowsy, Moderate Traffic</t>
-  </si>
-  <si>
-    <t>South Valley Highway, Denver, CO, 80201</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/9002774/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445794b-0fb9-5061-961c-e1cfe40d139f</t>
-  </si>
-  <si>
-    <t>04/10/2026 9:10:53 AM</t>
-  </si>
-  <si>
-    <t>South Valley Highway, Denver, CO, 80222</t>
-  </si>
-  <si>
-    <t>37</t>
-  </si>
-  <si>
-    <t>0.75</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/9002774/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=544577bb-3f1b-5bba-bb45-d2c3b48eec65</t>
-  </si>
-  <si>
-    <t>04/09/2026 4:26:59 PM</t>
-  </si>
-  <si>
-    <t>Very Drowsy, Light Traffic</t>
-  </si>
-  <si>
-    <t>E-470, Aurora, CO</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/9002774/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54457424-260d-5707-a598-be8e6f6e7e47</t>
-  </si>
-  <si>
-    <t>04/09/2026 11:00:17 AM</t>
-  </si>
-  <si>
-    <t>E-470, Aurora, CO, 80018</t>
-  </si>
-  <si>
-    <t>75</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/9002774/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=544572f9-0c36-5d15-a6a7-e7bfec9a621b</t>
-  </si>
-  <si>
-    <t>04/08/2026 11:21:28 AM</t>
-  </si>
-  <si>
-    <t>TT. 9985</t>
-  </si>
-  <si>
-    <t>TT DRIVERS, Trailers , Truck Drivers Pay Roll</t>
-  </si>
-  <si>
-    <t>I 25, Greenland, CO, 80118</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/9002774/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54456de6-1425-5166-8d73-85c42ffe3ba6</t>
-  </si>
-  <si>
-    <t>04/08/2026 7:37:19 AM</t>
-  </si>
-  <si>
-    <t>North Valley Highway, North Washington, CO, 80216-8470</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/9002774/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54456d18-dd8e-5629-affd-31687597988f</t>
-  </si>
-  <si>
-    <t>04/08/2026 7:22:49 AM</t>
-  </si>
-  <si>
-    <t>TT. 9329</t>
-  </si>
-  <si>
-    <t>KEVEN FREDRICH #0030</t>
-  </si>
-  <si>
-    <t>North Valley Highway, Denver, CO, 80216</t>
-  </si>
-  <si>
-    <t>26</t>
-  </si>
-  <si>
-    <t>0.61</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/9002774/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54456d0b-95bd-5c5f-8bfd-1129dbb66192</t>
-  </si>
-  <si>
-    <t>04/07/2026 11:45:21 AM</t>
-  </si>
-  <si>
-    <t>GILBERT NAVA  #1690</t>
-  </si>
-  <si>
-    <t>9411 County Road 59, 16.4 mi ENE Fort Lupton, Weld County, CO, 80643</t>
-  </si>
-  <si>
-    <t>52</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/9002774/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=544568d5-9859-515b-aeca-8722398d62eb</t>
-  </si>
-  <si>
-    <t>04/07/2026 10:28:57 AM</t>
-  </si>
-  <si>
-    <t>Very Drowsy, Construction, Light Traffic</t>
-  </si>
-  <si>
-    <t>20854 State Highway 52, 7.8 mi E Fort Lupton, Weld County, CO, 80642</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/9002774/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445688f-a348-57fb-b449-26184c346dce</t>
-  </si>
-  <si>
-    <t>04/07/2026 7:51:18 AM</t>
-  </si>
-  <si>
-    <t>County Road 16, Fort Lupton, CO, 80621</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/9002774/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=544567ff-5078-5333-886d-b67406377444</t>
-  </si>
-  <si>
-    <t>04/06/2026 1:30:22 PM</t>
-  </si>
-  <si>
-    <t>7983 State Highway 93, 5.9 mi N Golden, Jefferson County, CO, 80403</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/9002774/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445640f-5e49-55f4-a075-9b8161cddf14</t>
-  </si>
-  <si>
-    <t>04/06/2026 9:29:13 AM</t>
-  </si>
-  <si>
-    <t>I 70, Aurora, CO, 80019</t>
-  </si>
-  <si>
-    <t>0.56</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/9002774/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54456332-99b7-5f0b-ac85-40221491495e</t>
-  </si>
-  <si>
-    <t>04/06/2026 7:34:14 AM</t>
-  </si>
-  <si>
-    <t>E-470, Denver, CO, 80249</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/9002774/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=544562c9-5410-59c1-bae5-70287e35c44a</t>
-  </si>
-  <si>
-    <t>04/06/2026 7:33:45 AM</t>
-  </si>
-  <si>
-    <t>57</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/9002774/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=544562c8-e2cc-58e4-989c-2a5834953d73</t>
   </si>
 </sst>
 </file>
@@ -1336,7 +1264,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:O56"/>
+  <dimension ref="A1:O51"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.3">
@@ -1450,233 +1378,233 @@
         <v>18</v>
       </c>
       <c r="F3" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="G3" t="s">
         <v>20</v>
       </c>
       <c r="H3" t="s">
+        <v>21</v>
+      </c>
+      <c r="I3" t="s">
+        <v>22</v>
+      </c>
+      <c r="J3" t="s">
+        <v>29</v>
+      </c>
+      <c r="K3" t="s">
         <v>30</v>
       </c>
-      <c r="I3" t="s">
-        <v>22</v>
-      </c>
-      <c r="J3" t="s">
+      <c r="L3" t="s">
+        <v>22</v>
+      </c>
+      <c r="M3" t="s">
+        <v>22</v>
+      </c>
+      <c r="N3" t="s">
+        <v>22</v>
+      </c>
+      <c r="O3" t="s">
         <v>31</v>
-      </c>
-      <c r="K3" t="s">
-        <v>32</v>
-      </c>
-      <c r="L3" t="s">
-        <v>22</v>
-      </c>
-      <c r="M3" t="s">
-        <v>22</v>
-      </c>
-      <c r="N3" t="s">
-        <v>33</v>
-      </c>
-      <c r="O3" t="s">
-        <v>34</v>
       </c>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
+        <v>32</v>
+      </c>
+      <c r="B4" t="s">
+        <v>33</v>
+      </c>
+      <c r="C4" t="s">
+        <v>34</v>
+      </c>
+      <c r="D4" t="s">
+        <v>18</v>
+      </c>
+      <c r="E4" t="s">
+        <v>18</v>
+      </c>
+      <c r="F4" t="s">
         <v>35</v>
       </c>
-      <c r="B4" t="s">
+      <c r="G4" t="s">
         <v>36</v>
       </c>
-      <c r="C4" t="s">
+      <c r="H4" t="s">
         <v>37</v>
       </c>
-      <c r="D4" t="s">
-        <v>18</v>
-      </c>
-      <c r="E4" t="s">
-        <v>18</v>
-      </c>
-      <c r="F4" t="s">
-        <v>29</v>
-      </c>
-      <c r="G4" t="s">
+      <c r="I4" t="s">
+        <v>22</v>
+      </c>
+      <c r="J4" t="s">
         <v>38</v>
       </c>
-      <c r="H4" t="s">
-        <v>30</v>
-      </c>
-      <c r="I4" t="s">
-        <v>22</v>
-      </c>
-      <c r="J4" t="s">
+      <c r="K4" t="s">
         <v>39</v>
       </c>
-      <c r="K4" t="s">
+      <c r="L4" t="s">
+        <v>22</v>
+      </c>
+      <c r="M4" t="s">
+        <v>22</v>
+      </c>
+      <c r="N4" t="s">
         <v>40</v>
       </c>
-      <c r="L4" t="s">
-        <v>22</v>
-      </c>
-      <c r="M4" t="s">
-        <v>22</v>
-      </c>
-      <c r="N4" t="s">
+      <c r="O4" t="s">
         <v>41</v>
-      </c>
-      <c r="O4" t="s">
-        <v>42</v>
       </c>
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B5" t="s">
+        <v>27</v>
+      </c>
+      <c r="C5" t="s">
+        <v>28</v>
+      </c>
+      <c r="D5" t="s">
+        <v>18</v>
+      </c>
+      <c r="E5" t="s">
+        <v>18</v>
+      </c>
+      <c r="F5" t="s">
         <v>43</v>
       </c>
-      <c r="B5" t="s">
+      <c r="G5" t="s">
+        <v>20</v>
+      </c>
+      <c r="H5" t="s">
+        <v>37</v>
+      </c>
+      <c r="I5" t="s">
+        <v>22</v>
+      </c>
+      <c r="J5" t="s">
         <v>44</v>
       </c>
-      <c r="C5" t="s">
+      <c r="K5" t="s">
         <v>45</v>
       </c>
-      <c r="D5" t="s">
-        <v>18</v>
-      </c>
-      <c r="E5" t="s">
-        <v>18</v>
-      </c>
-      <c r="F5" t="s">
+      <c r="L5" t="s">
+        <v>22</v>
+      </c>
+      <c r="M5" t="s">
+        <v>22</v>
+      </c>
+      <c r="N5" t="s">
+        <v>22</v>
+      </c>
+      <c r="O5" t="s">
         <v>46</v>
-      </c>
-      <c r="G5" t="s">
-        <v>22</v>
-      </c>
-      <c r="H5" t="s">
-        <v>21</v>
-      </c>
-      <c r="I5" t="s">
-        <v>22</v>
-      </c>
-      <c r="J5" t="s">
-        <v>47</v>
-      </c>
-      <c r="K5" t="s">
-        <v>48</v>
-      </c>
-      <c r="L5" t="s">
-        <v>22</v>
-      </c>
-      <c r="M5" t="s">
-        <v>22</v>
-      </c>
-      <c r="N5" t="s">
-        <v>22</v>
-      </c>
-      <c r="O5" t="s">
-        <v>49</v>
       </c>
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
+        <v>47</v>
+      </c>
+      <c r="B6" t="s">
+        <v>48</v>
+      </c>
+      <c r="C6" t="s">
+        <v>49</v>
+      </c>
+      <c r="D6" t="s">
+        <v>18</v>
+      </c>
+      <c r="E6" t="s">
+        <v>18</v>
+      </c>
+      <c r="F6" t="s">
+        <v>35</v>
+      </c>
+      <c r="G6" t="s">
         <v>50</v>
       </c>
-      <c r="B6" t="s">
+      <c r="H6" t="s">
+        <v>37</v>
+      </c>
+      <c r="I6" t="s">
+        <v>22</v>
+      </c>
+      <c r="J6" t="s">
         <v>51</v>
       </c>
-      <c r="C6" t="s">
+      <c r="K6" t="s">
         <v>52</v>
       </c>
-      <c r="D6" t="s">
-        <v>18</v>
-      </c>
-      <c r="E6" t="s">
-        <v>18</v>
-      </c>
-      <c r="F6" t="s">
+      <c r="L6" t="s">
+        <v>22</v>
+      </c>
+      <c r="M6" t="s">
+        <v>22</v>
+      </c>
+      <c r="N6" t="s">
         <v>53</v>
       </c>
-      <c r="G6" t="s">
-        <v>20</v>
-      </c>
-      <c r="H6" t="s">
-        <v>30</v>
-      </c>
-      <c r="I6" t="s">
-        <v>22</v>
-      </c>
-      <c r="J6" t="s">
+      <c r="O6" t="s">
         <v>54</v>
-      </c>
-      <c r="K6" t="s">
-        <v>55</v>
-      </c>
-      <c r="L6" t="s">
-        <v>22</v>
-      </c>
-      <c r="M6" t="s">
-        <v>22</v>
-      </c>
-      <c r="N6" t="s">
-        <v>22</v>
-      </c>
-      <c r="O6" t="s">
-        <v>56</v>
       </c>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
+        <v>55</v>
+      </c>
+      <c r="B7" t="s">
+        <v>56</v>
+      </c>
+      <c r="C7" t="s">
         <v>57</v>
       </c>
-      <c r="B7" t="s">
+      <c r="D7" t="s">
+        <v>18</v>
+      </c>
+      <c r="E7" t="s">
+        <v>18</v>
+      </c>
+      <c r="F7" t="s">
         <v>58</v>
       </c>
-      <c r="C7" t="s">
+      <c r="G7" t="s">
+        <v>36</v>
+      </c>
+      <c r="H7" t="s">
+        <v>37</v>
+      </c>
+      <c r="I7" t="s">
+        <v>22</v>
+      </c>
+      <c r="J7" t="s">
         <v>59</v>
       </c>
-      <c r="D7" t="s">
-        <v>18</v>
-      </c>
-      <c r="E7" t="s">
-        <v>18</v>
-      </c>
-      <c r="F7" t="s">
-        <v>53</v>
-      </c>
-      <c r="G7" t="s">
-        <v>20</v>
-      </c>
-      <c r="H7" t="s">
-        <v>30</v>
-      </c>
-      <c r="I7" t="s">
-        <v>22</v>
-      </c>
-      <c r="J7" t="s">
+      <c r="K7" t="s">
         <v>60</v>
       </c>
-      <c r="K7" t="s">
-        <v>55</v>
-      </c>
       <c r="L7" t="s">
         <v>22</v>
       </c>
       <c r="M7" t="s">
-        <v>22</v>
+        <v>61</v>
       </c>
       <c r="N7" t="s">
         <v>22</v>
       </c>
       <c r="O7" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B8" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C8" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D8" t="s">
         <v>18</v>
@@ -1685,45 +1613,45 @@
         <v>18</v>
       </c>
       <c r="F8" t="s">
-        <v>65</v>
+        <v>43</v>
       </c>
       <c r="G8" t="s">
+        <v>20</v>
+      </c>
+      <c r="H8" t="s">
+        <v>21</v>
+      </c>
+      <c r="I8" t="s">
+        <v>22</v>
+      </c>
+      <c r="J8" t="s">
         <v>66</v>
       </c>
-      <c r="H8" t="s">
-        <v>30</v>
-      </c>
-      <c r="I8" t="s">
-        <v>22</v>
-      </c>
-      <c r="J8" t="s">
+      <c r="K8" t="s">
         <v>67</v>
       </c>
-      <c r="K8" t="s">
+      <c r="L8" t="s">
+        <v>22</v>
+      </c>
+      <c r="M8" t="s">
+        <v>22</v>
+      </c>
+      <c r="N8" t="s">
+        <v>22</v>
+      </c>
+      <c r="O8" t="s">
         <v>68</v>
-      </c>
-      <c r="L8" t="s">
-        <v>22</v>
-      </c>
-      <c r="M8" t="s">
-        <v>69</v>
-      </c>
-      <c r="N8" t="s">
-        <v>22</v>
-      </c>
-      <c r="O8" t="s">
-        <v>70</v>
       </c>
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="B9" t="s">
-        <v>44</v>
+        <v>27</v>
       </c>
       <c r="C9" t="s">
-        <v>45</v>
+        <v>28</v>
       </c>
       <c r="D9" t="s">
         <v>18</v>
@@ -1732,22 +1660,22 @@
         <v>18</v>
       </c>
       <c r="F9" t="s">
-        <v>46</v>
+        <v>19</v>
       </c>
       <c r="G9" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="H9" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="I9" t="s">
         <v>22</v>
       </c>
       <c r="J9" t="s">
-        <v>72</v>
+        <v>23</v>
       </c>
       <c r="K9" t="s">
-        <v>73</v>
+        <v>39</v>
       </c>
       <c r="L9" t="s">
         <v>22</v>
@@ -1759,112 +1687,112 @@
         <v>22</v>
       </c>
       <c r="O9" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
+        <v>71</v>
+      </c>
+      <c r="B10" t="s">
+        <v>72</v>
+      </c>
+      <c r="C10" t="s">
+        <v>73</v>
+      </c>
+      <c r="D10" t="s">
+        <v>74</v>
+      </c>
+      <c r="E10" t="s">
         <v>75</v>
       </c>
-      <c r="B10" t="s">
+      <c r="F10" t="s">
+        <v>43</v>
+      </c>
+      <c r="G10" t="s">
+        <v>20</v>
+      </c>
+      <c r="H10" t="s">
+        <v>21</v>
+      </c>
+      <c r="I10" t="s">
+        <v>22</v>
+      </c>
+      <c r="J10" t="s">
         <v>76</v>
       </c>
-      <c r="C10" t="s">
+      <c r="K10" t="s">
         <v>77</v>
       </c>
-      <c r="D10" t="s">
-        <v>18</v>
-      </c>
-      <c r="E10" t="s">
-        <v>18</v>
-      </c>
-      <c r="F10" t="s">
-        <v>29</v>
-      </c>
-      <c r="G10" t="s">
+      <c r="L10" t="s">
+        <v>22</v>
+      </c>
+      <c r="M10" t="s">
+        <v>22</v>
+      </c>
+      <c r="N10" t="s">
+        <v>22</v>
+      </c>
+      <c r="O10" t="s">
         <v>78</v>
-      </c>
-      <c r="H10" t="s">
-        <v>30</v>
-      </c>
-      <c r="I10" t="s">
-        <v>22</v>
-      </c>
-      <c r="J10" t="s">
-        <v>79</v>
-      </c>
-      <c r="K10" t="s">
-        <v>32</v>
-      </c>
-      <c r="L10" t="s">
-        <v>22</v>
-      </c>
-      <c r="M10" t="s">
-        <v>22</v>
-      </c>
-      <c r="N10" t="s">
-        <v>80</v>
-      </c>
-      <c r="O10" t="s">
-        <v>81</v>
       </c>
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="B11" t="s">
-        <v>83</v>
+        <v>72</v>
       </c>
       <c r="C11" t="s">
-        <v>84</v>
+        <v>73</v>
       </c>
       <c r="D11" t="s">
-        <v>18</v>
+        <v>74</v>
       </c>
       <c r="E11" t="s">
-        <v>18</v>
+        <v>75</v>
       </c>
       <c r="F11" t="s">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="G11" t="s">
         <v>20</v>
       </c>
       <c r="H11" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="I11" t="s">
         <v>22</v>
       </c>
       <c r="J11" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="K11" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="L11" t="s">
         <v>22</v>
       </c>
       <c r="M11" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
       <c r="N11" t="s">
         <v>22</v>
       </c>
       <c r="O11" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="B12" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="C12" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="D12" t="s">
         <v>18</v>
@@ -1873,23 +1801,23 @@
         <v>18</v>
       </c>
       <c r="F12" t="s">
-        <v>91</v>
+        <v>35</v>
       </c>
       <c r="G12" t="s">
         <v>20</v>
       </c>
       <c r="H12" t="s">
+        <v>21</v>
+      </c>
+      <c r="I12" t="s">
+        <v>22</v>
+      </c>
+      <c r="J12" t="s">
+        <v>86</v>
+      </c>
+      <c r="K12" t="s">
         <v>30</v>
       </c>
-      <c r="I12" t="s">
-        <v>22</v>
-      </c>
-      <c r="J12" t="s">
-        <v>92</v>
-      </c>
-      <c r="K12" t="s">
-        <v>93</v>
-      </c>
       <c r="L12" t="s">
         <v>22</v>
       </c>
@@ -1897,115 +1825,115 @@
         <v>22</v>
       </c>
       <c r="N12" t="s">
-        <v>22</v>
+        <v>87</v>
       </c>
       <c r="O12" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
+        <v>89</v>
+      </c>
+      <c r="B13" t="s">
+        <v>90</v>
+      </c>
+      <c r="C13" t="s">
+        <v>91</v>
+      </c>
+      <c r="D13" t="s">
+        <v>18</v>
+      </c>
+      <c r="E13" t="s">
+        <v>18</v>
+      </c>
+      <c r="F13" t="s">
+        <v>35</v>
+      </c>
+      <c r="G13" t="s">
+        <v>36</v>
+      </c>
+      <c r="H13" t="s">
+        <v>21</v>
+      </c>
+      <c r="I13" t="s">
+        <v>22</v>
+      </c>
+      <c r="J13" t="s">
+        <v>92</v>
+      </c>
+      <c r="K13" t="s">
+        <v>93</v>
+      </c>
+      <c r="L13" t="s">
+        <v>22</v>
+      </c>
+      <c r="M13" t="s">
+        <v>22</v>
+      </c>
+      <c r="N13" t="s">
+        <v>94</v>
+      </c>
+      <c r="O13" t="s">
         <v>95</v>
-      </c>
-      <c r="B13" t="s">
-        <v>96</v>
-      </c>
-      <c r="C13" t="s">
-        <v>97</v>
-      </c>
-      <c r="D13" t="s">
-        <v>18</v>
-      </c>
-      <c r="E13" t="s">
-        <v>18</v>
-      </c>
-      <c r="F13" t="s">
-        <v>53</v>
-      </c>
-      <c r="G13" t="s">
-        <v>38</v>
-      </c>
-      <c r="H13" t="s">
-        <v>30</v>
-      </c>
-      <c r="I13" t="s">
-        <v>22</v>
-      </c>
-      <c r="J13" t="s">
-        <v>98</v>
-      </c>
-      <c r="K13" t="s">
-        <v>99</v>
-      </c>
-      <c r="L13" t="s">
-        <v>22</v>
-      </c>
-      <c r="M13" t="s">
-        <v>22</v>
-      </c>
-      <c r="N13" t="s">
-        <v>22</v>
-      </c>
-      <c r="O13" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
+        <v>96</v>
+      </c>
+      <c r="B14" t="s">
+        <v>48</v>
+      </c>
+      <c r="C14" t="s">
+        <v>97</v>
+      </c>
+      <c r="D14" t="s">
+        <v>18</v>
+      </c>
+      <c r="E14" t="s">
+        <v>18</v>
+      </c>
+      <c r="F14" t="s">
+        <v>98</v>
+      </c>
+      <c r="G14" t="s">
+        <v>22</v>
+      </c>
+      <c r="H14" t="s">
+        <v>37</v>
+      </c>
+      <c r="I14" t="s">
+        <v>22</v>
+      </c>
+      <c r="J14" t="s">
+        <v>99</v>
+      </c>
+      <c r="K14" t="s">
+        <v>100</v>
+      </c>
+      <c r="L14" t="s">
+        <v>22</v>
+      </c>
+      <c r="M14" t="s">
+        <v>22</v>
+      </c>
+      <c r="N14" t="s">
+        <v>22</v>
+      </c>
+      <c r="O14" t="s">
         <v>101</v>
-      </c>
-      <c r="B14" t="s">
-        <v>102</v>
-      </c>
-      <c r="C14" t="s">
-        <v>103</v>
-      </c>
-      <c r="D14" t="s">
-        <v>18</v>
-      </c>
-      <c r="E14" t="s">
-        <v>18</v>
-      </c>
-      <c r="F14" t="s">
-        <v>53</v>
-      </c>
-      <c r="G14" t="s">
-        <v>20</v>
-      </c>
-      <c r="H14" t="s">
-        <v>30</v>
-      </c>
-      <c r="I14" t="s">
-        <v>104</v>
-      </c>
-      <c r="J14" t="s">
-        <v>105</v>
-      </c>
-      <c r="K14" t="s">
-        <v>106</v>
-      </c>
-      <c r="L14" t="s">
-        <v>22</v>
-      </c>
-      <c r="M14" t="s">
-        <v>22</v>
-      </c>
-      <c r="N14" t="s">
-        <v>22</v>
-      </c>
-      <c r="O14" t="s">
-        <v>107</v>
       </c>
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="B15" t="s">
-        <v>44</v>
+        <v>103</v>
       </c>
       <c r="C15" t="s">
-        <v>45</v>
+        <v>104</v>
       </c>
       <c r="D15" t="s">
         <v>18</v>
@@ -2014,22 +1942,22 @@
         <v>18</v>
       </c>
       <c r="F15" t="s">
-        <v>91</v>
+        <v>105</v>
       </c>
       <c r="G15" t="s">
         <v>20</v>
       </c>
       <c r="H15" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="I15" t="s">
         <v>22</v>
       </c>
       <c r="J15" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="K15" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="L15" t="s">
         <v>22</v>
@@ -2041,42 +1969,42 @@
         <v>22</v>
       </c>
       <c r="O15" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="B16" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="C16" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="D16" t="s">
         <v>18</v>
       </c>
       <c r="E16" t="s">
-        <v>115</v>
+        <v>18</v>
       </c>
       <c r="F16" t="s">
-        <v>19</v>
+        <v>105</v>
       </c>
       <c r="G16" t="s">
         <v>20</v>
       </c>
       <c r="H16" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="I16" t="s">
         <v>22</v>
       </c>
       <c r="J16" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="K16" t="s">
-        <v>117</v>
+        <v>107</v>
       </c>
       <c r="L16" t="s">
         <v>22</v>
@@ -2088,159 +2016,159 @@
         <v>22</v>
       </c>
       <c r="O16" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
+        <v>114</v>
+      </c>
+      <c r="B17" t="s">
+        <v>115</v>
+      </c>
+      <c r="C17" t="s">
+        <v>116</v>
+      </c>
+      <c r="D17" t="s">
+        <v>18</v>
+      </c>
+      <c r="E17" t="s">
+        <v>18</v>
+      </c>
+      <c r="F17" t="s">
+        <v>58</v>
+      </c>
+      <c r="G17" t="s">
+        <v>117</v>
+      </c>
+      <c r="H17" t="s">
+        <v>21</v>
+      </c>
+      <c r="I17" t="s">
+        <v>22</v>
+      </c>
+      <c r="J17" t="s">
+        <v>118</v>
+      </c>
+      <c r="K17" t="s">
         <v>119</v>
       </c>
-      <c r="B17" t="s">
-        <v>76</v>
-      </c>
-      <c r="C17" t="s">
-        <v>77</v>
-      </c>
-      <c r="D17" t="s">
-        <v>18</v>
-      </c>
-      <c r="E17" t="s">
-        <v>18</v>
-      </c>
-      <c r="F17" t="s">
-        <v>53</v>
-      </c>
-      <c r="G17" t="s">
-        <v>20</v>
-      </c>
-      <c r="H17" t="s">
-        <v>30</v>
-      </c>
-      <c r="I17" t="s">
-        <v>22</v>
-      </c>
-      <c r="J17" t="s">
+      <c r="L17" t="s">
+        <v>22</v>
+      </c>
+      <c r="M17" t="s">
+        <v>61</v>
+      </c>
+      <c r="N17" t="s">
+        <v>22</v>
+      </c>
+      <c r="O17" t="s">
         <v>120</v>
-      </c>
-      <c r="K17" t="s">
-        <v>121</v>
-      </c>
-      <c r="L17" t="s">
-        <v>22</v>
-      </c>
-      <c r="M17" t="s">
-        <v>22</v>
-      </c>
-      <c r="N17" t="s">
-        <v>22</v>
-      </c>
-      <c r="O17" t="s">
-        <v>122</v>
       </c>
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
+        <v>121</v>
+      </c>
+      <c r="B18" t="s">
+        <v>48</v>
+      </c>
+      <c r="C18" t="s">
+        <v>97</v>
+      </c>
+      <c r="D18" t="s">
+        <v>18</v>
+      </c>
+      <c r="E18" t="s">
+        <v>18</v>
+      </c>
+      <c r="F18" t="s">
+        <v>98</v>
+      </c>
+      <c r="G18" t="s">
+        <v>22</v>
+      </c>
+      <c r="H18" t="s">
+        <v>21</v>
+      </c>
+      <c r="I18" t="s">
+        <v>22</v>
+      </c>
+      <c r="J18" t="s">
+        <v>122</v>
+      </c>
+      <c r="K18" t="s">
         <v>123</v>
       </c>
-      <c r="B18" t="s">
-        <v>83</v>
-      </c>
-      <c r="C18" t="s">
+      <c r="L18" t="s">
+        <v>22</v>
+      </c>
+      <c r="M18" t="s">
+        <v>22</v>
+      </c>
+      <c r="N18" t="s">
+        <v>22</v>
+      </c>
+      <c r="O18" t="s">
         <v>124</v>
-      </c>
-      <c r="D18" t="s">
-        <v>18</v>
-      </c>
-      <c r="E18" t="s">
-        <v>18</v>
-      </c>
-      <c r="F18" t="s">
-        <v>65</v>
-      </c>
-      <c r="G18" t="s">
-        <v>20</v>
-      </c>
-      <c r="H18" t="s">
-        <v>30</v>
-      </c>
-      <c r="I18" t="s">
-        <v>22</v>
-      </c>
-      <c r="J18" t="s">
-        <v>125</v>
-      </c>
-      <c r="K18" t="s">
-        <v>126</v>
-      </c>
-      <c r="L18" t="s">
-        <v>22</v>
-      </c>
-      <c r="M18" t="s">
-        <v>69</v>
-      </c>
-      <c r="N18" t="s">
-        <v>22</v>
-      </c>
-      <c r="O18" t="s">
-        <v>127</v>
       </c>
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
+        <v>125</v>
+      </c>
+      <c r="B19" t="s">
+        <v>126</v>
+      </c>
+      <c r="C19" t="s">
+        <v>65</v>
+      </c>
+      <c r="D19" t="s">
+        <v>18</v>
+      </c>
+      <c r="E19" t="s">
+        <v>18</v>
+      </c>
+      <c r="F19" t="s">
+        <v>35</v>
+      </c>
+      <c r="G19" t="s">
+        <v>50</v>
+      </c>
+      <c r="H19" t="s">
+        <v>21</v>
+      </c>
+      <c r="I19" t="s">
+        <v>22</v>
+      </c>
+      <c r="J19" t="s">
+        <v>127</v>
+      </c>
+      <c r="K19" t="s">
+        <v>30</v>
+      </c>
+      <c r="L19" t="s">
+        <v>22</v>
+      </c>
+      <c r="M19" t="s">
+        <v>22</v>
+      </c>
+      <c r="N19" t="s">
         <v>128</v>
       </c>
-      <c r="B19" t="s">
+      <c r="O19" t="s">
         <v>129</v>
-      </c>
-      <c r="C19" t="s">
-        <v>130</v>
-      </c>
-      <c r="D19" t="s">
-        <v>18</v>
-      </c>
-      <c r="E19" t="s">
-        <v>18</v>
-      </c>
-      <c r="F19" t="s">
-        <v>65</v>
-      </c>
-      <c r="G19" t="s">
-        <v>20</v>
-      </c>
-      <c r="H19" t="s">
-        <v>30</v>
-      </c>
-      <c r="I19" t="s">
-        <v>22</v>
-      </c>
-      <c r="J19" t="s">
-        <v>131</v>
-      </c>
-      <c r="K19" t="s">
-        <v>86</v>
-      </c>
-      <c r="L19" t="s">
-        <v>22</v>
-      </c>
-      <c r="M19" t="s">
-        <v>69</v>
-      </c>
-      <c r="N19" t="s">
-        <v>22</v>
-      </c>
-      <c r="O19" t="s">
-        <v>132</v>
       </c>
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="B20" t="s">
-        <v>134</v>
+        <v>56</v>
       </c>
       <c r="C20" t="s">
-        <v>135</v>
+        <v>57</v>
       </c>
       <c r="D20" t="s">
         <v>18</v>
@@ -2249,92 +2177,92 @@
         <v>18</v>
       </c>
       <c r="F20" t="s">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="G20" t="s">
         <v>20</v>
       </c>
       <c r="H20" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="I20" t="s">
         <v>22</v>
       </c>
       <c r="J20" t="s">
-        <v>136</v>
+        <v>131</v>
       </c>
       <c r="K20" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="L20" t="s">
         <v>22</v>
       </c>
       <c r="M20" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
       <c r="N20" t="s">
         <v>22</v>
       </c>
       <c r="O20" t="s">
-        <v>138</v>
+        <v>133</v>
       </c>
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
+        <v>134</v>
+      </c>
+      <c r="B21" t="s">
+        <v>135</v>
+      </c>
+      <c r="C21" t="s">
+        <v>136</v>
+      </c>
+      <c r="D21" t="s">
+        <v>18</v>
+      </c>
+      <c r="E21" t="s">
+        <v>18</v>
+      </c>
+      <c r="F21" t="s">
+        <v>19</v>
+      </c>
+      <c r="G21" t="s">
+        <v>20</v>
+      </c>
+      <c r="H21" t="s">
+        <v>21</v>
+      </c>
+      <c r="I21" t="s">
+        <v>22</v>
+      </c>
+      <c r="J21" t="s">
+        <v>137</v>
+      </c>
+      <c r="K21" t="s">
+        <v>138</v>
+      </c>
+      <c r="L21" t="s">
+        <v>22</v>
+      </c>
+      <c r="M21" t="s">
+        <v>22</v>
+      </c>
+      <c r="N21" t="s">
+        <v>22</v>
+      </c>
+      <c r="O21" t="s">
         <v>139</v>
-      </c>
-      <c r="B21" t="s">
-        <v>140</v>
-      </c>
-      <c r="C21" t="s">
-        <v>37</v>
-      </c>
-      <c r="D21" t="s">
-        <v>18</v>
-      </c>
-      <c r="E21" t="s">
-        <v>115</v>
-      </c>
-      <c r="F21" t="s">
-        <v>29</v>
-      </c>
-      <c r="G21" t="s">
-        <v>141</v>
-      </c>
-      <c r="H21" t="s">
-        <v>30</v>
-      </c>
-      <c r="I21" t="s">
-        <v>22</v>
-      </c>
-      <c r="J21" t="s">
-        <v>142</v>
-      </c>
-      <c r="K21" t="s">
-        <v>143</v>
-      </c>
-      <c r="L21" t="s">
-        <v>22</v>
-      </c>
-      <c r="M21" t="s">
-        <v>22</v>
-      </c>
-      <c r="N21" t="s">
-        <v>144</v>
-      </c>
-      <c r="O21" t="s">
-        <v>145</v>
       </c>
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>146</v>
+        <v>140</v>
       </c>
       <c r="B22" t="s">
-        <v>147</v>
+        <v>64</v>
       </c>
       <c r="C22" t="s">
-        <v>59</v>
+        <v>141</v>
       </c>
       <c r="D22" t="s">
         <v>18</v>
@@ -2343,45 +2271,45 @@
         <v>18</v>
       </c>
       <c r="F22" t="s">
-        <v>65</v>
+        <v>105</v>
       </c>
       <c r="G22" t="s">
-        <v>20</v>
+        <v>36</v>
       </c>
       <c r="H22" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="I22" t="s">
         <v>22</v>
       </c>
       <c r="J22" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="K22" t="s">
-        <v>149</v>
+        <v>143</v>
       </c>
       <c r="L22" t="s">
         <v>22</v>
       </c>
       <c r="M22" t="s">
-        <v>69</v>
+        <v>22</v>
       </c>
       <c r="N22" t="s">
         <v>22</v>
       </c>
       <c r="O22" t="s">
-        <v>150</v>
+        <v>144</v>
       </c>
     </row>
     <row r="23" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>151</v>
+        <v>145</v>
       </c>
       <c r="B23" t="s">
-        <v>58</v>
+        <v>146</v>
       </c>
       <c r="C23" t="s">
-        <v>59</v>
+        <v>147</v>
       </c>
       <c r="D23" t="s">
         <v>18</v>
@@ -2390,22 +2318,22 @@
         <v>18</v>
       </c>
       <c r="F23" t="s">
-        <v>53</v>
+        <v>105</v>
       </c>
       <c r="G23" t="s">
         <v>20</v>
       </c>
       <c r="H23" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="I23" t="s">
-        <v>22</v>
+        <v>148</v>
       </c>
       <c r="J23" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="K23" t="s">
-        <v>121</v>
+        <v>150</v>
       </c>
       <c r="L23" t="s">
         <v>22</v>
@@ -2417,253 +2345,253 @@
         <v>22</v>
       </c>
       <c r="O23" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
     </row>
     <row r="24" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
+        <v>152</v>
+      </c>
+      <c r="B24" t="s">
+        <v>48</v>
+      </c>
+      <c r="C24" t="s">
+        <v>97</v>
+      </c>
+      <c r="D24" t="s">
+        <v>18</v>
+      </c>
+      <c r="E24" t="s">
+        <v>18</v>
+      </c>
+      <c r="F24" t="s">
+        <v>19</v>
+      </c>
+      <c r="G24" t="s">
+        <v>20</v>
+      </c>
+      <c r="H24" t="s">
+        <v>21</v>
+      </c>
+      <c r="I24" t="s">
+        <v>22</v>
+      </c>
+      <c r="J24" t="s">
+        <v>23</v>
+      </c>
+      <c r="K24" t="s">
+        <v>153</v>
+      </c>
+      <c r="L24" t="s">
+        <v>22</v>
+      </c>
+      <c r="M24" t="s">
+        <v>22</v>
+      </c>
+      <c r="N24" t="s">
+        <v>22</v>
+      </c>
+      <c r="O24" t="s">
         <v>154</v>
-      </c>
-      <c r="B24" t="s">
-        <v>155</v>
-      </c>
-      <c r="C24" t="s">
-        <v>156</v>
-      </c>
-      <c r="D24" t="s">
-        <v>18</v>
-      </c>
-      <c r="E24" t="s">
-        <v>18</v>
-      </c>
-      <c r="F24" t="s">
-        <v>53</v>
-      </c>
-      <c r="G24" t="s">
-        <v>38</v>
-      </c>
-      <c r="H24" t="s">
-        <v>30</v>
-      </c>
-      <c r="I24" t="s">
-        <v>22</v>
-      </c>
-      <c r="J24" t="s">
-        <v>157</v>
-      </c>
-      <c r="K24" t="s">
-        <v>117</v>
-      </c>
-      <c r="L24" t="s">
-        <v>22</v>
-      </c>
-      <c r="M24" t="s">
-        <v>22</v>
-      </c>
-      <c r="N24" t="s">
-        <v>22</v>
-      </c>
-      <c r="O24" t="s">
-        <v>158</v>
       </c>
     </row>
     <row r="25" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="B25" t="s">
-        <v>113</v>
+        <v>156</v>
       </c>
       <c r="C25" t="s">
-        <v>114</v>
+        <v>157</v>
       </c>
       <c r="D25" t="s">
         <v>18</v>
       </c>
       <c r="E25" t="s">
-        <v>115</v>
+        <v>75</v>
       </c>
       <c r="F25" t="s">
-        <v>91</v>
+        <v>43</v>
       </c>
       <c r="G25" t="s">
         <v>20</v>
       </c>
       <c r="H25" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="I25" t="s">
         <v>22</v>
       </c>
       <c r="J25" t="s">
+        <v>158</v>
+      </c>
+      <c r="K25" t="s">
+        <v>159</v>
+      </c>
+      <c r="L25" t="s">
+        <v>22</v>
+      </c>
+      <c r="M25" t="s">
+        <v>22</v>
+      </c>
+      <c r="N25" t="s">
+        <v>22</v>
+      </c>
+      <c r="O25" t="s">
         <v>160</v>
-      </c>
-      <c r="K25" t="s">
-        <v>161</v>
-      </c>
-      <c r="L25" t="s">
-        <v>22</v>
-      </c>
-      <c r="M25" t="s">
-        <v>22</v>
-      </c>
-      <c r="N25" t="s">
-        <v>22</v>
-      </c>
-      <c r="O25" t="s">
-        <v>162</v>
       </c>
     </row>
     <row r="26" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="B26" t="s">
-        <v>113</v>
+        <v>126</v>
       </c>
       <c r="C26" t="s">
-        <v>114</v>
+        <v>65</v>
       </c>
       <c r="D26" t="s">
         <v>18</v>
       </c>
       <c r="E26" t="s">
-        <v>115</v>
+        <v>18</v>
       </c>
       <c r="F26" t="s">
-        <v>91</v>
+        <v>105</v>
       </c>
       <c r="G26" t="s">
         <v>20</v>
       </c>
       <c r="H26" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="I26" t="s">
         <v>22</v>
       </c>
       <c r="J26" t="s">
+        <v>162</v>
+      </c>
+      <c r="K26" t="s">
+        <v>163</v>
+      </c>
+      <c r="L26" t="s">
+        <v>22</v>
+      </c>
+      <c r="M26" t="s">
+        <v>22</v>
+      </c>
+      <c r="N26" t="s">
+        <v>22</v>
+      </c>
+      <c r="O26" t="s">
         <v>164</v>
-      </c>
-      <c r="K26" t="s">
-        <v>93</v>
-      </c>
-      <c r="L26" t="s">
-        <v>22</v>
-      </c>
-      <c r="M26" t="s">
-        <v>22</v>
-      </c>
-      <c r="N26" t="s">
-        <v>22</v>
-      </c>
-      <c r="O26" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="27" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
+        <v>165</v>
+      </c>
+      <c r="B27" t="s">
+        <v>56</v>
+      </c>
+      <c r="C27" t="s">
         <v>166</v>
       </c>
-      <c r="B27" t="s">
+      <c r="D27" t="s">
+        <v>18</v>
+      </c>
+      <c r="E27" t="s">
+        <v>18</v>
+      </c>
+      <c r="F27" t="s">
+        <v>58</v>
+      </c>
+      <c r="G27" t="s">
+        <v>20</v>
+      </c>
+      <c r="H27" t="s">
+        <v>21</v>
+      </c>
+      <c r="I27" t="s">
+        <v>22</v>
+      </c>
+      <c r="J27" t="s">
         <v>167</v>
       </c>
-      <c r="C27" t="s">
-        <v>84</v>
-      </c>
-      <c r="D27" t="s">
-        <v>18</v>
-      </c>
-      <c r="E27" t="s">
-        <v>18</v>
-      </c>
-      <c r="F27" t="s">
-        <v>65</v>
-      </c>
-      <c r="G27" t="s">
+      <c r="K27" t="s">
         <v>168</v>
       </c>
-      <c r="H27" t="s">
-        <v>30</v>
-      </c>
-      <c r="I27" t="s">
-        <v>22</v>
-      </c>
-      <c r="J27" t="s">
+      <c r="L27" t="s">
+        <v>22</v>
+      </c>
+      <c r="M27" t="s">
+        <v>61</v>
+      </c>
+      <c r="N27" t="s">
+        <v>22</v>
+      </c>
+      <c r="O27" t="s">
         <v>169</v>
-      </c>
-      <c r="K27" t="s">
-        <v>170</v>
-      </c>
-      <c r="L27" t="s">
-        <v>22</v>
-      </c>
-      <c r="M27" t="s">
-        <v>69</v>
-      </c>
-      <c r="N27" t="s">
-        <v>22</v>
-      </c>
-      <c r="O27" t="s">
-        <v>171</v>
       </c>
     </row>
     <row r="28" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
+        <v>170</v>
+      </c>
+      <c r="B28" t="s">
+        <v>171</v>
+      </c>
+      <c r="C28" t="s">
         <v>172</v>
       </c>
-      <c r="B28" t="s">
-        <v>173</v>
-      </c>
-      <c r="C28" t="s">
-        <v>174</v>
-      </c>
       <c r="D28" t="s">
-        <v>175</v>
+        <v>18</v>
       </c>
       <c r="E28" t="s">
-        <v>115</v>
+        <v>18</v>
       </c>
       <c r="F28" t="s">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="G28" t="s">
         <v>20</v>
       </c>
       <c r="H28" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="I28" t="s">
         <v>22</v>
       </c>
       <c r="J28" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="K28" t="s">
-        <v>177</v>
+        <v>132</v>
       </c>
       <c r="L28" t="s">
         <v>22</v>
       </c>
       <c r="M28" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
       <c r="N28" t="s">
         <v>22</v>
       </c>
       <c r="O28" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
     </row>
     <row r="29" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="B29" t="s">
-        <v>180</v>
+        <v>27</v>
       </c>
       <c r="C29" t="s">
-        <v>181</v>
+        <v>28</v>
       </c>
       <c r="D29" t="s">
         <v>18</v>
@@ -2672,69 +2600,69 @@
         <v>18</v>
       </c>
       <c r="F29" t="s">
-        <v>29</v>
+        <v>58</v>
       </c>
       <c r="G29" t="s">
-        <v>182</v>
+        <v>20</v>
       </c>
       <c r="H29" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="I29" t="s">
         <v>22</v>
       </c>
       <c r="J29" t="s">
-        <v>183</v>
+        <v>176</v>
       </c>
       <c r="K29" t="s">
-        <v>184</v>
+        <v>45</v>
       </c>
       <c r="L29" t="s">
         <v>22</v>
       </c>
       <c r="M29" t="s">
-        <v>22</v>
+        <v>61</v>
       </c>
       <c r="N29" t="s">
-        <v>185</v>
+        <v>22</v>
       </c>
       <c r="O29" t="s">
-        <v>186</v>
+        <v>177</v>
       </c>
     </row>
     <row r="30" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>187</v>
+        <v>178</v>
       </c>
       <c r="B30" t="s">
-        <v>113</v>
+        <v>179</v>
       </c>
       <c r="C30" t="s">
-        <v>114</v>
+        <v>91</v>
       </c>
       <c r="D30" t="s">
         <v>18</v>
       </c>
       <c r="E30" t="s">
-        <v>115</v>
+        <v>75</v>
       </c>
       <c r="F30" t="s">
-        <v>19</v>
+        <v>35</v>
       </c>
       <c r="G30" t="s">
-        <v>168</v>
+        <v>180</v>
       </c>
       <c r="H30" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="I30" t="s">
         <v>22</v>
       </c>
       <c r="J30" t="s">
-        <v>188</v>
+        <v>181</v>
       </c>
       <c r="K30" t="s">
-        <v>189</v>
+        <v>182</v>
       </c>
       <c r="L30" t="s">
         <v>22</v>
@@ -2743,21 +2671,21 @@
         <v>22</v>
       </c>
       <c r="N30" t="s">
-        <v>22</v>
+        <v>183</v>
       </c>
       <c r="O30" t="s">
-        <v>190</v>
+        <v>184</v>
       </c>
     </row>
     <row r="31" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>191</v>
+        <v>185</v>
       </c>
       <c r="B31" t="s">
-        <v>192</v>
+        <v>186</v>
       </c>
       <c r="C31" t="s">
-        <v>193</v>
+        <v>111</v>
       </c>
       <c r="D31" t="s">
         <v>18</v>
@@ -2766,69 +2694,69 @@
         <v>18</v>
       </c>
       <c r="F31" t="s">
-        <v>91</v>
+        <v>58</v>
       </c>
       <c r="G31" t="s">
         <v>20</v>
       </c>
       <c r="H31" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="I31" t="s">
-        <v>194</v>
+        <v>22</v>
       </c>
       <c r="J31" t="s">
-        <v>195</v>
+        <v>187</v>
       </c>
       <c r="K31" t="s">
-        <v>196</v>
+        <v>188</v>
       </c>
       <c r="L31" t="s">
         <v>22</v>
       </c>
       <c r="M31" t="s">
-        <v>22</v>
+        <v>61</v>
       </c>
       <c r="N31" t="s">
         <v>22</v>
       </c>
       <c r="O31" t="s">
-        <v>197</v>
+        <v>189</v>
       </c>
     </row>
     <row r="32" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>198</v>
+        <v>190</v>
       </c>
       <c r="B32" t="s">
-        <v>140</v>
+        <v>110</v>
       </c>
       <c r="C32" t="s">
-        <v>199</v>
+        <v>111</v>
       </c>
       <c r="D32" t="s">
         <v>18</v>
       </c>
       <c r="E32" t="s">
-        <v>115</v>
+        <v>18</v>
       </c>
       <c r="F32" t="s">
-        <v>91</v>
+        <v>105</v>
       </c>
       <c r="G32" t="s">
-        <v>200</v>
+        <v>20</v>
       </c>
       <c r="H32" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="I32" t="s">
         <v>22</v>
       </c>
       <c r="J32" t="s">
-        <v>201</v>
+        <v>191</v>
       </c>
       <c r="K32" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="L32" t="s">
         <v>22</v>
@@ -2840,42 +2768,42 @@
         <v>22</v>
       </c>
       <c r="O32" t="s">
-        <v>202</v>
+        <v>192</v>
       </c>
     </row>
     <row r="33" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>203</v>
+        <v>193</v>
       </c>
       <c r="B33" t="s">
-        <v>173</v>
+        <v>194</v>
       </c>
       <c r="C33" t="s">
-        <v>174</v>
+        <v>195</v>
       </c>
       <c r="D33" t="s">
-        <v>175</v>
+        <v>18</v>
       </c>
       <c r="E33" t="s">
-        <v>115</v>
+        <v>18</v>
       </c>
       <c r="F33" t="s">
-        <v>19</v>
+        <v>105</v>
       </c>
       <c r="G33" t="s">
-        <v>20</v>
+        <v>36</v>
       </c>
       <c r="H33" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="I33" t="s">
-        <v>194</v>
+        <v>22</v>
       </c>
       <c r="J33" t="s">
-        <v>204</v>
+        <v>196</v>
       </c>
       <c r="K33" t="s">
-        <v>205</v>
+        <v>159</v>
       </c>
       <c r="L33" t="s">
         <v>22</v>
@@ -2887,112 +2815,112 @@
         <v>22</v>
       </c>
       <c r="O33" t="s">
-        <v>206</v>
+        <v>197</v>
       </c>
     </row>
     <row r="34" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>207</v>
+        <v>198</v>
       </c>
       <c r="B34" t="s">
-        <v>167</v>
+        <v>156</v>
       </c>
       <c r="C34" t="s">
-        <v>84</v>
+        <v>157</v>
       </c>
       <c r="D34" t="s">
         <v>18</v>
       </c>
       <c r="E34" t="s">
-        <v>18</v>
+        <v>75</v>
       </c>
       <c r="F34" t="s">
-        <v>65</v>
+        <v>19</v>
       </c>
       <c r="G34" t="s">
         <v>20</v>
       </c>
       <c r="H34" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="I34" t="s">
         <v>22</v>
       </c>
       <c r="J34" t="s">
-        <v>208</v>
+        <v>199</v>
       </c>
       <c r="K34" t="s">
-        <v>209</v>
+        <v>200</v>
       </c>
       <c r="L34" t="s">
         <v>22</v>
       </c>
       <c r="M34" t="s">
-        <v>69</v>
+        <v>22</v>
       </c>
       <c r="N34" t="s">
         <v>22</v>
       </c>
       <c r="O34" t="s">
-        <v>210</v>
+        <v>201</v>
       </c>
     </row>
     <row r="35" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>211</v>
+        <v>202</v>
       </c>
       <c r="B35" t="s">
-        <v>134</v>
+        <v>156</v>
       </c>
       <c r="C35" t="s">
-        <v>135</v>
+        <v>157</v>
       </c>
       <c r="D35" t="s">
         <v>18</v>
       </c>
       <c r="E35" t="s">
-        <v>18</v>
+        <v>75</v>
       </c>
       <c r="F35" t="s">
-        <v>65</v>
+        <v>19</v>
       </c>
       <c r="G35" t="s">
         <v>20</v>
       </c>
       <c r="H35" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="I35" t="s">
-        <v>104</v>
+        <v>22</v>
       </c>
       <c r="J35" t="s">
-        <v>212</v>
+        <v>203</v>
       </c>
       <c r="K35" t="s">
-        <v>213</v>
+        <v>138</v>
       </c>
       <c r="L35" t="s">
         <v>22</v>
       </c>
       <c r="M35" t="s">
-        <v>69</v>
+        <v>22</v>
       </c>
       <c r="N35" t="s">
         <v>22</v>
       </c>
       <c r="O35" t="s">
-        <v>214</v>
+        <v>204</v>
       </c>
     </row>
     <row r="36" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>215</v>
+        <v>205</v>
       </c>
       <c r="B36" t="s">
-        <v>89</v>
+        <v>206</v>
       </c>
       <c r="C36" t="s">
-        <v>90</v>
+        <v>57</v>
       </c>
       <c r="D36" t="s">
         <v>18</v>
@@ -3001,92 +2929,92 @@
         <v>18</v>
       </c>
       <c r="F36" t="s">
-        <v>29</v>
+        <v>58</v>
       </c>
       <c r="G36" t="s">
-        <v>20</v>
+        <v>207</v>
       </c>
       <c r="H36" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="I36" t="s">
-        <v>104</v>
+        <v>22</v>
       </c>
       <c r="J36" t="s">
-        <v>216</v>
+        <v>208</v>
       </c>
       <c r="K36" t="s">
-        <v>69</v>
+        <v>209</v>
       </c>
       <c r="L36" t="s">
         <v>22</v>
       </c>
       <c r="M36" t="s">
-        <v>22</v>
+        <v>61</v>
       </c>
       <c r="N36" t="s">
-        <v>217</v>
+        <v>22</v>
       </c>
       <c r="O36" t="s">
-        <v>218</v>
+        <v>210</v>
       </c>
     </row>
     <row r="37" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>219</v>
+        <v>211</v>
       </c>
       <c r="B37" t="s">
-        <v>180</v>
+        <v>72</v>
       </c>
       <c r="C37" t="s">
-        <v>181</v>
+        <v>73</v>
       </c>
       <c r="D37" t="s">
-        <v>18</v>
+        <v>74</v>
       </c>
       <c r="E37" t="s">
-        <v>18</v>
+        <v>75</v>
       </c>
       <c r="F37" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="G37" t="s">
-        <v>38</v>
+        <v>20</v>
       </c>
       <c r="H37" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="I37" t="s">
-        <v>104</v>
+        <v>22</v>
       </c>
       <c r="J37" t="s">
-        <v>220</v>
+        <v>212</v>
       </c>
       <c r="K37" t="s">
-        <v>221</v>
+        <v>213</v>
       </c>
       <c r="L37" t="s">
         <v>22</v>
       </c>
       <c r="M37" t="s">
-        <v>22</v>
+        <v>61</v>
       </c>
       <c r="N37" t="s">
         <v>22</v>
       </c>
       <c r="O37" t="s">
-        <v>222</v>
+        <v>214</v>
       </c>
     </row>
     <row r="38" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>223</v>
+        <v>215</v>
       </c>
       <c r="B38" t="s">
-        <v>224</v>
+        <v>216</v>
       </c>
       <c r="C38" t="s">
-        <v>225</v>
+        <v>217</v>
       </c>
       <c r="D38" t="s">
         <v>18</v>
@@ -3095,22 +3023,22 @@
         <v>18</v>
       </c>
       <c r="F38" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="G38" t="s">
-        <v>226</v>
+        <v>218</v>
       </c>
       <c r="H38" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="I38" t="s">
-        <v>104</v>
+        <v>22</v>
       </c>
       <c r="J38" t="s">
-        <v>227</v>
+        <v>219</v>
       </c>
       <c r="K38" t="s">
-        <v>40</v>
+        <v>220</v>
       </c>
       <c r="L38" t="s">
         <v>22</v>
@@ -3119,68 +3047,68 @@
         <v>22</v>
       </c>
       <c r="N38" t="s">
-        <v>228</v>
+        <v>53</v>
       </c>
       <c r="O38" t="s">
-        <v>229</v>
+        <v>221</v>
       </c>
     </row>
     <row r="39" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>230</v>
+        <v>222</v>
       </c>
       <c r="B39" t="s">
+        <v>156</v>
+      </c>
+      <c r="C39" t="s">
+        <v>157</v>
+      </c>
+      <c r="D39" t="s">
+        <v>18</v>
+      </c>
+      <c r="E39" t="s">
+        <v>75</v>
+      </c>
+      <c r="F39" t="s">
+        <v>43</v>
+      </c>
+      <c r="G39" t="s">
+        <v>207</v>
+      </c>
+      <c r="H39" t="s">
+        <v>21</v>
+      </c>
+      <c r="I39" t="s">
+        <v>22</v>
+      </c>
+      <c r="J39" t="s">
+        <v>223</v>
+      </c>
+      <c r="K39" t="s">
         <v>224</v>
       </c>
-      <c r="C39" t="s">
+      <c r="L39" t="s">
+        <v>22</v>
+      </c>
+      <c r="M39" t="s">
+        <v>22</v>
+      </c>
+      <c r="N39" t="s">
+        <v>22</v>
+      </c>
+      <c r="O39" t="s">
         <v>225</v>
-      </c>
-      <c r="D39" t="s">
-        <v>18</v>
-      </c>
-      <c r="E39" t="s">
-        <v>18</v>
-      </c>
-      <c r="F39" t="s">
-        <v>29</v>
-      </c>
-      <c r="G39" t="s">
-        <v>231</v>
-      </c>
-      <c r="H39" t="s">
-        <v>30</v>
-      </c>
-      <c r="I39" t="s">
-        <v>104</v>
-      </c>
-      <c r="J39" t="s">
-        <v>232</v>
-      </c>
-      <c r="K39" t="s">
-        <v>233</v>
-      </c>
-      <c r="L39" t="s">
-        <v>22</v>
-      </c>
-      <c r="M39" t="s">
-        <v>22</v>
-      </c>
-      <c r="N39" t="s">
-        <v>234</v>
-      </c>
-      <c r="O39" t="s">
-        <v>235</v>
       </c>
     </row>
     <row r="40" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>236</v>
+        <v>226</v>
       </c>
       <c r="B40" t="s">
-        <v>27</v>
+        <v>227</v>
       </c>
       <c r="C40" t="s">
-        <v>193</v>
+        <v>228</v>
       </c>
       <c r="D40" t="s">
         <v>18</v>
@@ -3189,22 +3117,22 @@
         <v>18</v>
       </c>
       <c r="F40" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="G40" t="s">
-        <v>237</v>
+        <v>20</v>
       </c>
       <c r="H40" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="I40" t="s">
-        <v>104</v>
+        <v>229</v>
       </c>
       <c r="J40" t="s">
-        <v>238</v>
+        <v>230</v>
       </c>
       <c r="K40" t="s">
-        <v>239</v>
+        <v>231</v>
       </c>
       <c r="L40" t="s">
         <v>22</v>
@@ -3213,45 +3141,45 @@
         <v>22</v>
       </c>
       <c r="N40" t="s">
-        <v>240</v>
+        <v>22</v>
       </c>
       <c r="O40" t="s">
-        <v>241</v>
+        <v>232</v>
       </c>
     </row>
     <row r="41" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>242</v>
+        <v>233</v>
       </c>
       <c r="B41" t="s">
-        <v>243</v>
+        <v>179</v>
       </c>
       <c r="C41" t="s">
-        <v>124</v>
+        <v>234</v>
       </c>
       <c r="D41" t="s">
         <v>18</v>
       </c>
       <c r="E41" t="s">
-        <v>18</v>
+        <v>75</v>
       </c>
       <c r="F41" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="G41" t="s">
-        <v>38</v>
+        <v>235</v>
       </c>
       <c r="H41" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="I41" t="s">
-        <v>104</v>
+        <v>22</v>
       </c>
       <c r="J41" t="s">
-        <v>244</v>
+        <v>236</v>
       </c>
       <c r="K41" t="s">
-        <v>245</v>
+        <v>200</v>
       </c>
       <c r="L41" t="s">
         <v>22</v>
@@ -3260,45 +3188,45 @@
         <v>22</v>
       </c>
       <c r="N41" t="s">
-        <v>246</v>
+        <v>22</v>
       </c>
       <c r="O41" t="s">
-        <v>247</v>
+        <v>237</v>
       </c>
     </row>
     <row r="42" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>248</v>
+        <v>238</v>
       </c>
       <c r="B42" t="s">
-        <v>249</v>
+        <v>72</v>
       </c>
       <c r="C42" t="s">
-        <v>250</v>
+        <v>73</v>
       </c>
       <c r="D42" t="s">
-        <v>18</v>
+        <v>74</v>
       </c>
       <c r="E42" t="s">
-        <v>18</v>
+        <v>75</v>
       </c>
       <c r="F42" t="s">
-        <v>29</v>
+        <v>43</v>
       </c>
       <c r="G42" t="s">
-        <v>251</v>
+        <v>20</v>
       </c>
       <c r="H42" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="I42" t="s">
-        <v>252</v>
+        <v>229</v>
       </c>
       <c r="J42" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="K42" t="s">
-        <v>254</v>
+        <v>240</v>
       </c>
       <c r="L42" t="s">
         <v>22</v>
@@ -3307,21 +3235,21 @@
         <v>22</v>
       </c>
       <c r="N42" t="s">
-        <v>255</v>
+        <v>22</v>
       </c>
       <c r="O42" t="s">
-        <v>256</v>
+        <v>241</v>
       </c>
     </row>
     <row r="43" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>257</v>
+        <v>242</v>
       </c>
       <c r="B43" t="s">
-        <v>249</v>
+        <v>206</v>
       </c>
       <c r="C43" t="s">
-        <v>250</v>
+        <v>57</v>
       </c>
       <c r="D43" t="s">
         <v>18</v>
@@ -3330,45 +3258,45 @@
         <v>18</v>
       </c>
       <c r="F43" t="s">
-        <v>258</v>
+        <v>58</v>
       </c>
       <c r="G43" t="s">
-        <v>259</v>
+        <v>20</v>
       </c>
       <c r="H43" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="I43" t="s">
-        <v>252</v>
+        <v>22</v>
       </c>
       <c r="J43" t="s">
-        <v>260</v>
+        <v>243</v>
       </c>
       <c r="K43" t="s">
-        <v>24</v>
+        <v>244</v>
       </c>
       <c r="L43" t="s">
         <v>22</v>
       </c>
       <c r="M43" t="s">
-        <v>22</v>
+        <v>61</v>
       </c>
       <c r="N43" t="s">
         <v>22</v>
       </c>
       <c r="O43" t="s">
-        <v>261</v>
+        <v>245</v>
       </c>
     </row>
     <row r="44" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>262</v>
+        <v>246</v>
       </c>
       <c r="B44" t="s">
-        <v>167</v>
+        <v>27</v>
       </c>
       <c r="C44" t="s">
-        <v>84</v>
+        <v>28</v>
       </c>
       <c r="D44" t="s">
         <v>18</v>
@@ -3377,69 +3305,69 @@
         <v>18</v>
       </c>
       <c r="F44" t="s">
-        <v>29</v>
+        <v>58</v>
       </c>
       <c r="G44" t="s">
-        <v>182</v>
+        <v>20</v>
       </c>
       <c r="H44" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="I44" t="s">
-        <v>104</v>
+        <v>148</v>
       </c>
       <c r="J44" t="s">
-        <v>263</v>
+        <v>247</v>
       </c>
       <c r="K44" t="s">
-        <v>264</v>
+        <v>248</v>
       </c>
       <c r="L44" t="s">
         <v>22</v>
       </c>
       <c r="M44" t="s">
-        <v>22</v>
+        <v>61</v>
       </c>
       <c r="N44" t="s">
-        <v>265</v>
+        <v>22</v>
       </c>
       <c r="O44" t="s">
-        <v>266</v>
+        <v>249</v>
       </c>
     </row>
     <row r="45" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>267</v>
+        <v>250</v>
       </c>
       <c r="B45" t="s">
-        <v>113</v>
+        <v>135</v>
       </c>
       <c r="C45" t="s">
-        <v>114</v>
+        <v>136</v>
       </c>
       <c r="D45" t="s">
         <v>18</v>
       </c>
       <c r="E45" t="s">
-        <v>115</v>
+        <v>18</v>
       </c>
       <c r="F45" t="s">
-        <v>258</v>
+        <v>35</v>
       </c>
       <c r="G45" t="s">
-        <v>268</v>
+        <v>20</v>
       </c>
       <c r="H45" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="I45" t="s">
-        <v>104</v>
+        <v>148</v>
       </c>
       <c r="J45" t="s">
-        <v>269</v>
+        <v>251</v>
       </c>
       <c r="K45" t="s">
-        <v>48</v>
+        <v>61</v>
       </c>
       <c r="L45" t="s">
         <v>22</v>
@@ -3448,92 +3376,92 @@
         <v>22</v>
       </c>
       <c r="N45" t="s">
-        <v>22</v>
+        <v>252</v>
       </c>
       <c r="O45" t="s">
-        <v>270</v>
+        <v>253</v>
       </c>
     </row>
     <row r="46" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>271</v>
+        <v>254</v>
       </c>
       <c r="B46" t="s">
-        <v>113</v>
+        <v>216</v>
       </c>
       <c r="C46" t="s">
-        <v>114</v>
+        <v>217</v>
       </c>
       <c r="D46" t="s">
         <v>18</v>
       </c>
       <c r="E46" t="s">
-        <v>115</v>
+        <v>18</v>
       </c>
       <c r="F46" t="s">
-        <v>65</v>
+        <v>105</v>
       </c>
       <c r="G46" t="s">
-        <v>20</v>
+        <v>36</v>
       </c>
       <c r="H46" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="I46" t="s">
-        <v>104</v>
+        <v>148</v>
       </c>
       <c r="J46" t="s">
-        <v>272</v>
+        <v>255</v>
       </c>
       <c r="K46" t="s">
-        <v>273</v>
+        <v>256</v>
       </c>
       <c r="L46" t="s">
         <v>22</v>
       </c>
       <c r="M46" t="s">
-        <v>69</v>
+        <v>22</v>
       </c>
       <c r="N46" t="s">
         <v>22</v>
       </c>
       <c r="O46" t="s">
-        <v>274</v>
+        <v>257</v>
       </c>
     </row>
     <row r="47" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>275</v>
+        <v>258</v>
       </c>
       <c r="B47" t="s">
-        <v>276</v>
+        <v>259</v>
       </c>
       <c r="C47" t="s">
-        <v>59</v>
+        <v>260</v>
       </c>
       <c r="D47" t="s">
         <v>18</v>
       </c>
       <c r="E47" t="s">
-        <v>277</v>
+        <v>18</v>
       </c>
       <c r="F47" t="s">
-        <v>19</v>
+        <v>35</v>
       </c>
       <c r="G47" t="s">
-        <v>20</v>
+        <v>261</v>
       </c>
       <c r="H47" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="I47" t="s">
-        <v>104</v>
+        <v>148</v>
       </c>
       <c r="J47" t="s">
-        <v>278</v>
+        <v>262</v>
       </c>
       <c r="K47" t="s">
-        <v>273</v>
+        <v>93</v>
       </c>
       <c r="L47" t="s">
         <v>22</v>
@@ -3542,21 +3470,21 @@
         <v>22</v>
       </c>
       <c r="N47" t="s">
-        <v>22</v>
+        <v>263</v>
       </c>
       <c r="O47" t="s">
-        <v>279</v>
+        <v>264</v>
       </c>
     </row>
     <row r="48" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>280</v>
+        <v>265</v>
       </c>
       <c r="B48" t="s">
-        <v>224</v>
+        <v>259</v>
       </c>
       <c r="C48" t="s">
-        <v>225</v>
+        <v>260</v>
       </c>
       <c r="D48" t="s">
         <v>18</v>
@@ -3565,22 +3493,22 @@
         <v>18</v>
       </c>
       <c r="F48" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="G48" t="s">
-        <v>182</v>
+        <v>266</v>
       </c>
       <c r="H48" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="I48" t="s">
-        <v>104</v>
+        <v>148</v>
       </c>
       <c r="J48" t="s">
-        <v>281</v>
+        <v>267</v>
       </c>
       <c r="K48" t="s">
-        <v>93</v>
+        <v>268</v>
       </c>
       <c r="L48" t="s">
         <v>22</v>
@@ -3589,21 +3517,21 @@
         <v>22</v>
       </c>
       <c r="N48" t="s">
-        <v>246</v>
+        <v>269</v>
       </c>
       <c r="O48" t="s">
-        <v>282</v>
+        <v>270</v>
       </c>
     </row>
     <row r="49" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>283</v>
+        <v>271</v>
       </c>
       <c r="B49" t="s">
-        <v>284</v>
+        <v>84</v>
       </c>
       <c r="C49" t="s">
-        <v>285</v>
+        <v>228</v>
       </c>
       <c r="D49" t="s">
         <v>18</v>
@@ -3612,22 +3540,22 @@
         <v>18</v>
       </c>
       <c r="F49" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="G49" t="s">
-        <v>182</v>
+        <v>272</v>
       </c>
       <c r="H49" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="I49" t="s">
-        <v>104</v>
+        <v>148</v>
       </c>
       <c r="J49" t="s">
-        <v>286</v>
+        <v>273</v>
       </c>
       <c r="K49" t="s">
-        <v>287</v>
+        <v>274</v>
       </c>
       <c r="L49" t="s">
         <v>22</v>
@@ -3636,21 +3564,21 @@
         <v>22</v>
       </c>
       <c r="N49" t="s">
-        <v>288</v>
+        <v>40</v>
       </c>
       <c r="O49" t="s">
-        <v>289</v>
+        <v>275</v>
       </c>
     </row>
     <row r="50" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>290</v>
+        <v>276</v>
       </c>
       <c r="B50" t="s">
-        <v>102</v>
+        <v>277</v>
       </c>
       <c r="C50" t="s">
-        <v>291</v>
+        <v>166</v>
       </c>
       <c r="D50" t="s">
         <v>18</v>
@@ -3659,22 +3587,22 @@
         <v>18</v>
       </c>
       <c r="F50" t="s">
-        <v>258</v>
+        <v>35</v>
       </c>
       <c r="G50" t="s">
-        <v>268</v>
+        <v>36</v>
       </c>
       <c r="H50" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="I50" t="s">
-        <v>104</v>
+        <v>148</v>
       </c>
       <c r="J50" t="s">
-        <v>292</v>
+        <v>278</v>
       </c>
       <c r="K50" t="s">
-        <v>293</v>
+        <v>279</v>
       </c>
       <c r="L50" t="s">
         <v>22</v>
@@ -3683,21 +3611,21 @@
         <v>22</v>
       </c>
       <c r="N50" t="s">
-        <v>22</v>
+        <v>280</v>
       </c>
       <c r="O50" t="s">
-        <v>294</v>
+        <v>281</v>
       </c>
     </row>
     <row r="51" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>295</v>
+        <v>282</v>
       </c>
       <c r="B51" t="s">
-        <v>102</v>
+        <v>283</v>
       </c>
       <c r="C51" t="s">
-        <v>291</v>
+        <v>284</v>
       </c>
       <c r="D51" t="s">
         <v>18</v>
@@ -3706,22 +3634,22 @@
         <v>18</v>
       </c>
       <c r="F51" t="s">
-        <v>258</v>
+        <v>35</v>
       </c>
       <c r="G51" t="s">
-        <v>296</v>
+        <v>285</v>
       </c>
       <c r="H51" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="I51" t="s">
-        <v>104</v>
+        <v>286</v>
       </c>
       <c r="J51" t="s">
-        <v>297</v>
+        <v>287</v>
       </c>
       <c r="K51" t="s">
-        <v>189</v>
+        <v>288</v>
       </c>
       <c r="L51" t="s">
         <v>22</v>
@@ -3730,245 +3658,10 @@
         <v>22</v>
       </c>
       <c r="N51" t="s">
-        <v>22</v>
+        <v>289</v>
       </c>
       <c r="O51" t="s">
-        <v>298</v>
-      </c>
-    </row>
-    <row r="52" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A52" t="s">
-        <v>299</v>
-      </c>
-      <c r="B52" t="s">
-        <v>102</v>
-      </c>
-      <c r="C52" t="s">
-        <v>291</v>
-      </c>
-      <c r="D52" t="s">
-        <v>18</v>
-      </c>
-      <c r="E52" t="s">
-        <v>18</v>
-      </c>
-      <c r="F52" t="s">
-        <v>29</v>
-      </c>
-      <c r="G52" t="s">
-        <v>168</v>
-      </c>
-      <c r="H52" t="s">
-        <v>30</v>
-      </c>
-      <c r="I52" t="s">
-        <v>104</v>
-      </c>
-      <c r="J52" t="s">
-        <v>300</v>
-      </c>
-      <c r="K52" t="s">
-        <v>69</v>
-      </c>
-      <c r="L52" t="s">
-        <v>22</v>
-      </c>
-      <c r="M52" t="s">
-        <v>22</v>
-      </c>
-      <c r="N52" t="s">
-        <v>228</v>
-      </c>
-      <c r="O52" t="s">
-        <v>301</v>
-      </c>
-    </row>
-    <row r="53" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A53" t="s">
-        <v>302</v>
-      </c>
-      <c r="B53" t="s">
-        <v>58</v>
-      </c>
-      <c r="C53" t="s">
-        <v>97</v>
-      </c>
-      <c r="D53" t="s">
-        <v>18</v>
-      </c>
-      <c r="E53" t="s">
-        <v>18</v>
-      </c>
-      <c r="F53" t="s">
-        <v>19</v>
-      </c>
-      <c r="G53" t="s">
-        <v>20</v>
-      </c>
-      <c r="H53" t="s">
-        <v>30</v>
-      </c>
-      <c r="I53" t="s">
-        <v>104</v>
-      </c>
-      <c r="J53" t="s">
-        <v>303</v>
-      </c>
-      <c r="K53" t="s">
-        <v>177</v>
-      </c>
-      <c r="L53" t="s">
-        <v>22</v>
-      </c>
-      <c r="M53" t="s">
-        <v>22</v>
-      </c>
-      <c r="N53" t="s">
-        <v>22</v>
-      </c>
-      <c r="O53" t="s">
-        <v>304</v>
-      </c>
-    </row>
-    <row r="54" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A54" t="s">
-        <v>305</v>
-      </c>
-      <c r="B54" t="s">
-        <v>83</v>
-      </c>
-      <c r="C54" t="s">
-        <v>90</v>
-      </c>
-      <c r="D54" t="s">
-        <v>18</v>
-      </c>
-      <c r="E54" t="s">
-        <v>18</v>
-      </c>
-      <c r="F54" t="s">
-        <v>29</v>
-      </c>
-      <c r="G54" t="s">
-        <v>20</v>
-      </c>
-      <c r="H54" t="s">
-        <v>30</v>
-      </c>
-      <c r="I54" t="s">
-        <v>104</v>
-      </c>
-      <c r="J54" t="s">
-        <v>306</v>
-      </c>
-      <c r="K54" t="s">
-        <v>161</v>
-      </c>
-      <c r="L54" t="s">
-        <v>22</v>
-      </c>
-      <c r="M54" t="s">
-        <v>22</v>
-      </c>
-      <c r="N54" t="s">
-        <v>307</v>
-      </c>
-      <c r="O54" t="s">
-        <v>308</v>
-      </c>
-    </row>
-    <row r="55" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A55" t="s">
-        <v>309</v>
-      </c>
-      <c r="B55" t="s">
-        <v>113</v>
-      </c>
-      <c r="C55" t="s">
-        <v>114</v>
-      </c>
-      <c r="D55" t="s">
-        <v>18</v>
-      </c>
-      <c r="E55" t="s">
-        <v>115</v>
-      </c>
-      <c r="F55" t="s">
-        <v>65</v>
-      </c>
-      <c r="G55" t="s">
-        <v>38</v>
-      </c>
-      <c r="H55" t="s">
-        <v>30</v>
-      </c>
-      <c r="I55" t="s">
-        <v>104</v>
-      </c>
-      <c r="J55" t="s">
-        <v>310</v>
-      </c>
-      <c r="K55" t="s">
-        <v>149</v>
-      </c>
-      <c r="L55" t="s">
-        <v>22</v>
-      </c>
-      <c r="M55" t="s">
-        <v>69</v>
-      </c>
-      <c r="N55" t="s">
-        <v>22</v>
-      </c>
-      <c r="O55" t="s">
-        <v>311</v>
-      </c>
-    </row>
-    <row r="56" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A56" t="s">
-        <v>312</v>
-      </c>
-      <c r="B56" t="s">
-        <v>113</v>
-      </c>
-      <c r="C56" t="s">
-        <v>114</v>
-      </c>
-      <c r="D56" t="s">
-        <v>18</v>
-      </c>
-      <c r="E56" t="s">
-        <v>115</v>
-      </c>
-      <c r="F56" t="s">
-        <v>19</v>
-      </c>
-      <c r="G56" t="s">
-        <v>20</v>
-      </c>
-      <c r="H56" t="s">
-        <v>30</v>
-      </c>
-      <c r="I56" t="s">
-        <v>104</v>
-      </c>
-      <c r="J56" t="s">
-        <v>310</v>
-      </c>
-      <c r="K56" t="s">
-        <v>313</v>
-      </c>
-      <c r="L56" t="s">
-        <v>22</v>
-      </c>
-      <c r="M56" t="s">
-        <v>22</v>
-      </c>
-      <c r="N56" t="s">
-        <v>22</v>
-      </c>
-      <c r="O56" t="s">
-        <v>314</v>
+        <v>290</v>
       </c>
     </row>
   </sheetData>
